--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="93">
   <si>
     <t>LMTD</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>KABUPATEN</t>
-  </si>
-  <si>
-    <t>REGION</t>
   </si>
   <si>
     <t>AREA</t>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t>BENGKAYANG</t>
-  </si>
-  <si>
-    <t>KALIMANTAN</t>
   </si>
   <si>
     <t>WEST KALIMANTAN</t>
@@ -305,6 +299,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>NAMA PT</t>
   </si>
 </sst>
 </file>
@@ -914,7 +911,7 @@
     <col min="1" max="1" width="43" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.54296875" bestFit="1" customWidth="1"/>
@@ -1209,31 +1206,31 @@
         <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>11</v>
@@ -1254,7 +1251,7 @@
         <v>46138</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T4" s="13">
         <v>46199</v>
@@ -1263,7 +1260,7 @@
         <v>46229</v>
       </c>
       <c r="V4" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W4" s="14" t="s">
         <v>0</v>
@@ -1275,19 +1272,19 @@
         <v>11</v>
       </c>
       <c r="Z4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="AA4" s="14" t="s">
+      <c r="AB4" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="AB4" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="AC4" s="15">
         <v>46138</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4" s="15">
         <v>46199</v>
@@ -1296,7 +1293,7 @@
         <v>46229</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH4" s="9" t="s">
         <v>0</v>
@@ -1308,10 +1305,10 @@
         <v>4</v>
       </c>
       <c r="AK4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL4" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="AM4" s="9" t="s">
         <v>4</v>
@@ -1320,7 +1317,7 @@
         <v>46138</v>
       </c>
       <c r="AO4" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP4" s="16">
         <v>46199</v>
@@ -1329,7 +1326,7 @@
         <v>46229</v>
       </c>
       <c r="AR4" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS4" s="17" t="s">
         <v>0</v>
@@ -1341,19 +1338,19 @@
         <v>5</v>
       </c>
       <c r="AV4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="AW4" s="17" t="s">
+      <c r="AX4" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>28</v>
       </c>
       <c r="AY4" s="18">
         <v>46138</v>
       </c>
       <c r="AZ4" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4" s="18">
         <v>46199</v>
@@ -1362,7 +1359,7 @@
         <v>46229</v>
       </c>
       <c r="BC4" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD4" s="19" t="s">
         <v>0</v>
@@ -1374,19 +1371,19 @@
         <v>6</v>
       </c>
       <c r="BG4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="BH4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="BH4" s="19" t="s">
+      <c r="BI4" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="BI4" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="BJ4" s="20">
         <v>46138</v>
       </c>
       <c r="BK4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BL4" s="20">
         <v>46199</v>
@@ -1395,7 +1392,7 @@
         <v>46229</v>
       </c>
       <c r="BN4" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BO4" s="21" t="s">
         <v>0</v>
@@ -1407,19 +1404,19 @@
         <v>7</v>
       </c>
       <c r="BR4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="BS4" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="BS4" s="21" t="s">
+      <c r="BT4" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="BT4" s="21" t="s">
-        <v>28</v>
       </c>
       <c r="BU4" s="22">
         <v>46138</v>
       </c>
       <c r="BV4" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW4" s="22">
         <v>46199</v>
@@ -1428,7 +1425,7 @@
         <v>46229</v>
       </c>
       <c r="BY4" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BZ4" s="23" t="s">
         <v>0</v>
@@ -1440,19 +1437,19 @@
         <v>8</v>
       </c>
       <c r="CC4" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="CD4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="CD4" s="23" t="s">
+      <c r="CE4" s="23" t="s">
         <v>27</v>
-      </c>
-      <c r="CE4" s="23" t="s">
-        <v>28</v>
       </c>
       <c r="CF4" s="16">
         <v>46138</v>
       </c>
       <c r="CG4" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CH4" s="16">
         <v>46199</v>
@@ -1461,7 +1458,7 @@
         <v>46229</v>
       </c>
       <c r="CJ4" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CK4" s="17" t="s">
         <v>0</v>
@@ -1473,39 +1470,39 @@
         <v>9</v>
       </c>
       <c r="CN4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="CO4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="CO4" s="17" t="s">
+      <c r="CP4" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="CP4" s="17" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4">
         <v>32.258000000000003</v>
@@ -1514,10 +1511,10 @@
         <v>8</v>
       </c>
       <c r="K5" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L5" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M5" s="44">
         <v>-6.9563784143034102E-3</v>
@@ -1768,28 +1765,28 @@
     </row>
     <row r="6" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4">
         <v>9.1969999999999992</v>
@@ -1798,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L6" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M6" s="44">
         <v>1.4956422478599501E-2</v>
@@ -2052,28 +2049,28 @@
     </row>
     <row r="7" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="4">
         <v>6.1909999999999998</v>
@@ -2082,10 +2079,10 @@
         <v>3</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L7" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M7" s="44">
         <v>-2.18303969287722E-2</v>
@@ -2336,28 +2333,28 @@
     </row>
     <row r="8" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I8" s="4">
         <v>13.444000000000001</v>
@@ -2366,10 +2363,10 @@
         <v>4</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L8" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M8" s="44">
         <v>-1.59724595273714E-3</v>
@@ -2620,22 +2617,22 @@
     </row>
     <row r="9" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>10</v>
@@ -2650,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L9" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M9" s="44">
         <v>-1.34839130517767E-3</v>
@@ -2904,28 +2901,28 @@
     </row>
     <row r="10" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I10" s="4">
         <v>6.2549999999999999</v>
@@ -2934,10 +2931,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M10" s="44">
         <v>-1.8541841050492201E-2</v>
@@ -3188,28 +3185,28 @@
     </row>
     <row r="11" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I11" s="4">
         <v>33.159999999999997</v>
@@ -3218,10 +3215,10 @@
         <v>11</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M11" s="44">
         <v>-3.4738601049839599E-3</v>
@@ -3472,28 +3469,28 @@
     </row>
     <row r="12" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="4">
         <v>23.364000000000001</v>
@@ -3502,10 +3499,10 @@
         <v>7</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L12" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M12" s="44">
         <v>5.1991762586428604E-3</v>
@@ -3756,28 +3753,28 @@
     </row>
     <row r="13" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B13" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I13" s="4">
         <v>15.622</v>
@@ -3786,10 +3783,10 @@
         <v>6</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M13" s="44">
         <v>2.8139270743727102E-2</v>
@@ -4040,28 +4037,28 @@
     </row>
     <row r="14" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" s="4">
         <v>19.111000000000001</v>
@@ -4070,10 +4067,10 @@
         <v>8</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M14" s="44">
         <v>-2.7799390228398599E-2</v>
@@ -4324,22 +4321,22 @@
     </row>
     <row r="15" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B15" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="D15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>10</v>
@@ -4354,10 +4351,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M15" s="44">
         <v>3.0956134924987399E-2</v>
@@ -4608,28 +4605,28 @@
     </row>
     <row r="16" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I16" s="4">
         <v>11.452999999999999</v>
@@ -4638,10 +4635,10 @@
         <v>4</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M16" s="44">
         <v>-2.3381311654927499E-3</v>
@@ -4892,28 +4889,28 @@
     </row>
     <row r="17" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I17" s="4">
         <v>27.367000000000001</v>
@@ -4922,10 +4919,10 @@
         <v>7</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L17" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M17" s="44">
         <v>-1.1165519506899401E-3</v>
@@ -5176,28 +5173,28 @@
     </row>
     <row r="18" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I18" s="4">
         <v>23.956</v>
@@ -5206,10 +5203,10 @@
         <v>9</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M18" s="44">
         <v>6.5544447008488698E-3</v>
@@ -5460,22 +5457,22 @@
     </row>
     <row r="19" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B19" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>10</v>
@@ -5490,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L19" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M19" s="44">
         <v>7.0561324149275198E-2</v>
@@ -5744,28 +5741,28 @@
     </row>
     <row r="20" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="D20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I20" s="4">
         <v>16.844000000000001</v>
@@ -5774,10 +5771,10 @@
         <v>8</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L20" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M20" s="44">
         <v>-5.2672217778418897E-3</v>
@@ -6028,28 +6025,28 @@
     </row>
     <row r="21" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="D21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I21" s="4">
         <v>9.0890000000000004</v>
@@ -6058,10 +6055,10 @@
         <v>5</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L21" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M21" s="44">
         <v>-6.0304671237463102E-2</v>
@@ -6822,7 +6819,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>4</v>
@@ -6839,7 +6836,7 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B2" s="28">
         <v>0.35460000000000003</v>
@@ -6856,7 +6853,7 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="28">
         <v>0.35340000000000005</v>
@@ -6873,7 +6870,7 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="28">
         <v>0.35600000000000004</v>
@@ -6890,7 +6887,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" s="28">
         <v>0.36349999999999999</v>
@@ -6907,7 +6904,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="28">
         <v>0.35320000000000001</v>
@@ -6924,7 +6921,7 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>4</v>
@@ -6941,7 +6938,7 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B10" s="28">
         <v>0.28760000000000002</v>
@@ -6958,7 +6955,7 @@
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="28">
         <v>0.2949</v>
@@ -6975,7 +6972,7 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B12" s="28">
         <v>0.30760000000000004</v>
@@ -6992,7 +6989,7 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B13" s="28">
         <v>0.26419999999999999</v>
@@ -7009,7 +7006,7 @@
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="28">
         <v>0.26170000000000004</v>
@@ -7026,7 +7023,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>4</v>
@@ -7043,7 +7040,7 @@
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" s="28">
         <v>0.19820000000000002</v>
@@ -7060,7 +7057,7 @@
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="28">
         <v>0.20420000000000002</v>
@@ -7077,7 +7074,7 @@
     </row>
     <row r="20" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="28">
         <v>0.2122</v>
@@ -7094,7 +7091,7 @@
     </row>
     <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="28">
         <v>0.23980000000000001</v>
@@ -7111,7 +7108,7 @@
     </row>
     <row r="22" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="28">
         <v>0.18989999999999999</v>
@@ -7128,7 +7125,7 @@
     </row>
     <row r="25" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>4</v>
@@ -7145,7 +7142,7 @@
     </row>
     <row r="26" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26" s="28">
         <v>0.50309999999999999</v>
@@ -7162,7 +7159,7 @@
     </row>
     <row r="27" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="28">
         <v>0.43459999999999999</v>
@@ -7179,7 +7176,7 @@
     </row>
     <row r="28" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B28" s="28">
         <v>0.51649999999999996</v>
@@ -7196,7 +7193,7 @@
     </row>
     <row r="29" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="28">
         <v>0.48899999999999999</v>
@@ -7213,7 +7210,7 @@
     </row>
     <row r="30" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="28">
         <v>0.47710000000000002</v>
@@ -7230,7 +7227,7 @@
     </row>
     <row r="33" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>4</v>
@@ -7247,7 +7244,7 @@
     </row>
     <row r="34" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" s="28">
         <v>0.17910000000000001</v>
@@ -7264,7 +7261,7 @@
     </row>
     <row r="35" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="28">
         <v>0.193</v>
@@ -7281,7 +7278,7 @@
     </row>
     <row r="36" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B36" s="28">
         <v>0.17480000000000001</v>
@@ -7298,7 +7295,7 @@
     </row>
     <row r="37" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="28">
         <v>0.15659999999999999</v>
@@ -7315,7 +7312,7 @@
     </row>
     <row r="38" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="28">
         <v>0.14069999999999999</v>
@@ -7332,7 +7329,7 @@
     </row>
     <row r="41" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>4</v>
@@ -7349,7 +7346,7 @@
     </row>
     <row r="42" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B42" s="28">
         <v>0.37340000000000001</v>
@@ -7366,7 +7363,7 @@
     </row>
     <row r="43" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" s="28">
         <v>0.37729999999999997</v>
@@ -7383,7 +7380,7 @@
     </row>
     <row r="44" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B44" s="28">
         <v>0.36060000000000003</v>
@@ -7400,7 +7397,7 @@
     </row>
     <row r="45" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B45" s="28">
         <v>0.36090000000000005</v>
@@ -7417,7 +7414,7 @@
     </row>
     <row r="46" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" s="28">
         <v>0.36909999999999998</v>
@@ -7434,7 +7431,7 @@
     </row>
     <row r="49" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>4</v>
@@ -7451,7 +7448,7 @@
     </row>
     <row r="50" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B50" s="28">
         <v>0.5262</v>
@@ -7468,7 +7465,7 @@
     </row>
     <row r="51" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" s="28">
         <v>0.54289999999999994</v>
@@ -7485,7 +7482,7 @@
     </row>
     <row r="52" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B52" s="28">
         <v>0.53010000000000002</v>
@@ -7502,7 +7499,7 @@
     </row>
     <row r="53" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B53" s="28">
         <v>0.52560000000000007</v>
@@ -7519,7 +7516,7 @@
     </row>
     <row r="54" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B54" s="28">
         <v>0.55100000000000005</v>
@@ -7536,7 +7533,7 @@
     </row>
     <row r="57" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>4</v>
@@ -7553,7 +7550,7 @@
     </row>
     <row r="58" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B58" s="28">
         <v>0.3836</v>
@@ -7570,7 +7567,7 @@
     </row>
     <row r="59" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="28">
         <v>0.39390000000000003</v>
@@ -7587,7 +7584,7 @@
     </row>
     <row r="60" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B60" s="28">
         <v>0.39479999999999998</v>
@@ -7604,7 +7601,7 @@
     </row>
     <row r="61" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B61" s="28">
         <v>0.41649999999999998</v>
@@ -7621,7 +7618,7 @@
     </row>
     <row r="62" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B62" s="28">
         <v>0.39909999999999995</v>
@@ -7638,7 +7635,7 @@
     </row>
     <row r="65" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>4</v>
@@ -7655,7 +7652,7 @@
     </row>
     <row r="66" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B66" s="28">
         <v>0.42749999999999999</v>
@@ -7672,7 +7669,7 @@
     </row>
     <row r="67" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B67" s="28">
         <v>0.39380000000000004</v>
@@ -7689,7 +7686,7 @@
     </row>
     <row r="68" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B68" s="28">
         <v>0.5</v>
@@ -7706,7 +7703,7 @@
     </row>
     <row r="69" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B69" s="28">
         <v>0.44390000000000002</v>
@@ -7723,7 +7720,7 @@
     </row>
     <row r="70" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" s="28">
         <v>0.434</v>
@@ -7740,7 +7737,7 @@
     </row>
     <row r="73" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>4</v>
@@ -7757,7 +7754,7 @@
     </row>
     <row r="74" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B74" s="28">
         <v>0.28149999999999997</v>
@@ -7774,7 +7771,7 @@
     </row>
     <row r="75" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" s="28">
         <v>0.2742</v>
@@ -7791,7 +7788,7 @@
     </row>
     <row r="76" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B76" s="28">
         <v>0.28260000000000002</v>
@@ -7808,7 +7805,7 @@
     </row>
     <row r="77" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B77" s="28">
         <v>0.30590000000000001</v>
@@ -7825,7 +7822,7 @@
     </row>
     <row r="78" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B78" s="28">
         <v>0.30499999999999999</v>
@@ -7842,7 +7839,7 @@
     </row>
     <row r="81" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>4</v>
@@ -7859,7 +7856,7 @@
     </row>
     <row r="82" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B82" s="28">
         <v>0.3</v>
@@ -7876,7 +7873,7 @@
     </row>
     <row r="83" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B83" s="28">
         <v>0.3</v>
@@ -7893,7 +7890,7 @@
     </row>
     <row r="84" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B84" s="28">
         <v>0.28760000000000002</v>
@@ -7910,7 +7907,7 @@
     </row>
     <row r="85" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B85" s="28">
         <v>0.27550000000000002</v>
@@ -7927,7 +7924,7 @@
     </row>
     <row r="86" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B86" s="28">
         <v>0.30309999999999998</v>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="89" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>4</v>
@@ -7961,7 +7958,7 @@
     </row>
     <row r="90" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B90" s="28">
         <v>0.3342</v>
@@ -7978,7 +7975,7 @@
     </row>
     <row r="91" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B91" s="28">
         <v>0.33679999999999999</v>
@@ -7995,7 +7992,7 @@
     </row>
     <row r="92" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B92" s="28">
         <v>0.31329999999999997</v>
@@ -8012,7 +8009,7 @@
     </row>
     <row r="93" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B93" s="28">
         <v>0.31069999999999998</v>
@@ -8029,7 +8026,7 @@
     </row>
     <row r="94" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B94" s="28">
         <v>0.3</v>
@@ -8046,7 +8043,7 @@
     </row>
     <row r="97" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>4</v>
@@ -8063,7 +8060,7 @@
     </row>
     <row r="98" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B98" s="28">
         <v>0.22949999999999998</v>
@@ -8080,7 +8077,7 @@
     </row>
     <row r="99" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" s="28">
         <v>0.22839999999999999</v>
@@ -8097,7 +8094,7 @@
     </row>
     <row r="100" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B100" s="28">
         <v>0.22889999999999999</v>
@@ -8114,7 +8111,7 @@
     </row>
     <row r="101" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B101" s="28">
         <v>0.22940000000000002</v>
@@ -8131,7 +8128,7 @@
     </row>
     <row r="102" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B102" s="28">
         <v>0.22270000000000001</v>
@@ -8148,7 +8145,7 @@
     </row>
     <row r="105" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>4</v>
@@ -8165,7 +8162,7 @@
     </row>
     <row r="106" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B106" s="28">
         <v>0.1245</v>
@@ -8182,7 +8179,7 @@
     </row>
     <row r="107" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" s="28">
         <v>0.14000000000000001</v>
@@ -8199,7 +8196,7 @@
     </row>
     <row r="108" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B108" s="28">
         <v>0.11550000000000001</v>
@@ -8216,7 +8213,7 @@
     </row>
     <row r="109" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B109" s="28">
         <v>0.12939999999999999</v>
@@ -8233,7 +8230,7 @@
     </row>
     <row r="110" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A110" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B110" s="28">
         <v>0.12869999999999998</v>
@@ -8250,7 +8247,7 @@
     </row>
     <row r="113" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>4</v>
@@ -8267,7 +8264,7 @@
     </row>
     <row r="114" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B114" s="28">
         <v>0.35189999999999999</v>
@@ -8284,7 +8281,7 @@
     </row>
     <row r="115" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B115" s="28">
         <v>0.27360000000000001</v>
@@ -8301,7 +8298,7 @@
     </row>
     <row r="116" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A116" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B116" s="28">
         <v>0.45779999999999998</v>
@@ -8318,7 +8315,7 @@
     </row>
     <row r="117" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B117" s="28">
         <v>0.44579999999999997</v>
@@ -8335,7 +8332,7 @@
     </row>
     <row r="118" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A118" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B118" s="28">
         <v>0.4244</v>
@@ -8352,7 +8349,7 @@
     </row>
     <row r="121" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>4</v>
@@ -8369,7 +8366,7 @@
     </row>
     <row r="122" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B122" s="28">
         <v>0.34100000000000003</v>
@@ -8386,7 +8383,7 @@
     </row>
     <row r="123" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" s="28">
         <v>0.34770000000000001</v>
@@ -8403,7 +8400,7 @@
     </row>
     <row r="124" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B124" s="28">
         <v>0.34429999999999999</v>
@@ -8420,7 +8417,7 @@
     </row>
     <row r="125" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B125" s="28">
         <v>0.34340000000000004</v>
@@ -8437,7 +8434,7 @@
     </row>
     <row r="126" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A126" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B126" s="28">
         <v>0.34100000000000003</v>
@@ -8454,7 +8451,7 @@
     </row>
     <row r="129" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>4</v>
@@ -8471,7 +8468,7 @@
     </row>
     <row r="130" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B130" s="28">
         <v>0.3105</v>
@@ -8488,7 +8485,7 @@
     </row>
     <row r="131" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B131" s="28">
         <v>0.28039999999999998</v>
@@ -8505,7 +8502,7 @@
     </row>
     <row r="132" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B132" s="28">
         <v>0.3251</v>
@@ -8522,7 +8519,7 @@
     </row>
     <row r="133" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B133" s="28">
         <v>0.35729999999999995</v>
@@ -8539,7 +8536,7 @@
     </row>
     <row r="134" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B134" s="28">
         <v>0.31730000000000003</v>
@@ -8569,63 +8566,63 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="E1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="26" t="s">
+      <c r="F1" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="I1" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="J1" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="K1" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="L1" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" s="26" t="s">
+      <c r="M1" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="N1" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="P1" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="Q1" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="R1" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q1" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R1" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B2" s="28">
         <v>0.35460000000000003</v>
@@ -8681,7 +8678,7 @@
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="28">
         <v>0.35340000000000005</v>
@@ -8737,7 +8734,7 @@
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="28">
         <v>0.35600000000000004</v>
@@ -8793,7 +8790,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" s="28">
         <v>0.36349999999999999</v>
@@ -8849,7 +8846,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="28">
         <v>0.35320000000000001</v>
@@ -8905,63 +8902,63 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="26" t="s">
+      <c r="E9" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="26" t="s">
+      <c r="F9" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="G9" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="I9" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="J9" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="26" t="s">
+      <c r="K9" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="26" t="s">
+      <c r="L9" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="26" t="s">
+      <c r="M9" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="N9" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N9" s="26" t="s">
+      <c r="P9" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O9" s="26" t="s">
+      <c r="Q9" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P9" s="26" t="s">
+      <c r="R9" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q9" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="28">
         <v>0.3538</v>
@@ -9017,7 +9014,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11" s="28">
         <v>0.35320000000000001</v>
@@ -9073,63 +9070,63 @@
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="E14" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="26" t="s">
+      <c r="F14" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="G14" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="I14" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="J14" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="K14" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="L14" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="26" t="s">
+      <c r="M14" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="N14" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O14" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="26" t="s">
+      <c r="P14" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O14" s="26" t="s">
+      <c r="Q14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P14" s="26" t="s">
+      <c r="R14" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q14" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R14" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B15" s="28">
         <v>8.7899999999999992E-2</v>
@@ -9185,7 +9182,7 @@
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="28">
         <v>8.7599999999999997E-2</v>
@@ -9241,7 +9238,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="28">
         <v>8.5299999999999987E-2</v>
@@ -9297,7 +9294,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="28">
         <v>8.2899999999999988E-2</v>
@@ -9353,7 +9350,7 @@
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="28">
         <v>8.6599999999999996E-2</v>
@@ -9409,63 +9406,63 @@
     </row>
     <row r="22" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="E22" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="26" t="s">
+      <c r="F22" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="G22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="I22" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H22" s="26" t="s">
+      <c r="J22" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="26" t="s">
+      <c r="K22" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J22" s="26" t="s">
+      <c r="L22" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="26" t="s">
+      <c r="M22" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M22" s="26" t="s">
+      <c r="N22" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O22" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N22" s="26" t="s">
+      <c r="P22" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O22" s="26" t="s">
+      <c r="Q22" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P22" s="26" t="s">
+      <c r="R22" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q22" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R22" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23" s="28">
         <v>8.48E-2</v>
@@ -9521,7 +9518,7 @@
     </row>
     <row r="24" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" s="28">
         <v>8.6599999999999996E-2</v>
@@ -9577,63 +9574,63 @@
     </row>
     <row r="27" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="E27" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="G27" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="I27" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="J27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="K27" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="L27" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L27" s="26" t="s">
+      <c r="M27" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="N27" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N27" s="26" t="s">
+      <c r="P27" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O27" s="26" t="s">
+      <c r="Q27" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P27" s="26" t="s">
+      <c r="R27" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q27" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R27" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="28">
         <v>0.4204</v>
@@ -9689,7 +9686,7 @@
     </row>
     <row r="29" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="28">
         <v>0.42729999999999996</v>
@@ -9745,7 +9742,7 @@
     </row>
     <row r="30" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" s="28">
         <v>0.42520000000000002</v>
@@ -9801,7 +9798,7 @@
     </row>
     <row r="31" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B31" s="28">
         <v>0.42680000000000001</v>
@@ -9857,7 +9854,7 @@
     </row>
     <row r="32" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="28">
         <v>0.42219999999999996</v>
@@ -9913,63 +9910,63 @@
     </row>
     <row r="35" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="26" t="s">
+      <c r="E35" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" s="26" t="s">
+      <c r="F35" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="G35" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H35" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="I35" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H35" s="26" t="s">
+      <c r="J35" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="26" t="s">
+      <c r="K35" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="26" t="s">
+      <c r="L35" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K35" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L35" s="26" t="s">
+      <c r="M35" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M35" s="26" t="s">
+      <c r="N35" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O35" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N35" s="26" t="s">
+      <c r="P35" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O35" s="26" t="s">
+      <c r="Q35" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P35" s="26" t="s">
+      <c r="R35" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q35" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R35" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B36" s="28">
         <v>0.42799999999999999</v>
@@ -10025,7 +10022,7 @@
     </row>
     <row r="37" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B37" s="28">
         <v>0.42219999999999996</v>
@@ -10081,63 +10078,63 @@
     </row>
     <row r="40" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="26" t="s">
+      <c r="E40" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="26" t="s">
+      <c r="F40" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F40" s="26" t="s">
+      <c r="G40" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G40" s="26" t="s">
+      <c r="I40" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H40" s="26" t="s">
+      <c r="J40" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I40" s="26" t="s">
+      <c r="K40" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J40" s="26" t="s">
+      <c r="L40" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L40" s="26" t="s">
+      <c r="M40" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M40" s="26" t="s">
+      <c r="N40" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O40" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N40" s="26" t="s">
+      <c r="P40" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O40" s="26" t="s">
+      <c r="Q40" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P40" s="26" t="s">
+      <c r="R40" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q40" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R40" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B41" s="28">
         <v>0.13720000000000002</v>
@@ -10193,7 +10190,7 @@
     </row>
     <row r="42" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="28">
         <v>0.1318</v>
@@ -10249,7 +10246,7 @@
     </row>
     <row r="43" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B43" s="28">
         <v>0.13350000000000001</v>
@@ -10305,7 +10302,7 @@
     </row>
     <row r="44" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B44" s="28">
         <v>0.1268</v>
@@ -10361,7 +10358,7 @@
     </row>
     <row r="45" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="28">
         <v>0.13800000000000001</v>
@@ -10417,63 +10414,63 @@
     </row>
     <row r="48" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="26" t="s">
+      <c r="E48" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D48" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="26" t="s">
+      <c r="F48" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="G48" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H48" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G48" s="26" t="s">
+      <c r="I48" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="26" t="s">
+      <c r="J48" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I48" s="26" t="s">
+      <c r="K48" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J48" s="26" t="s">
+      <c r="L48" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K48" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L48" s="26" t="s">
+      <c r="M48" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="M48" s="26" t="s">
+      <c r="N48" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O48" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="N48" s="26" t="s">
+      <c r="P48" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="O48" s="26" t="s">
+      <c r="Q48" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="P48" s="26" t="s">
+      <c r="R48" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="Q48" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R48" s="26" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="28">
         <v>0.13339999999999999</v>
@@ -10529,7 +10526,7 @@
     </row>
     <row r="50" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50" s="28">
         <v>0.13800000000000001</v>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="97">
   <si>
     <t>LMTD</t>
   </si>
@@ -303,6 +303,18 @@
   <si>
     <t>NAMA PT</t>
   </si>
+  <si>
+    <t>W4-Jul</t>
+  </si>
+  <si>
+    <t>W4-Aug</t>
+  </si>
+  <si>
+    <t>W5-Aug</t>
+  </si>
+  <si>
+    <t>WoW</t>
+  </si>
 </sst>
 </file>
 
@@ -312,7 +324,7 @@
     <numFmt numFmtId="164" formatCode="mmm\-d"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -395,8 +407,21 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color indexed="8"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,6 +512,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF595959"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -536,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -678,6 +709,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1103,97 +1147,97 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="51" t="s">
+      <c r="R3" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="51" t="s">
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="52"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="51" t="s">
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="AO3" s="52"/>
-      <c r="AP3" s="52"/>
-      <c r="AQ3" s="52"/>
-      <c r="AR3" s="52"/>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="51" t="s">
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
-      <c r="BB3" s="52"/>
-      <c r="BC3" s="52"/>
-      <c r="BD3" s="52"/>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="52"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="52"/>
-      <c r="BJ3" s="51" t="s">
+      <c r="AZ3" s="57"/>
+      <c r="BA3" s="57"/>
+      <c r="BB3" s="57"/>
+      <c r="BC3" s="57"/>
+      <c r="BD3" s="57"/>
+      <c r="BE3" s="57"/>
+      <c r="BF3" s="57"/>
+      <c r="BG3" s="57"/>
+      <c r="BH3" s="57"/>
+      <c r="BI3" s="57"/>
+      <c r="BJ3" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="52"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="52"/>
-      <c r="BP3" s="52"/>
-      <c r="BQ3" s="52"/>
-      <c r="BR3" s="52"/>
-      <c r="BS3" s="52"/>
-      <c r="BT3" s="52"/>
-      <c r="BU3" s="51" t="s">
+      <c r="BK3" s="57"/>
+      <c r="BL3" s="57"/>
+      <c r="BM3" s="57"/>
+      <c r="BN3" s="57"/>
+      <c r="BO3" s="57"/>
+      <c r="BP3" s="57"/>
+      <c r="BQ3" s="57"/>
+      <c r="BR3" s="57"/>
+      <c r="BS3" s="57"/>
+      <c r="BT3" s="57"/>
+      <c r="BU3" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="BV3" s="52"/>
-      <c r="BW3" s="52"/>
-      <c r="BX3" s="52"/>
-      <c r="BY3" s="52"/>
-      <c r="BZ3" s="52"/>
-      <c r="CA3" s="52"/>
-      <c r="CB3" s="52"/>
-      <c r="CC3" s="52"/>
-      <c r="CD3" s="52"/>
-      <c r="CE3" s="52"/>
-      <c r="CF3" s="51" t="s">
+      <c r="BV3" s="57"/>
+      <c r="BW3" s="57"/>
+      <c r="BX3" s="57"/>
+      <c r="BY3" s="57"/>
+      <c r="BZ3" s="57"/>
+      <c r="CA3" s="57"/>
+      <c r="CB3" s="57"/>
+      <c r="CC3" s="57"/>
+      <c r="CD3" s="57"/>
+      <c r="CE3" s="57"/>
+      <c r="CF3" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="CG3" s="52"/>
-      <c r="CH3" s="52"/>
-      <c r="CI3" s="52"/>
-      <c r="CJ3" s="52"/>
-      <c r="CK3" s="52"/>
-      <c r="CL3" s="52"/>
-      <c r="CM3" s="52"/>
-      <c r="CN3" s="52"/>
-      <c r="CO3" s="52"/>
-      <c r="CP3" s="52"/>
+      <c r="CG3" s="57"/>
+      <c r="CH3" s="57"/>
+      <c r="CI3" s="57"/>
+      <c r="CJ3" s="57"/>
+      <c r="CK3" s="57"/>
+      <c r="CL3" s="57"/>
+      <c r="CM3" s="57"/>
+      <c r="CN3" s="57"/>
+      <c r="CO3" s="57"/>
+      <c r="CP3" s="57"/>
     </row>
     <row r="4" spans="1:94" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
@@ -6406,35 +6450,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:S4"/>
+  <dimension ref="A2:Y4"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="19" width="12.453125" customWidth="1"/>
+    <col min="2" max="7" width="25.08984375" style="51" customWidth="1"/>
+    <col min="8" max="25" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="42">
         <v>46264</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>2</v>
-      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
       <c r="H2" s="29" t="s">
         <v>0</v>
       </c>
@@ -6450,149 +6483,204 @@
       <c r="L2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="30" t="s">
+      <c r="N2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="P2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="R2" s="30" t="s">
+      <c r="Q2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" s="29" t="s">
         <v>1</v>
       </c>
       <c r="S2" s="30" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="15" x14ac:dyDescent="0.3">
+      <c r="T2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="X2" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="I3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="J3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="K3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="L3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="M3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="N3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="O3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="P3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="Q3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="R3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="S3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="T3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="U3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="V3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="38" t="s">
+      <c r="W3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="38" t="s">
+      <c r="X3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="38" t="s">
+      <c r="Y3" s="38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="54">
         <v>0.343542430432489</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C4" s="54">
+        <v>0.33758422899148</v>
+      </c>
+      <c r="D4" s="54">
+        <v>0.339650831985919</v>
+      </c>
+      <c r="E4" s="54">
+        <v>0.33818616907233601</v>
+      </c>
+      <c r="F4" s="54">
         <v>0.33675168049224202</v>
       </c>
-      <c r="D4" s="41">
-        <f>IFERROR(C4-B4,"")</f>
-        <v>-6.7907499402469762E-3</v>
-      </c>
-      <c r="E4" s="40">
-        <v>8.7694971658933196E-2</v>
-      </c>
-      <c r="F4" s="40">
-        <v>8.8678012769633802E-2</v>
-      </c>
-      <c r="G4" s="41">
-        <f>IFERROR(F4-E4,"")</f>
-        <v>9.830411107006054E-4</v>
+      <c r="G4" s="55">
+        <f>F4-E4</f>
+        <v>-1.4344885800939844E-3</v>
       </c>
       <c r="H4" s="40">
-        <v>0.39116083386317801</v>
+        <v>0.343542430432489</v>
       </c>
       <c r="I4" s="40">
-        <v>0.38795664786575701</v>
+        <v>0.33675168049224202</v>
       </c>
       <c r="J4" s="41">
         <f>IFERROR(I4-H4,"")</f>
-        <v>-3.2041859974210052E-3</v>
+        <v>-6.7907499402469762E-3</v>
       </c>
       <c r="K4" s="40">
-        <v>0.17760176404540001</v>
+        <v>8.7694971658933196E-2</v>
       </c>
       <c r="L4" s="40">
-        <v>0.186613658872367</v>
+        <v>8.8678012769633802E-2</v>
       </c>
       <c r="M4" s="41">
         <f>IFERROR(L4-K4,"")</f>
-        <v>9.0118948269669874E-3</v>
+        <v>9.830411107006054E-4</v>
       </c>
       <c r="N4" s="40">
-        <v>0.166860567362455</v>
+        <v>0.39116083386317801</v>
       </c>
       <c r="O4" s="40">
-        <v>0.17595824933798801</v>
+        <v>0.38795664786575701</v>
       </c>
       <c r="P4" s="41">
         <f>IFERROR(O4-N4,"")</f>
-        <v>9.0976819755330118E-3</v>
+        <v>-3.2041859974210052E-3</v>
       </c>
       <c r="Q4" s="40">
-        <v>1.0741196682945301E-2</v>
+        <v>0.17760176404540001</v>
       </c>
       <c r="R4" s="40">
-        <v>1.0655409534379E-2</v>
+        <v>0.186613658872367</v>
       </c>
       <c r="S4" s="41">
         <f>IFERROR(R4-Q4,"")</f>
+        <v>9.0118948269669874E-3</v>
+      </c>
+      <c r="T4" s="40">
+        <v>0.166860567362455</v>
+      </c>
+      <c r="U4" s="40">
+        <v>0.17595824933798801</v>
+      </c>
+      <c r="V4" s="41">
+        <f>IFERROR(U4-T4,"")</f>
+        <v>9.0976819755330118E-3</v>
+      </c>
+      <c r="W4" s="40">
+        <v>1.0741196682945301E-2</v>
+      </c>
+      <c r="X4" s="40">
+        <v>1.0655409534379E-2</v>
+      </c>
+      <c r="Y4" s="41">
+        <f>IFERROR(X4-W4,"")</f>
         <v>-8.578714856630025E-5</v>
       </c>
     </row>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -964,9 +964,10 @@
     <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -1561,250 +1562,250 @@
         <v>35</v>
       </c>
       <c r="M5" s="44">
-        <v>-6.9563784143034102E-3</v>
+        <v>4.4283149939036703E-3</v>
       </c>
       <c r="N5" s="45">
-        <v>-1.09365555197141E-2</v>
+        <v>1.7915418964072299E-3</v>
       </c>
       <c r="O5" s="45">
-        <v>3.9801771054107501E-3</v>
+        <v>2.6367730974964101E-3</v>
       </c>
       <c r="P5" s="45">
-        <v>-3.9485891512089904E-3</v>
+        <v>-8.7061015109322609E-3</v>
       </c>
       <c r="Q5" s="45">
-        <v>1.0904967565512401E-2</v>
+        <v>4.27778651702862E-3</v>
       </c>
       <c r="R5" s="46">
-        <v>0.44246915055723202</v>
+        <v>0.44096630490028998</v>
       </c>
       <c r="S5" s="46">
-        <v>0.44096630490028998</v>
+        <v>0.44123961542051698</v>
       </c>
       <c r="T5" s="46">
-        <v>0.44123961542051698</v>
+        <v>0.44638556053538198</v>
       </c>
       <c r="U5" s="46">
-        <v>0.44638556053538198</v>
+        <v>0.43942918212107901</v>
       </c>
       <c r="V5" s="46">
+        <v>0.44305003971405899</v>
+      </c>
+      <c r="W5" s="46">
+        <v>0.43862172472015498</v>
+      </c>
+      <c r="X5" s="46">
+        <v>0.44305003971405899</v>
+      </c>
+      <c r="Y5" s="46">
+        <v>4.4283149939036703E-3</v>
+      </c>
+      <c r="Z5" s="46">
         <v>0.43942918212107901</v>
       </c>
-      <c r="W5" s="46">
-        <v>0.44638556053538198</v>
-      </c>
-      <c r="X5" s="46">
-        <v>0.43942918212107901</v>
-      </c>
-      <c r="Y5" s="46">
-        <v>-6.9563784143034102E-3</v>
-      </c>
-      <c r="Z5" s="46">
-        <v>0.44538104788167499</v>
-      </c>
       <c r="AA5" s="46">
-        <v>0.43942918212107901</v>
+        <v>0.44305003971405899</v>
       </c>
       <c r="AB5" s="46">
-        <v>-5.9518657605958101E-3</v>
+        <v>3.6208575929799801E-3</v>
       </c>
       <c r="AC5" s="46">
-        <v>0.354596791060384</v>
+        <v>0.35339492331150801</v>
       </c>
       <c r="AD5" s="46">
-        <v>0.35339492331150801</v>
+        <v>0.35595382557018002</v>
       </c>
       <c r="AE5" s="46">
-        <v>0.35595382557018002</v>
+        <v>0.363517180401841</v>
       </c>
       <c r="AF5" s="46">
-        <v>0.363517180401841</v>
+        <v>0.35258062488212699</v>
       </c>
       <c r="AG5" s="46">
+        <v>0.35561556791103999</v>
+      </c>
+      <c r="AH5" s="46">
+        <v>0.35382402601463298</v>
+      </c>
+      <c r="AI5" s="46">
+        <v>0.35561556791103999</v>
+      </c>
+      <c r="AJ5" s="46">
+        <v>1.7915418964072299E-3</v>
+      </c>
+      <c r="AK5" s="46">
         <v>0.35258062488212699</v>
       </c>
-      <c r="AH5" s="46">
-        <v>0.363517180401841</v>
-      </c>
-      <c r="AI5" s="46">
-        <v>0.35258062488212699</v>
-      </c>
-      <c r="AJ5" s="46">
-        <v>-1.09365555197141E-2</v>
-      </c>
-      <c r="AK5" s="46">
-        <v>0.359864627726247</v>
-      </c>
       <c r="AL5" s="46">
-        <v>0.35258062488212699</v>
+        <v>0.35561556791103999</v>
       </c>
       <c r="AM5" s="46">
-        <v>-7.2840028441197901E-3</v>
+        <v>3.0349430289131102E-3</v>
       </c>
       <c r="AN5" s="46">
-        <v>8.7872359496847796E-2</v>
+        <v>8.7571381588782193E-2</v>
       </c>
       <c r="AO5" s="46">
-        <v>8.7571381588782193E-2</v>
+        <v>8.5285789850337607E-2</v>
       </c>
       <c r="AP5" s="46">
-        <v>8.5285789850337607E-2</v>
+        <v>8.2868380133540698E-2</v>
       </c>
       <c r="AQ5" s="46">
-        <v>8.2868380133540698E-2</v>
+        <v>8.6848557238951393E-2</v>
       </c>
       <c r="AR5" s="46">
+        <v>8.7434471803018304E-2</v>
+      </c>
+      <c r="AS5" s="46">
+        <v>8.4797698705521896E-2</v>
+      </c>
+      <c r="AT5" s="46">
+        <v>8.7434471803018304E-2</v>
+      </c>
+      <c r="AU5" s="46">
+        <v>2.6367730974964101E-3</v>
+      </c>
+      <c r="AV5" s="46">
         <v>8.6848557238951393E-2</v>
       </c>
-      <c r="AS5" s="46">
-        <v>8.2868380133540698E-2</v>
-      </c>
-      <c r="AT5" s="46">
-        <v>8.6848557238951393E-2</v>
-      </c>
-      <c r="AU5" s="46">
-        <v>3.9801771054107501E-3</v>
-      </c>
-      <c r="AV5" s="46">
-        <v>8.5516420155427403E-2</v>
-      </c>
       <c r="AW5" s="46">
-        <v>8.6848557238951393E-2</v>
+        <v>8.7434471803018304E-2</v>
       </c>
       <c r="AX5" s="46">
-        <v>1.33213708352398E-3</v>
+        <v>5.8591456406685604E-4</v>
       </c>
       <c r="AY5" s="46">
-        <v>0.42035913830708999</v>
+        <v>0.42727299907316102</v>
       </c>
       <c r="AZ5" s="46">
-        <v>0.42727299907316102</v>
+        <v>0.42524658514577302</v>
       </c>
       <c r="BA5" s="46">
-        <v>0.42524658514577302</v>
+        <v>0.426781304308058</v>
       </c>
       <c r="BB5" s="46">
-        <v>0.426781304308058</v>
+        <v>0.422832715156849</v>
       </c>
       <c r="BC5" s="46">
+        <v>0.41925337569499599</v>
+      </c>
+      <c r="BD5" s="46">
+        <v>0.42795947720592797</v>
+      </c>
+      <c r="BE5" s="46">
+        <v>0.41925337569499599</v>
+      </c>
+      <c r="BF5" s="47">
+        <v>-8.7061015109322609E-3</v>
+      </c>
+      <c r="BG5" s="46">
         <v>0.422832715156849</v>
       </c>
-      <c r="BD5" s="46">
-        <v>0.426781304308058</v>
-      </c>
-      <c r="BE5" s="46">
-        <v>0.422832715156849</v>
-      </c>
-      <c r="BF5" s="47">
-        <v>-3.9485891512089904E-3</v>
-      </c>
-      <c r="BG5" s="46">
-        <v>0.41861995487590897</v>
-      </c>
       <c r="BH5" s="46">
-        <v>0.422832715156849</v>
+        <v>0.41925337569499599</v>
       </c>
       <c r="BI5" s="47">
-        <v>4.2127602809404197E-3</v>
+        <v>-3.5793394618531299E-3</v>
       </c>
       <c r="BJ5" s="46">
-        <v>0.137171711135678</v>
+        <v>0.131760696026549</v>
       </c>
       <c r="BK5" s="46">
-        <v>0.131760696026549</v>
+        <v>0.13351379943371</v>
       </c>
       <c r="BL5" s="46">
-        <v>0.13351379943371</v>
+        <v>0.12683313515656</v>
       </c>
       <c r="BM5" s="46">
-        <v>0.12683313515656</v>
+        <v>0.13773810272207199</v>
       </c>
       <c r="BN5" s="46">
+        <v>0.137696584590945</v>
+      </c>
+      <c r="BO5" s="46">
+        <v>0.13341879807391699</v>
+      </c>
+      <c r="BP5" s="46">
+        <v>0.137696584590945</v>
+      </c>
+      <c r="BQ5" s="46">
+        <v>4.27778651702862E-3</v>
+      </c>
+      <c r="BR5" s="46">
         <v>0.13773810272207199</v>
       </c>
-      <c r="BO5" s="46">
-        <v>0.12683313515656</v>
-      </c>
-      <c r="BP5" s="46">
-        <v>0.13773810272207199</v>
-      </c>
-      <c r="BQ5" s="46">
-        <v>1.0904967565512401E-2</v>
-      </c>
-      <c r="BR5" s="46">
-        <v>0.13599899724241701</v>
-      </c>
       <c r="BS5" s="46">
-        <v>0.13773810272207199</v>
+        <v>0.137696584590945</v>
       </c>
       <c r="BT5" s="46">
-        <v>1.73910547965539E-3</v>
+        <v>-4.15181311268498E-5</v>
       </c>
       <c r="BU5" s="46">
-        <v>0.13182347844273801</v>
+        <v>0.12877089126080099</v>
       </c>
       <c r="BV5" s="46">
-        <v>0.12877089126080099</v>
+        <v>0.12850430940601801</v>
       </c>
       <c r="BW5" s="46">
-        <v>0.12850430940601801</v>
+        <v>0.123784261715296</v>
       </c>
       <c r="BX5" s="46">
-        <v>0.123784261715296</v>
+        <v>0.133620418683598</v>
       </c>
       <c r="BY5" s="46">
+        <v>0.13261318506751399</v>
+      </c>
+      <c r="BZ5" s="46">
+        <v>0.12907260333937801</v>
+      </c>
+      <c r="CA5" s="46">
+        <v>0.13261318506751399</v>
+      </c>
+      <c r="CB5" s="46">
+        <v>-1.00723361608451E-3</v>
+      </c>
+      <c r="CC5" s="46">
         <v>0.133620418683598</v>
       </c>
-      <c r="BZ5" s="46">
-        <v>0.123784261715296</v>
-      </c>
-      <c r="CA5" s="46">
-        <v>0.133620418683598</v>
-      </c>
-      <c r="CB5" s="46">
-        <v>9.8361569683022097E-3</v>
-      </c>
-      <c r="CC5" s="46">
-        <v>0.12976309852093301</v>
-      </c>
       <c r="CD5" s="46">
-        <v>0.133620418683598</v>
+        <v>0.13261318506751399</v>
       </c>
       <c r="CE5" s="46">
-        <v>3.85732016266585E-3</v>
+        <v>-1.00723361608451E-3</v>
       </c>
       <c r="CF5" s="46">
-        <v>5.3482326929397399E-3</v>
+        <v>2.9898047657487999E-3</v>
       </c>
       <c r="CG5" s="46">
-        <v>2.9898047657487999E-3</v>
+        <v>5.0094900276922098E-3</v>
       </c>
       <c r="CH5" s="46">
-        <v>5.0094900276922098E-3</v>
+        <v>3.0488734412634499E-3</v>
       </c>
       <c r="CI5" s="46">
-        <v>3.0488734412634499E-3</v>
+        <v>4.1176840384736296E-3</v>
       </c>
       <c r="CJ5" s="46">
+        <v>5.0833995234312902E-3</v>
+      </c>
+      <c r="CK5" s="46">
+        <v>4.3461947345381797E-3</v>
+      </c>
+      <c r="CL5" s="46">
+        <v>5.0833995234312902E-3</v>
+      </c>
+      <c r="CM5" s="46">
+        <v>9.6571548495766703E-4</v>
+      </c>
+      <c r="CN5" s="46">
         <v>4.1176840384736296E-3</v>
       </c>
-      <c r="CK5" s="46">
-        <v>3.0488734412634499E-3</v>
-      </c>
-      <c r="CL5" s="46">
-        <v>4.1176840384736296E-3</v>
-      </c>
-      <c r="CM5" s="46">
-        <v>1.0688105972101701E-3</v>
-      </c>
-      <c r="CN5" s="46">
-        <v>6.2358987214840801E-3</v>
-      </c>
       <c r="CO5" s="46">
-        <v>4.1176840384736296E-3</v>
+        <v>5.0833995234312902E-3</v>
       </c>
       <c r="CP5" s="46">
-        <v>-2.1182146830104501E-3</v>
+        <v>9.6571548495766703E-4</v>
       </c>
     </row>
     <row r="6" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1845,85 +1846,85 @@
         <v>35</v>
       </c>
       <c r="M6" s="44">
-        <v>1.4956422478599501E-2</v>
+        <v>3.8331045462847201E-3</v>
       </c>
       <c r="N6" s="45">
-        <v>3.3758991046516001E-2</v>
+        <v>1.4858542945774199E-2</v>
       </c>
       <c r="O6" s="45">
-        <v>-1.8802568567916501E-2</v>
+        <v>-1.1025438399489501E-2</v>
       </c>
       <c r="P6" s="45">
-        <v>-1.6446821104770599E-2</v>
+        <v>-8.7330513547234602E-4</v>
       </c>
       <c r="Q6" s="45">
-        <v>1.4903986261711199E-3</v>
+        <v>-2.9597994108123099E-3</v>
       </c>
       <c r="R6" s="46">
-        <v>0.28758465011286699</v>
+        <v>0.29486277269528499</v>
       </c>
       <c r="S6" s="46">
+        <v>0.30758226037196001</v>
+      </c>
+      <c r="T6" s="46">
+        <v>0.330335057342028</v>
+      </c>
+      <c r="U6" s="46">
+        <v>0.34529147982062802</v>
+      </c>
+      <c r="V6" s="46">
+        <v>0.33415508740475097</v>
+      </c>
+      <c r="W6" s="46">
+        <v>0.33032198285846698</v>
+      </c>
+      <c r="X6" s="46">
+        <v>0.33415508740475097</v>
+      </c>
+      <c r="Y6" s="46">
+        <v>3.8331045462847201E-3</v>
+      </c>
+      <c r="Z6" s="46">
+        <v>0.34529147982062802</v>
+      </c>
+      <c r="AA6" s="46">
+        <v>0.33415508740475097</v>
+      </c>
+      <c r="AB6" s="46">
+        <v>-1.1136392415876601E-2</v>
+      </c>
+      <c r="AC6" s="46">
         <v>0.29486277269528499</v>
       </c>
-      <c r="T6" s="46">
+      <c r="AD6" s="46">
         <v>0.30758226037196001</v>
       </c>
-      <c r="U6" s="46">
-        <v>0.330335057342028</v>
-      </c>
-      <c r="V6" s="46">
-        <v>0.34529147982062802</v>
-      </c>
-      <c r="W6" s="46">
-        <v>0.330335057342028</v>
-      </c>
-      <c r="X6" s="46">
-        <v>0.34529147982062802</v>
-      </c>
-      <c r="Y6" s="46">
-        <v>1.4956422478599501E-2</v>
-      </c>
-      <c r="Z6" s="46">
-        <v>0.34171086004150297</v>
-      </c>
-      <c r="AA6" s="46">
-        <v>0.34529147982062802</v>
-      </c>
-      <c r="AB6" s="46">
-        <v>3.58061977912444E-3</v>
-      </c>
-      <c r="AC6" s="46">
-        <v>0.28758465011286699</v>
-      </c>
-      <c r="AD6" s="46">
-        <v>0.29486277269528499</v>
-      </c>
       <c r="AE6" s="46">
-        <v>0.30758226037196001</v>
+        <v>0.26422307173375298</v>
       </c>
       <c r="AF6" s="46">
-        <v>0.26422307173375298</v>
+        <v>0.29798206278026901</v>
       </c>
       <c r="AG6" s="46">
+        <v>0.28865979381443302</v>
+      </c>
+      <c r="AH6" s="46">
+        <v>0.27380125086865897</v>
+      </c>
+      <c r="AI6" s="46">
+        <v>0.28865979381443302</v>
+      </c>
+      <c r="AJ6" s="46">
+        <v>1.4858542945774199E-2</v>
+      </c>
+      <c r="AK6" s="46">
         <v>0.29798206278026901</v>
       </c>
-      <c r="AH6" s="46">
-        <v>0.26422307173375298</v>
-      </c>
-      <c r="AI6" s="46">
-        <v>0.29798206278026901</v>
-      </c>
-      <c r="AJ6" s="46">
-        <v>3.3758991046516001E-2</v>
-      </c>
-      <c r="AK6" s="46">
-        <v>0.29167627392206602</v>
-      </c>
       <c r="AL6" s="46">
-        <v>0.29798206278026901</v>
+        <v>0.28865979381443302</v>
       </c>
       <c r="AM6" s="46">
-        <v>6.3057888582031003E-3</v>
+        <v>-9.3222689658361002E-3</v>
       </c>
       <c r="AN6" s="46">
         <v>0</v>
@@ -1932,133 +1933,133 @@
         <v>0</v>
       </c>
       <c r="AP6" s="46">
-        <v>0</v>
+        <v>6.6111985608275206E-2</v>
       </c>
       <c r="AQ6" s="46">
-        <v>6.6111985608275206E-2</v>
+        <v>4.7309417040358702E-2</v>
       </c>
       <c r="AR6" s="46">
+        <v>4.5495293590318203E-2</v>
+      </c>
+      <c r="AS6" s="46">
+        <v>5.6520731989807699E-2</v>
+      </c>
+      <c r="AT6" s="46">
+        <v>4.5495293590318203E-2</v>
+      </c>
+      <c r="AU6" s="46">
+        <v>-1.1025438399489501E-2</v>
+      </c>
+      <c r="AV6" s="46">
         <v>4.7309417040358702E-2</v>
       </c>
-      <c r="AS6" s="46">
-        <v>6.6111985608275206E-2</v>
-      </c>
-      <c r="AT6" s="46">
-        <v>4.7309417040358702E-2</v>
-      </c>
-      <c r="AU6" s="46">
-        <v>-1.8802568567916501E-2</v>
-      </c>
-      <c r="AV6" s="46">
-        <v>5.0034586119437403E-2</v>
-      </c>
       <c r="AW6" s="46">
-        <v>4.7309417040358702E-2</v>
+        <v>4.5495293590318203E-2</v>
       </c>
       <c r="AX6" s="46">
-        <v>-2.7251690790786498E-3</v>
+        <v>-1.8141234500405E-3</v>
       </c>
       <c r="AY6" s="46">
-        <v>0.36726862302483099</v>
+        <v>0.32488857612010302</v>
       </c>
       <c r="AZ6" s="46">
-        <v>0.32488857612010302</v>
+        <v>0.33094897472579898</v>
       </c>
       <c r="BA6" s="46">
-        <v>0.33094897472579898</v>
+        <v>0.33483247132898603</v>
       </c>
       <c r="BB6" s="46">
+        <v>0.318385650224215</v>
+      </c>
+      <c r="BC6" s="46">
+        <v>0.32944867772299402</v>
+      </c>
+      <c r="BD6" s="46">
+        <v>0.33032198285846698</v>
+      </c>
+      <c r="BE6" s="46">
+        <v>0.32944867772299402</v>
+      </c>
+      <c r="BF6" s="47">
+        <v>-8.7330513547234602E-4</v>
+      </c>
+      <c r="BG6" s="46">
+        <v>0.318385650224215</v>
+      </c>
+      <c r="BH6" s="46">
+        <v>0.32944867772299402</v>
+      </c>
+      <c r="BI6" s="47">
+        <v>1.1063027498779E-2</v>
+      </c>
+      <c r="BJ6" s="46">
+        <v>0.38024865118461199</v>
+      </c>
+      <c r="BK6" s="46">
+        <v>0.361468764902241</v>
+      </c>
+      <c r="BL6" s="46">
         <v>0.33483247132898603</v>
       </c>
-      <c r="BC6" s="46">
-        <v>0.318385650224215</v>
-      </c>
-      <c r="BD6" s="46">
+      <c r="BM6" s="46">
+        <v>0.33632286995515698</v>
+      </c>
+      <c r="BN6" s="46">
+        <v>0.33639623487225501</v>
+      </c>
+      <c r="BO6" s="46">
+        <v>0.33935603428306699</v>
+      </c>
+      <c r="BP6" s="46">
+        <v>0.33639623487225501</v>
+      </c>
+      <c r="BQ6" s="46">
+        <v>-2.9597994108123099E-3</v>
+      </c>
+      <c r="BR6" s="46">
+        <v>0.33632286995515698</v>
+      </c>
+      <c r="BS6" s="46">
+        <v>0.33639623487225501</v>
+      </c>
+      <c r="BT6" s="46">
+        <v>7.3364917097640299E-5</v>
+      </c>
+      <c r="BU6" s="46">
+        <v>0.38024865118461199</v>
+      </c>
+      <c r="BV6" s="46">
+        <v>0.361468764902241</v>
+      </c>
+      <c r="BW6" s="46">
         <v>0.33483247132898603</v>
       </c>
-      <c r="BE6" s="46">
-        <v>0.318385650224215</v>
-      </c>
-      <c r="BF6" s="47">
-        <v>-1.6446821104770599E-2</v>
-      </c>
-      <c r="BG6" s="46">
-        <v>0.31888402121282</v>
-      </c>
-      <c r="BH6" s="46">
-        <v>0.318385650224215</v>
-      </c>
-      <c r="BI6" s="47">
-        <v>-4.9837098860472395E-4</v>
-      </c>
-      <c r="BJ6" s="46">
-        <v>0.34514672686230202</v>
-      </c>
-      <c r="BK6" s="46">
-        <v>0.38024865118461199</v>
-      </c>
-      <c r="BL6" s="46">
-        <v>0.361468764902241</v>
-      </c>
-      <c r="BM6" s="46">
-        <v>0.33483247132898603</v>
-      </c>
-      <c r="BN6" s="46">
+      <c r="BX6" s="46">
         <v>0.33632286995515698</v>
       </c>
-      <c r="BO6" s="46">
-        <v>0.33483247132898603</v>
-      </c>
-      <c r="BP6" s="46">
+      <c r="BY6" s="46">
+        <v>0.33639623487225501</v>
+      </c>
+      <c r="BZ6" s="46">
+        <v>0.33935603428306699</v>
+      </c>
+      <c r="CA6" s="46">
+        <v>0.33639623487225501</v>
+      </c>
+      <c r="CB6" s="46">
+        <v>7.3364917097640299E-5</v>
+      </c>
+      <c r="CC6" s="46">
         <v>0.33632286995515698</v>
       </c>
-      <c r="BQ6" s="46">
-        <v>1.4903986261711199E-3</v>
-      </c>
-      <c r="BR6" s="46">
-        <v>0.33940511874567703</v>
-      </c>
-      <c r="BS6" s="46">
-        <v>0.33632286995515698</v>
-      </c>
-      <c r="BT6" s="46">
-        <v>-3.08224879051977E-3</v>
-      </c>
-      <c r="BU6" s="46">
-        <v>0.323024830699774</v>
-      </c>
-      <c r="BV6" s="46">
-        <v>0.38024865118461199</v>
-      </c>
-      <c r="BW6" s="46">
-        <v>0.361468764902241</v>
-      </c>
-      <c r="BX6" s="46">
-        <v>0.33483247132898603</v>
-      </c>
-      <c r="BY6" s="46">
-        <v>0.33632286995515698</v>
-      </c>
-      <c r="BZ6" s="46">
-        <v>0.33483247132898603</v>
-      </c>
-      <c r="CA6" s="46">
-        <v>0.33632286995515698</v>
-      </c>
-      <c r="CB6" s="46">
-        <v>1.4903986261711199E-3</v>
-      </c>
-      <c r="CC6" s="46">
-        <v>0.33940511874567703</v>
-      </c>
       <c r="CD6" s="46">
-        <v>0.33632286995515698</v>
+        <v>0.33639623487225501</v>
       </c>
       <c r="CE6" s="46">
-        <v>-3.08224879051977E-3</v>
+        <v>7.3364917097640299E-5</v>
       </c>
       <c r="CF6" s="46">
-        <v>2.2121896162528201E-2</v>
+        <v>0</v>
       </c>
       <c r="CG6" s="46">
         <v>0</v>
@@ -2129,85 +2130,85 @@
         <v>91</v>
       </c>
       <c r="M7" s="44">
-        <v>-2.18303969287722E-2</v>
+        <v>3.9240893499163099E-2</v>
       </c>
       <c r="N7" s="45">
-        <v>-2.18303969287722E-2</v>
+        <v>-5.4445728782772703E-3</v>
       </c>
       <c r="O7" s="45">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="P7" s="45">
-        <v>1.3573730033591601E-2</v>
+        <v>-7.0275990962928497E-2</v>
       </c>
       <c r="Q7" s="45">
-        <v>8.2566668951806303E-3</v>
+        <v>3.1035097463765399E-2</v>
       </c>
       <c r="R7" s="46">
-        <v>0.19818181818181799</v>
+        <v>0.20422535211267601</v>
       </c>
       <c r="S7" s="46">
+        <v>0.21222130470685399</v>
+      </c>
+      <c r="T7" s="46">
+        <v>0.239761431411531</v>
+      </c>
+      <c r="U7" s="46">
+        <v>0.217931034482759</v>
+      </c>
+      <c r="V7" s="46">
+        <v>0.246420824295011</v>
+      </c>
+      <c r="W7" s="46">
+        <v>0.20717993079584801</v>
+      </c>
+      <c r="X7" s="46">
+        <v>0.246420824295011</v>
+      </c>
+      <c r="Y7" s="46">
+        <v>3.9240893499163099E-2</v>
+      </c>
+      <c r="Z7" s="46">
+        <v>0.217931034482759</v>
+      </c>
+      <c r="AA7" s="46">
+        <v>0.246420824295011</v>
+      </c>
+      <c r="AB7" s="46">
+        <v>2.8489789812252201E-2</v>
+      </c>
+      <c r="AC7" s="46">
         <v>0.20422535211267601</v>
       </c>
-      <c r="T7" s="46">
+      <c r="AD7" s="46">
         <v>0.21222130470685399</v>
       </c>
-      <c r="U7" s="46">
+      <c r="AE7" s="46">
         <v>0.239761431411531</v>
       </c>
-      <c r="V7" s="46">
+      <c r="AF7" s="46">
         <v>0.217931034482759</v>
       </c>
-      <c r="W7" s="46">
-        <v>0.239761431411531</v>
-      </c>
-      <c r="X7" s="46">
+      <c r="AG7" s="46">
+        <v>0.20173535791757</v>
+      </c>
+      <c r="AH7" s="46">
+        <v>0.20717993079584801</v>
+      </c>
+      <c r="AI7" s="46">
+        <v>0.20173535791757</v>
+      </c>
+      <c r="AJ7" s="46">
+        <v>-5.4445728782772703E-3</v>
+      </c>
+      <c r="AK7" s="46">
         <v>0.217931034482759</v>
       </c>
-      <c r="Y7" s="46">
-        <v>-2.18303969287722E-2</v>
-      </c>
-      <c r="Z7" s="46">
-        <v>0.20621856424325599</v>
-      </c>
-      <c r="AA7" s="46">
-        <v>0.217931034482759</v>
-      </c>
-      <c r="AB7" s="46">
-        <v>1.1712470239503E-2</v>
-      </c>
-      <c r="AC7" s="46">
-        <v>0.19818181818181799</v>
-      </c>
-      <c r="AD7" s="46">
-        <v>0.20422535211267601</v>
-      </c>
-      <c r="AE7" s="46">
-        <v>0.21222130470685399</v>
-      </c>
-      <c r="AF7" s="46">
-        <v>0.239761431411531</v>
-      </c>
-      <c r="AG7" s="46">
-        <v>0.217931034482759</v>
-      </c>
-      <c r="AH7" s="46">
-        <v>0.239761431411531</v>
-      </c>
-      <c r="AI7" s="46">
-        <v>0.217931034482759</v>
-      </c>
-      <c r="AJ7" s="46">
-        <v>-2.18303969287722E-2</v>
-      </c>
-      <c r="AK7" s="46">
-        <v>0.20621856424325599</v>
-      </c>
       <c r="AL7" s="46">
-        <v>0.217931034482759</v>
+        <v>0.20173535791757</v>
       </c>
       <c r="AM7" s="46">
-        <v>1.1712470239503E-2</v>
+        <v>-1.61956765651881E-2</v>
       </c>
       <c r="AN7" s="46">
         <v>0</v>
@@ -2222,124 +2223,124 @@
         <v>0</v>
       </c>
       <c r="AR7" s="46">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="AS7" s="46">
         <v>0</v>
       </c>
       <c r="AT7" s="46">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="AU7" s="46">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="AV7" s="46">
         <v>0</v>
       </c>
       <c r="AW7" s="46">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="AX7" s="46">
-        <v>0</v>
+        <v>4.4685466377440301E-2</v>
       </c>
       <c r="AY7" s="46">
-        <v>0.70499999999999996</v>
+        <v>0.65977112676056304</v>
       </c>
       <c r="AZ7" s="46">
-        <v>0.65977112676056304</v>
+        <v>0.68166804293971905</v>
       </c>
       <c r="BA7" s="46">
-        <v>0.68166804293971905</v>
+        <v>0.66918489065606401</v>
       </c>
       <c r="BB7" s="46">
-        <v>0.66918489065606401</v>
+        <v>0.68275862068965498</v>
       </c>
       <c r="BC7" s="46">
+        <v>0.645986984815618</v>
+      </c>
+      <c r="BD7" s="46">
+        <v>0.71626297577854703</v>
+      </c>
+      <c r="BE7" s="46">
+        <v>0.645986984815618</v>
+      </c>
+      <c r="BF7" s="46">
+        <v>-7.0275990962928497E-2</v>
+      </c>
+      <c r="BG7" s="46">
         <v>0.68275862068965498</v>
       </c>
-      <c r="BD7" s="46">
-        <v>0.66918489065606401</v>
-      </c>
-      <c r="BE7" s="46">
-        <v>0.68275862068965498</v>
-      </c>
-      <c r="BF7" s="46">
-        <v>1.3573730033591601E-2</v>
-      </c>
-      <c r="BG7" s="46">
-        <v>0.65935070873342505</v>
-      </c>
       <c r="BH7" s="46">
-        <v>0.68275862068965498</v>
+        <v>0.645986984815618</v>
       </c>
       <c r="BI7" s="47">
-        <v>2.34079119562304E-2</v>
+        <v>-3.6771635874036999E-2</v>
       </c>
       <c r="BJ7" s="46">
-        <v>9.6818181818181803E-2</v>
+        <v>0.13600352112676101</v>
       </c>
       <c r="BK7" s="46">
+        <v>0.106110652353427</v>
+      </c>
+      <c r="BL7" s="46">
+        <v>9.1053677932405597E-2</v>
+      </c>
+      <c r="BM7" s="46">
+        <v>9.9310344827586203E-2</v>
+      </c>
+      <c r="BN7" s="46">
+        <v>0.107592190889371</v>
+      </c>
+      <c r="BO7" s="46">
+        <v>7.6557093425605502E-2</v>
+      </c>
+      <c r="BP7" s="46">
+        <v>0.107592190889371</v>
+      </c>
+      <c r="BQ7" s="47">
+        <v>3.1035097463765399E-2</v>
+      </c>
+      <c r="BR7" s="46">
+        <v>9.9310344827586203E-2</v>
+      </c>
+      <c r="BS7" s="46">
+        <v>0.107592190889371</v>
+      </c>
+      <c r="BT7" s="46">
+        <v>8.2818460617847308E-3</v>
+      </c>
+      <c r="BU7" s="46">
         <v>0.13600352112676101</v>
       </c>
-      <c r="BL7" s="46">
+      <c r="BV7" s="46">
         <v>0.106110652353427</v>
       </c>
-      <c r="BM7" s="46">
+      <c r="BW7" s="46">
         <v>9.1053677932405597E-2</v>
       </c>
-      <c r="BN7" s="46">
+      <c r="BX7" s="46">
         <v>9.9310344827586203E-2</v>
       </c>
-      <c r="BO7" s="46">
-        <v>9.1053677932405597E-2</v>
-      </c>
-      <c r="BP7" s="46">
+      <c r="BY7" s="46">
+        <v>0.107592190889371</v>
+      </c>
+      <c r="BZ7" s="46">
+        <v>7.6557093425605502E-2</v>
+      </c>
+      <c r="CA7" s="46">
+        <v>0.107592190889371</v>
+      </c>
+      <c r="CB7" s="46">
+        <v>8.2818460617847308E-3</v>
+      </c>
+      <c r="CC7" s="46">
         <v>9.9310344827586203E-2</v>
       </c>
-      <c r="BQ7" s="47">
-        <v>8.2566668951806303E-3</v>
-      </c>
-      <c r="BR7" s="46">
-        <v>0.13443072702332001</v>
-      </c>
-      <c r="BS7" s="46">
-        <v>9.9310344827586203E-2</v>
-      </c>
-      <c r="BT7" s="46">
-        <v>-3.51203821957334E-2</v>
-      </c>
-      <c r="BU7" s="46">
-        <v>9.6818181818181803E-2</v>
-      </c>
-      <c r="BV7" s="46">
-        <v>0.13600352112676101</v>
-      </c>
-      <c r="BW7" s="46">
-        <v>0.106110652353427</v>
-      </c>
-      <c r="BX7" s="46">
-        <v>9.1053677932405597E-2</v>
-      </c>
-      <c r="BY7" s="46">
-        <v>9.9310344827586203E-2</v>
-      </c>
-      <c r="BZ7" s="46">
-        <v>9.1053677932405597E-2</v>
-      </c>
-      <c r="CA7" s="46">
-        <v>9.9310344827586203E-2</v>
-      </c>
-      <c r="CB7" s="46">
-        <v>8.2566668951806303E-3</v>
-      </c>
-      <c r="CC7" s="46">
-        <v>0.13443072702332001</v>
-      </c>
       <c r="CD7" s="46">
-        <v>9.9310344827586203E-2</v>
+        <v>0.107592190889371</v>
       </c>
       <c r="CE7" s="46">
-        <v>-3.51203821957334E-2</v>
+        <v>8.2818460617847308E-3</v>
       </c>
       <c r="CF7" s="46">
         <v>0</v>
@@ -2413,223 +2414,223 @@
         <v>35</v>
       </c>
       <c r="M8" s="44">
-        <v>-1.59724595273714E-3</v>
+        <v>7.9639151348487296E-3</v>
       </c>
       <c r="N8" s="45">
-        <v>-1.4495739445358501E-2</v>
+        <v>3.1074940826037998E-3</v>
       </c>
       <c r="O8" s="45">
-        <v>1.2898493492621401E-2</v>
+        <v>4.8564210522448296E-3</v>
       </c>
       <c r="P8" s="45">
-        <v>3.31805402485874E-3</v>
+        <v>-6.9539164115550202E-3</v>
       </c>
       <c r="Q8" s="45">
-        <v>-1.7208080721216499E-3</v>
+        <v>-1.00999872329365E-3</v>
       </c>
       <c r="R8" s="46">
-        <v>0.60287667040701798</v>
+        <v>0.55001639881928499</v>
       </c>
       <c r="S8" s="46">
-        <v>0.55001639881928499</v>
+        <v>0.617042775345234</v>
       </c>
       <c r="T8" s="46">
-        <v>0.617042775345234</v>
+        <v>0.58561066126855599</v>
       </c>
       <c r="U8" s="46">
-        <v>0.58561066126855599</v>
+        <v>0.58401341531581896</v>
       </c>
       <c r="V8" s="46">
+        <v>0.57984144960362405</v>
+      </c>
+      <c r="W8" s="46">
+        <v>0.57187753446877498</v>
+      </c>
+      <c r="X8" s="46">
+        <v>0.57984144960362405</v>
+      </c>
+      <c r="Y8" s="46">
+        <v>7.9639151348487296E-3</v>
+      </c>
+      <c r="Z8" s="46">
         <v>0.58401341531581896</v>
       </c>
-      <c r="W8" s="46">
-        <v>0.58561066126855599</v>
-      </c>
-      <c r="X8" s="46">
-        <v>0.58401341531581896</v>
-      </c>
-      <c r="Y8" s="46">
-        <v>-1.59724595273714E-3</v>
-      </c>
-      <c r="Z8" s="46">
-        <v>0.57064064488756905</v>
-      </c>
       <c r="AA8" s="46">
-        <v>0.58401341531581896</v>
+        <v>0.57984144960362405</v>
       </c>
       <c r="AB8" s="46">
-        <v>1.33727704282499E-2</v>
+        <v>-4.1719657121948002E-3</v>
       </c>
       <c r="AC8" s="46">
-        <v>0.503111292461491</v>
+        <v>0.43456871105280398</v>
       </c>
       <c r="AD8" s="46">
-        <v>0.43456871105280398</v>
+        <v>0.51650387335803305</v>
       </c>
       <c r="AE8" s="46">
-        <v>0.51650387335803305</v>
+        <v>0.48895074224021601</v>
       </c>
       <c r="AF8" s="46">
-        <v>0.48895074224021601</v>
+        <v>0.47445500279485697</v>
       </c>
       <c r="AG8" s="46">
+        <v>0.47451868629671601</v>
+      </c>
+      <c r="AH8" s="46">
+        <v>0.47141119221411198</v>
+      </c>
+      <c r="AI8" s="46">
+        <v>0.47451868629671601</v>
+      </c>
+      <c r="AJ8" s="46">
+        <v>3.1074940826037998E-3</v>
+      </c>
+      <c r="AK8" s="46">
         <v>0.47445500279485697</v>
       </c>
-      <c r="AH8" s="46">
-        <v>0.48895074224021601</v>
-      </c>
-      <c r="AI8" s="46">
-        <v>0.47445500279485697</v>
-      </c>
-      <c r="AJ8" s="46">
-        <v>-1.4495739445358501E-2</v>
-      </c>
-      <c r="AK8" s="46">
-        <v>0.46117946542214699</v>
-      </c>
       <c r="AL8" s="46">
-        <v>0.47445500279485697</v>
+        <v>0.47451868629671601</v>
       </c>
       <c r="AM8" s="46">
-        <v>1.32755373727107E-2</v>
+        <v>6.3683501858258204E-5</v>
       </c>
       <c r="AN8" s="46">
-        <v>9.9765377945526895E-2</v>
+        <v>0.115447687766481</v>
       </c>
       <c r="AO8" s="46">
-        <v>0.115447687766481</v>
+        <v>0.100538901987201</v>
       </c>
       <c r="AP8" s="46">
-        <v>0.100538901987201</v>
+        <v>9.6659919028340105E-2</v>
       </c>
       <c r="AQ8" s="46">
-        <v>9.6659919028340105E-2</v>
+        <v>0.109558412520961</v>
       </c>
       <c r="AR8" s="46">
+        <v>0.105322763306908</v>
+      </c>
+      <c r="AS8" s="46">
+        <v>0.100466342254663</v>
+      </c>
+      <c r="AT8" s="46">
+        <v>0.105322763306908</v>
+      </c>
+      <c r="AU8" s="46">
+        <v>4.8564210522448296E-3</v>
+      </c>
+      <c r="AV8" s="46">
         <v>0.109558412520961</v>
       </c>
-      <c r="AS8" s="46">
-        <v>9.6659919028340105E-2</v>
-      </c>
-      <c r="AT8" s="46">
-        <v>0.109558412520961</v>
-      </c>
-      <c r="AU8" s="46">
-        <v>1.2898493492621401E-2</v>
-      </c>
-      <c r="AV8" s="46">
-        <v>0.109461179465422</v>
-      </c>
       <c r="AW8" s="46">
-        <v>0.109558412520961</v>
+        <v>0.105322763306908</v>
       </c>
       <c r="AX8" s="47">
-        <v>9.7233055539283603E-5</v>
+        <v>-4.2356492140531703E-3</v>
       </c>
       <c r="AY8" s="46">
-        <v>0.34775068856472502</v>
+        <v>0.387230786050071</v>
       </c>
       <c r="AZ8" s="46">
-        <v>0.387230786050071</v>
+        <v>0.337318962613675</v>
       </c>
       <c r="BA8" s="46">
-        <v>0.337318962613675</v>
+        <v>0.35509446693657198</v>
       </c>
       <c r="BB8" s="46">
-        <v>0.35509446693657198</v>
+        <v>0.358412520961431</v>
       </c>
       <c r="BC8" s="46">
+        <v>0.36693091732729299</v>
+      </c>
+      <c r="BD8" s="46">
+        <v>0.37388483373884801</v>
+      </c>
+      <c r="BE8" s="46">
+        <v>0.36693091732729299</v>
+      </c>
+      <c r="BF8" s="47">
+        <v>-6.9539164115550202E-3</v>
+      </c>
+      <c r="BG8" s="46">
         <v>0.358412520961431</v>
       </c>
-      <c r="BD8" s="46">
-        <v>0.35509446693657198</v>
-      </c>
-      <c r="BE8" s="46">
-        <v>0.358412520961431</v>
-      </c>
-      <c r="BF8" s="47">
-        <v>3.31805402485874E-3</v>
-      </c>
-      <c r="BG8" s="46">
-        <v>0.36773440814594799</v>
-      </c>
       <c r="BH8" s="46">
-        <v>0.358412520961431</v>
+        <v>0.36693091732729299</v>
       </c>
       <c r="BI8" s="47">
-        <v>-9.3218871845173207E-3</v>
+        <v>8.5183963658623796E-3</v>
       </c>
       <c r="BJ8" s="46">
-        <v>4.9372641028256697E-2</v>
+        <v>6.2752815130643902E-2</v>
       </c>
       <c r="BK8" s="46">
-        <v>6.2752815130643902E-2</v>
+        <v>4.5638262041091303E-2</v>
       </c>
       <c r="BL8" s="46">
+        <v>5.9294871794871799E-2</v>
+      </c>
+      <c r="BM8" s="46">
+        <v>5.7574063722750098E-2</v>
+      </c>
+      <c r="BN8" s="46">
+        <v>5.3227633069082701E-2</v>
+      </c>
+      <c r="BO8" s="46">
+        <v>5.4237631792376298E-2</v>
+      </c>
+      <c r="BP8" s="46">
+        <v>5.3227633069082701E-2</v>
+      </c>
+      <c r="BQ8" s="46">
+        <v>-1.00999872329365E-3</v>
+      </c>
+      <c r="BR8" s="46">
+        <v>5.7574063722750098E-2</v>
+      </c>
+      <c r="BS8" s="46">
+        <v>5.3227633069082701E-2</v>
+      </c>
+      <c r="BT8" s="46">
+        <v>-4.3464306536674701E-3</v>
+      </c>
+      <c r="BU8" s="46">
+        <v>5.1710943478736199E-2</v>
+      </c>
+      <c r="BV8" s="46">
         <v>4.5638262041091303E-2</v>
       </c>
-      <c r="BM8" s="46">
+      <c r="BW8" s="46">
         <v>5.9294871794871799E-2</v>
       </c>
-      <c r="BN8" s="46">
+      <c r="BX8" s="46">
         <v>5.7574063722750098E-2</v>
       </c>
-      <c r="BO8" s="46">
-        <v>5.9294871794871799E-2</v>
-      </c>
-      <c r="BP8" s="46">
+      <c r="BY8" s="46">
+        <v>5.3227633069082701E-2</v>
+      </c>
+      <c r="BZ8" s="46">
+        <v>5.4237631792376298E-2</v>
+      </c>
+      <c r="CA8" s="46">
+        <v>5.3227633069082701E-2</v>
+      </c>
+      <c r="CB8" s="47">
+        <v>-4.3464306536674701E-3</v>
+      </c>
+      <c r="CC8" s="46">
         <v>5.7574063722750098E-2</v>
       </c>
-      <c r="BQ8" s="46">
-        <v>-1.7208080721216499E-3</v>
-      </c>
-      <c r="BR8" s="46">
-        <v>6.1624946966482803E-2</v>
-      </c>
-      <c r="BS8" s="46">
-        <v>5.7574063722750098E-2</v>
-      </c>
-      <c r="BT8" s="46">
-        <v>-4.0508832437326798E-3</v>
-      </c>
-      <c r="BU8" s="46">
-        <v>4.9372641028256697E-2</v>
-      </c>
-      <c r="BV8" s="46">
-        <v>5.1710943478736199E-2</v>
-      </c>
-      <c r="BW8" s="46">
-        <v>4.5638262041091303E-2</v>
-      </c>
-      <c r="BX8" s="46">
-        <v>5.9294871794871799E-2</v>
-      </c>
-      <c r="BY8" s="46">
-        <v>5.7574063722750098E-2</v>
-      </c>
-      <c r="BZ8" s="46">
-        <v>5.9294871794871799E-2</v>
-      </c>
-      <c r="CA8" s="46">
-        <v>5.7574063722750098E-2</v>
-      </c>
-      <c r="CB8" s="47">
-        <v>-1.7208080721216499E-3</v>
-      </c>
-      <c r="CC8" s="46">
-        <v>6.1624946966482803E-2</v>
-      </c>
       <c r="CD8" s="46">
-        <v>5.7574063722750098E-2</v>
+        <v>5.3227633069082701E-2</v>
       </c>
       <c r="CE8" s="46">
-        <v>-4.0508832437326798E-3</v>
+        <v>-4.3464306536674701E-3</v>
       </c>
       <c r="CF8" s="46">
-        <v>0</v>
+        <v>1.10418716519077E-2</v>
       </c>
       <c r="CG8" s="46">
-        <v>1.10418716519077E-2</v>
+        <v>0</v>
       </c>
       <c r="CH8" s="46">
         <v>0</v>
@@ -2697,85 +2698,85 @@
         <v>91</v>
       </c>
       <c r="M9" s="44">
-        <v>-1.34839130517767E-3</v>
+        <v>2.8355037920147201E-2</v>
       </c>
       <c r="N9" s="45">
-        <v>-1.34839130517767E-3</v>
+        <v>2.8355037920147201E-2</v>
       </c>
       <c r="O9" s="45">
         <v>0</v>
       </c>
       <c r="P9" s="45">
-        <v>-1.5091279317593499E-2</v>
+        <v>2.7141090170944002E-2</v>
       </c>
       <c r="Q9" s="45">
-        <v>1.6439670622771199E-2</v>
+        <v>-5.5496128091091203E-2</v>
       </c>
       <c r="R9" s="46">
-        <v>0.179087452471483</v>
+        <v>0.19304502897904599</v>
       </c>
       <c r="S9" s="46">
+        <v>0.174812857771907</v>
+      </c>
+      <c r="T9" s="46">
+        <v>0.15664018161180501</v>
+      </c>
+      <c r="U9" s="46">
+        <v>0.15529179030662699</v>
+      </c>
+      <c r="V9" s="46">
+        <v>0.174540682414698</v>
+      </c>
+      <c r="W9" s="46">
+        <v>0.14618564449455099</v>
+      </c>
+      <c r="X9" s="46">
+        <v>0.174540682414698</v>
+      </c>
+      <c r="Y9" s="46">
+        <v>2.8355037920147201E-2</v>
+      </c>
+      <c r="Z9" s="46">
+        <v>0.15529179030662699</v>
+      </c>
+      <c r="AA9" s="46">
+        <v>0.174540682414698</v>
+      </c>
+      <c r="AB9" s="46">
+        <v>1.9248892108071101E-2</v>
+      </c>
+      <c r="AC9" s="46">
         <v>0.19304502897904599</v>
       </c>
-      <c r="T9" s="46">
+      <c r="AD9" s="46">
         <v>0.174812857771907</v>
       </c>
-      <c r="U9" s="46">
+      <c r="AE9" s="46">
         <v>0.15664018161180501</v>
       </c>
-      <c r="V9" s="46">
+      <c r="AF9" s="46">
         <v>0.15529179030662699</v>
       </c>
-      <c r="W9" s="46">
-        <v>0.15664018161180501</v>
-      </c>
-      <c r="X9" s="46">
+      <c r="AG9" s="46">
+        <v>0.174540682414698</v>
+      </c>
+      <c r="AH9" s="46">
+        <v>0.14618564449455099</v>
+      </c>
+      <c r="AI9" s="46">
+        <v>0.174540682414698</v>
+      </c>
+      <c r="AJ9" s="46">
+        <v>2.8355037920147201E-2</v>
+      </c>
+      <c r="AK9" s="46">
         <v>0.15529179030662699</v>
       </c>
-      <c r="Y9" s="46">
-        <v>-1.34839130517767E-3</v>
-      </c>
-      <c r="Z9" s="46">
-        <v>0.17107875579086701</v>
-      </c>
-      <c r="AA9" s="46">
-        <v>0.15529179030662699</v>
-      </c>
-      <c r="AB9" s="46">
-        <v>-1.5786965484239902E-2</v>
-      </c>
-      <c r="AC9" s="46">
-        <v>0.179087452471483</v>
-      </c>
-      <c r="AD9" s="46">
-        <v>0.19304502897904599</v>
-      </c>
-      <c r="AE9" s="46">
-        <v>0.174812857771907</v>
-      </c>
-      <c r="AF9" s="46">
-        <v>0.15664018161180501</v>
-      </c>
-      <c r="AG9" s="46">
-        <v>0.15529179030662699</v>
-      </c>
-      <c r="AH9" s="46">
-        <v>0.15664018161180501</v>
-      </c>
-      <c r="AI9" s="46">
-        <v>0.15529179030662699</v>
-      </c>
-      <c r="AJ9" s="46">
-        <v>-1.34839130517767E-3</v>
-      </c>
-      <c r="AK9" s="46">
-        <v>0.17107875579086701</v>
-      </c>
       <c r="AL9" s="46">
-        <v>0.15529179030662699</v>
+        <v>0.174540682414698</v>
       </c>
       <c r="AM9" s="46">
-        <v>-1.5786965484239902E-2</v>
+        <v>1.9248892108071101E-2</v>
       </c>
       <c r="AN9" s="46">
         <v>0</v>
@@ -2811,103 +2812,103 @@
         <v>0</v>
       </c>
       <c r="AY9" s="46">
-        <v>0.65361216730037996</v>
+        <v>0.65358894337940299</v>
       </c>
       <c r="AZ9" s="46">
-        <v>0.65358894337940299</v>
+        <v>0.63672391017173002</v>
       </c>
       <c r="BA9" s="46">
-        <v>0.63672391017173002</v>
+        <v>0.69428679530836201</v>
       </c>
       <c r="BB9" s="46">
-        <v>0.69428679530836201</v>
+        <v>0.679195515990768</v>
       </c>
       <c r="BC9" s="46">
+        <v>0.67125984251968496</v>
+      </c>
+      <c r="BD9" s="46">
+        <v>0.64411875234874105</v>
+      </c>
+      <c r="BE9" s="46">
+        <v>0.67125984251968496</v>
+      </c>
+      <c r="BF9" s="47">
+        <v>2.7141090170944002E-2</v>
+      </c>
+      <c r="BG9" s="46">
         <v>0.679195515990768</v>
       </c>
-      <c r="BD9" s="46">
-        <v>0.69428679530836201</v>
-      </c>
-      <c r="BE9" s="46">
-        <v>0.679195515990768</v>
-      </c>
-      <c r="BF9" s="47">
-        <v>-1.5091279317593499E-2</v>
-      </c>
-      <c r="BG9" s="46">
-        <v>0.66776968894771704</v>
-      </c>
       <c r="BH9" s="46">
-        <v>0.679195515990768</v>
+        <v>0.67125984251968496</v>
       </c>
       <c r="BI9" s="46">
-        <v>1.1425827043051499E-2</v>
+        <v>-7.9356734710831506E-3</v>
       </c>
       <c r="BJ9" s="46">
-        <v>0.16730038022813701</v>
+        <v>0.15336602764155099</v>
       </c>
       <c r="BK9" s="46">
+        <v>0.18846323205636301</v>
+      </c>
+      <c r="BL9" s="46">
+        <v>0.149073023079834</v>
+      </c>
+      <c r="BM9" s="46">
+        <v>0.16551269370260499</v>
+      </c>
+      <c r="BN9" s="46">
+        <v>0.15419947506561699</v>
+      </c>
+      <c r="BO9" s="46">
+        <v>0.20969560315670799</v>
+      </c>
+      <c r="BP9" s="46">
+        <v>0.15419947506561699</v>
+      </c>
+      <c r="BQ9" s="46">
+        <v>-5.5496128091091203E-2</v>
+      </c>
+      <c r="BR9" s="46">
+        <v>0.16551269370260499</v>
+      </c>
+      <c r="BS9" s="46">
+        <v>0.15419947506561699</v>
+      </c>
+      <c r="BT9" s="47">
+        <v>-1.13132186369879E-2</v>
+      </c>
+      <c r="BU9" s="46">
         <v>0.15336602764155099</v>
       </c>
-      <c r="BL9" s="46">
+      <c r="BV9" s="46">
         <v>0.18846323205636301</v>
       </c>
-      <c r="BM9" s="46">
+      <c r="BW9" s="46">
         <v>0.149073023079834</v>
       </c>
-      <c r="BN9" s="46">
+      <c r="BX9" s="46">
         <v>0.16551269370260499</v>
       </c>
-      <c r="BO9" s="46">
-        <v>0.149073023079834</v>
-      </c>
-      <c r="BP9" s="46">
+      <c r="BY9" s="46">
+        <v>0.15419947506561699</v>
+      </c>
+      <c r="BZ9" s="46">
+        <v>0.20969560315670799</v>
+      </c>
+      <c r="CA9" s="46">
+        <v>0.15419947506561699</v>
+      </c>
+      <c r="CB9" s="46">
+        <v>-1.13132186369879E-2</v>
+      </c>
+      <c r="CC9" s="46">
         <v>0.16551269370260499</v>
       </c>
-      <c r="BQ9" s="46">
-        <v>1.6439670622771199E-2</v>
-      </c>
-      <c r="BR9" s="46">
-        <v>0.161151555261416</v>
-      </c>
-      <c r="BS9" s="46">
-        <v>0.16551269370260499</v>
-      </c>
-      <c r="BT9" s="47">
-        <v>4.3611384411884101E-3</v>
-      </c>
-      <c r="BU9" s="46">
-        <v>0.16730038022813701</v>
-      </c>
-      <c r="BV9" s="46">
-        <v>0.15336602764155099</v>
-      </c>
-      <c r="BW9" s="46">
-        <v>0.18846323205636301</v>
-      </c>
-      <c r="BX9" s="46">
-        <v>0.149073023079834</v>
-      </c>
-      <c r="BY9" s="46">
-        <v>0.16551269370260499</v>
-      </c>
-      <c r="BZ9" s="46">
-        <v>0.149073023079834</v>
-      </c>
-      <c r="CA9" s="46">
-        <v>0.16551269370260499</v>
-      </c>
-      <c r="CB9" s="46">
-        <v>1.6439670622771199E-2</v>
-      </c>
-      <c r="CC9" s="46">
-        <v>0.161151555261416</v>
-      </c>
       <c r="CD9" s="46">
-        <v>0.16551269370260499</v>
+        <v>0.15419947506561699</v>
       </c>
       <c r="CE9" s="47">
-        <v>4.3611384411884101E-3</v>
+        <v>-1.13132186369879E-2</v>
       </c>
       <c r="CF9" s="46">
         <v>0</v>
@@ -2981,217 +2982,217 @@
         <v>91</v>
       </c>
       <c r="M10" s="44">
-        <v>-1.8541841050492201E-2</v>
+        <v>-3.5427197881974801E-3</v>
       </c>
       <c r="N10" s="45">
-        <v>-1.65621251857931E-2</v>
+        <v>-1.35776943277008E-2</v>
       </c>
       <c r="O10" s="45">
-        <v>-1.9797158646991898E-3</v>
+        <v>1.0034974539503401E-2</v>
       </c>
       <c r="P10" s="45">
-        <v>1.7032213423667199E-2</v>
+        <v>-3.83217967306748E-3</v>
       </c>
       <c r="Q10" s="45">
-        <v>1.5096276268250399E-3</v>
+        <v>7.3748994612649697E-3</v>
       </c>
       <c r="R10" s="46">
-        <v>0.40353589025214998</v>
+        <v>0.40793167992512902</v>
       </c>
       <c r="S10" s="46">
-        <v>0.40793167992512902</v>
+        <v>0.39028397089884997</v>
       </c>
       <c r="T10" s="46">
-        <v>0.39028397089884997</v>
+        <v>0.39272535582498702</v>
       </c>
       <c r="U10" s="46">
-        <v>0.39272535582498702</v>
+        <v>0.37418351477449502</v>
       </c>
       <c r="V10" s="46">
+        <v>0.37547460236018498</v>
+      </c>
+      <c r="W10" s="46">
+        <v>0.37901732214838202</v>
+      </c>
+      <c r="X10" s="46">
+        <v>0.37547460236018498</v>
+      </c>
+      <c r="Y10" s="46">
+        <v>-3.5427197881974801E-3</v>
+      </c>
+      <c r="Z10" s="46">
         <v>0.37418351477449502</v>
       </c>
-      <c r="W10" s="46">
-        <v>0.39272535582498702</v>
-      </c>
-      <c r="X10" s="46">
-        <v>0.37418351477449502</v>
-      </c>
-      <c r="Y10" s="46">
-        <v>-1.8541841050492201E-2</v>
-      </c>
-      <c r="Z10" s="46">
-        <v>0.38200875139920598</v>
-      </c>
       <c r="AA10" s="46">
-        <v>0.37418351477449502</v>
+        <v>0.37547460236018498</v>
       </c>
       <c r="AB10" s="46">
-        <v>-7.8252366247116793E-3</v>
+        <v>1.2910875856901301E-3</v>
       </c>
       <c r="AC10" s="46">
-        <v>0.37339387498792398</v>
+        <v>0.377281235376696</v>
       </c>
       <c r="AD10" s="46">
-        <v>0.377281235376696</v>
+        <v>0.360596104200892</v>
       </c>
       <c r="AE10" s="46">
-        <v>0.360596104200892</v>
+        <v>0.360885608856089</v>
       </c>
       <c r="AF10" s="46">
-        <v>0.360885608856089</v>
+        <v>0.34432348367029503</v>
       </c>
       <c r="AG10" s="46">
+        <v>0.34386865059004601</v>
+      </c>
+      <c r="AH10" s="46">
+        <v>0.35744634491774702</v>
+      </c>
+      <c r="AI10" s="46">
+        <v>0.34386865059004601</v>
+      </c>
+      <c r="AJ10" s="46">
+        <v>-1.35776943277008E-2</v>
+      </c>
+      <c r="AK10" s="46">
         <v>0.34432348367029503</v>
       </c>
-      <c r="AH10" s="46">
-        <v>0.360885608856089</v>
-      </c>
-      <c r="AI10" s="46">
-        <v>0.34432348367029503</v>
-      </c>
-      <c r="AJ10" s="46">
-        <v>-1.65621251857931E-2</v>
-      </c>
-      <c r="AK10" s="46">
-        <v>0.34832604050066102</v>
-      </c>
       <c r="AL10" s="46">
-        <v>0.34432348367029503</v>
+        <v>0.34386865059004601</v>
       </c>
       <c r="AM10" s="46">
-        <v>-4.0025568303659904E-3</v>
+        <v>-4.5483308024929498E-4</v>
       </c>
       <c r="AN10" s="46">
-        <v>3.0142015264225702E-2</v>
+        <v>3.0650444548432399E-2</v>
       </c>
       <c r="AO10" s="46">
-        <v>3.0650444548432399E-2</v>
+        <v>2.9687866697958198E-2</v>
       </c>
       <c r="AP10" s="46">
-        <v>2.9687866697958198E-2</v>
+        <v>3.1839746968898297E-2</v>
       </c>
       <c r="AQ10" s="46">
-        <v>3.1839746968898297E-2</v>
+        <v>2.9860031104199099E-2</v>
       </c>
       <c r="AR10" s="46">
+        <v>3.1605951770138502E-2</v>
+      </c>
+      <c r="AS10" s="46">
+        <v>2.1570977230635099E-2</v>
+      </c>
+      <c r="AT10" s="46">
+        <v>3.1605951770138502E-2</v>
+      </c>
+      <c r="AU10" s="46">
+        <v>1.0034974539503401E-2</v>
+      </c>
+      <c r="AV10" s="46">
         <v>2.9860031104199099E-2</v>
       </c>
-      <c r="AS10" s="46">
-        <v>3.1839746968898297E-2</v>
-      </c>
-      <c r="AT10" s="46">
-        <v>2.9860031104199099E-2</v>
-      </c>
-      <c r="AU10" s="46">
-        <v>-1.9797158646991898E-3</v>
-      </c>
-      <c r="AV10" s="46">
-        <v>3.3682710898544799E-2</v>
-      </c>
       <c r="AW10" s="46">
-        <v>2.9860031104199099E-2</v>
+        <v>3.1605951770138502E-2</v>
       </c>
       <c r="AX10" s="46">
-        <v>-3.82267979434576E-3</v>
+        <v>1.74592066593946E-3</v>
       </c>
       <c r="AY10" s="46">
-        <v>0.50333301130325603</v>
+        <v>0.51895180159101495</v>
       </c>
       <c r="AZ10" s="46">
-        <v>0.51895180159101495</v>
+        <v>0.51842290542126301</v>
       </c>
       <c r="BA10" s="46">
-        <v>0.51842290542126301</v>
+        <v>0.51702688455456003</v>
       </c>
       <c r="BB10" s="46">
-        <v>0.51702688455456003</v>
+        <v>0.53405909797822704</v>
       </c>
       <c r="BC10" s="46">
+        <v>0.52857875833760903</v>
+      </c>
+      <c r="BD10" s="46">
+        <v>0.53241093801067696</v>
+      </c>
+      <c r="BE10" s="46">
+        <v>0.52857875833760903</v>
+      </c>
+      <c r="BF10" s="46">
+        <v>-3.83217967306748E-3</v>
+      </c>
+      <c r="BG10" s="46">
         <v>0.53405909797822704</v>
       </c>
-      <c r="BD10" s="46">
-        <v>0.51702688455456003</v>
-      </c>
-      <c r="BE10" s="46">
-        <v>0.53405909797822704</v>
-      </c>
-      <c r="BF10" s="46">
-        <v>1.7032213423667199E-2</v>
-      </c>
-      <c r="BG10" s="46">
-        <v>0.52304874325837003</v>
-      </c>
       <c r="BH10" s="46">
-        <v>0.53405909797822704</v>
+        <v>0.52857875833760903</v>
       </c>
       <c r="BI10" s="47">
-        <v>1.10103547198572E-2</v>
+        <v>-5.4803396406180004E-3</v>
       </c>
       <c r="BJ10" s="46">
-        <v>9.3131098444594704E-2</v>
+        <v>7.3116518483855905E-2</v>
       </c>
       <c r="BK10" s="46">
+        <v>9.1293123679887303E-2</v>
+      </c>
+      <c r="BL10" s="46">
+        <v>9.0247759620453394E-2</v>
+      </c>
+      <c r="BM10" s="46">
+        <v>9.1757387247278402E-2</v>
+      </c>
+      <c r="BN10" s="46">
+        <v>9.5946639302206302E-2</v>
+      </c>
+      <c r="BO10" s="46">
+        <v>8.8571739840941299E-2</v>
+      </c>
+      <c r="BP10" s="46">
+        <v>9.5946639302206302E-2</v>
+      </c>
+      <c r="BQ10" s="47">
+        <v>7.3748994612649697E-3</v>
+      </c>
+      <c r="BR10" s="46">
+        <v>9.1757387247278402E-2</v>
+      </c>
+      <c r="BS10" s="46">
+        <v>9.5946639302206302E-2</v>
+      </c>
+      <c r="BT10" s="47">
+        <v>4.1892520549278696E-3</v>
+      </c>
+      <c r="BU10" s="46">
         <v>7.3116518483855905E-2</v>
       </c>
-      <c r="BL10" s="46">
+      <c r="BV10" s="46">
         <v>9.1293123679887303E-2</v>
       </c>
-      <c r="BM10" s="46">
+      <c r="BW10" s="46">
         <v>9.0247759620453394E-2</v>
       </c>
-      <c r="BN10" s="46">
-        <v>9.1757387247278402E-2</v>
-      </c>
-      <c r="BO10" s="46">
-        <v>9.0247759620453394E-2</v>
-      </c>
-      <c r="BP10" s="46">
-        <v>9.1757387247278402E-2</v>
-      </c>
-      <c r="BQ10" s="47">
-        <v>1.5096276268250399E-3</v>
-      </c>
-      <c r="BR10" s="46">
-        <v>9.4942505342423905E-2</v>
-      </c>
-      <c r="BS10" s="46">
-        <v>9.1757387247278402E-2</v>
-      </c>
-      <c r="BT10" s="47">
-        <v>-3.1851180951455401E-3</v>
-      </c>
-      <c r="BU10" s="46">
-        <v>9.3131098444594704E-2</v>
-      </c>
-      <c r="BV10" s="46">
-        <v>7.3116518483855905E-2</v>
-      </c>
-      <c r="BW10" s="46">
-        <v>9.1293123679887303E-2</v>
-      </c>
       <c r="BX10" s="46">
-        <v>9.0247759620453394E-2</v>
+        <v>8.1389320891653696E-2</v>
       </c>
       <c r="BY10" s="46">
+        <v>8.2606464853771197E-2</v>
+      </c>
+      <c r="BZ10" s="46">
+        <v>8.8571739840941299E-2</v>
+      </c>
+      <c r="CA10" s="46">
+        <v>8.2606464853771197E-2</v>
+      </c>
+      <c r="CB10" s="47">
+        <v>1.2171439621174601E-3</v>
+      </c>
+      <c r="CC10" s="46">
         <v>8.1389320891653696E-2</v>
       </c>
-      <c r="BZ10" s="46">
-        <v>9.0247759620453394E-2</v>
-      </c>
-      <c r="CA10" s="46">
-        <v>8.1389320891653696E-2</v>
-      </c>
-      <c r="CB10" s="47">
-        <v>-8.8584387287996402E-3</v>
-      </c>
-      <c r="CC10" s="46">
-        <v>8.2731250636002895E-2</v>
-      </c>
       <c r="CD10" s="46">
-        <v>8.1389320891653696E-2</v>
+        <v>8.2606464853771197E-2</v>
       </c>
       <c r="CE10" s="47">
-        <v>-1.34192974434914E-3</v>
+        <v>1.2171439621174601E-3</v>
       </c>
       <c r="CF10" s="46">
         <v>0</v>
@@ -3203,28 +3204,28 @@
         <v>0</v>
       </c>
       <c r="CI10" s="46">
-        <v>0</v>
+        <v>1.03680663556247E-2</v>
       </c>
       <c r="CJ10" s="46">
+        <v>1.33401744484351E-2</v>
+      </c>
+      <c r="CK10" s="46">
+        <v>0</v>
+      </c>
+      <c r="CL10" s="46">
+        <v>1.33401744484351E-2</v>
+      </c>
+      <c r="CM10" s="46">
+        <v>2.9721080928104202E-3</v>
+      </c>
+      <c r="CN10" s="46">
         <v>1.03680663556247E-2</v>
       </c>
-      <c r="CK10" s="46">
-        <v>0</v>
-      </c>
-      <c r="CL10" s="46">
-        <v>1.03680663556247E-2</v>
-      </c>
-      <c r="CM10" s="46">
-        <v>1.03680663556247E-2</v>
-      </c>
-      <c r="CN10" s="46">
-        <v>1.22112547064211E-2</v>
-      </c>
       <c r="CO10" s="46">
-        <v>1.03680663556247E-2</v>
+        <v>1.33401744484351E-2</v>
       </c>
       <c r="CP10" s="46">
-        <v>-1.8431883507964101E-3</v>
+        <v>2.9721080928104202E-3</v>
       </c>
     </row>
     <row r="11" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3265,250 +3266,250 @@
         <v>35</v>
       </c>
       <c r="M11" s="44">
-        <v>-3.4738601049839599E-3</v>
+        <v>-1.1213735905333E-2</v>
       </c>
       <c r="N11" s="45">
-        <v>6.4717268063279E-3</v>
+        <v>-1.06100756791276E-2</v>
       </c>
       <c r="O11" s="45">
-        <v>-9.9455869113118708E-3</v>
+        <v>-6.0366022620544197E-4</v>
       </c>
       <c r="P11" s="45">
-        <v>-7.7097028646833099E-5</v>
+        <v>1.6418271192724699E-3</v>
       </c>
       <c r="Q11" s="45">
-        <v>3.5509571336307701E-3</v>
+        <v>9.5719087860606008E-3</v>
       </c>
       <c r="R11" s="46">
-        <v>0.57332996377727197</v>
+        <v>0.58203592814371297</v>
       </c>
       <c r="S11" s="46">
-        <v>0.58203592814371297</v>
+        <v>0.57177574792592001</v>
       </c>
       <c r="T11" s="46">
-        <v>0.57177574792592001</v>
+        <v>0.575809199318569</v>
       </c>
       <c r="U11" s="46">
-        <v>0.575809199318569</v>
+        <v>0.57233533921358504</v>
       </c>
       <c r="V11" s="46">
+        <v>0.57812368531762703</v>
+      </c>
+      <c r="W11" s="46">
+        <v>0.58933742122295996</v>
+      </c>
+      <c r="X11" s="46">
+        <v>0.57812368531762703</v>
+      </c>
+      <c r="Y11" s="46">
+        <v>-1.1213735905333E-2</v>
+      </c>
+      <c r="Z11" s="46">
         <v>0.57233533921358504</v>
       </c>
-      <c r="W11" s="46">
-        <v>0.575809199318569</v>
-      </c>
-      <c r="X11" s="46">
-        <v>0.57233533921358504</v>
-      </c>
-      <c r="Y11" s="46">
-        <v>-3.4738601049839599E-3</v>
-      </c>
-      <c r="Z11" s="46">
-        <v>0.57288107342278505</v>
-      </c>
       <c r="AA11" s="46">
-        <v>0.57233533921358504</v>
+        <v>0.57812368531762703</v>
       </c>
       <c r="AB11" s="46">
-        <v>-5.4573420920023296E-4</v>
+        <v>5.7883461040422199E-3</v>
       </c>
       <c r="AC11" s="46">
-        <v>0.52615617892342703</v>
+        <v>0.54294268605645801</v>
       </c>
       <c r="AD11" s="46">
-        <v>0.54294268605645801</v>
+        <v>0.53012653984748204</v>
       </c>
       <c r="AE11" s="46">
-        <v>0.53012653984748204</v>
+        <v>0.52555366269165205</v>
       </c>
       <c r="AF11" s="46">
-        <v>0.52555366269165205</v>
+        <v>0.53202538949797995</v>
       </c>
       <c r="AG11" s="46">
+        <v>0.53554901135885602</v>
+      </c>
+      <c r="AH11" s="46">
+        <v>0.54615908703798299</v>
+      </c>
+      <c r="AI11" s="46">
+        <v>0.53554901135885602</v>
+      </c>
+      <c r="AJ11" s="46">
+        <v>-1.06100756791276E-2</v>
+      </c>
+      <c r="AK11" s="46">
         <v>0.53202538949797995</v>
       </c>
-      <c r="AH11" s="46">
-        <v>0.52555366269165205</v>
-      </c>
-      <c r="AI11" s="46">
-        <v>0.53202538949797995</v>
-      </c>
-      <c r="AJ11" s="46">
-        <v>6.4717268063279E-3</v>
-      </c>
-      <c r="AK11" s="46">
-        <v>0.53187765647137297</v>
-      </c>
       <c r="AL11" s="46">
-        <v>0.53202538949797995</v>
+        <v>0.53554901135885602</v>
       </c>
       <c r="AM11" s="46">
-        <v>1.47733026607755E-4</v>
+        <v>3.5236218608752901E-3</v>
       </c>
       <c r="AN11" s="46">
-        <v>4.7173784853845498E-2</v>
+        <v>3.90932420872541E-2</v>
       </c>
       <c r="AO11" s="46">
-        <v>3.90932420872541E-2</v>
+        <v>4.1649208078437902E-2</v>
       </c>
       <c r="AP11" s="46">
-        <v>4.1649208078437902E-2</v>
+        <v>5.0255536626916501E-2</v>
       </c>
       <c r="AQ11" s="46">
-        <v>5.0255536626916501E-2</v>
+        <v>4.0309949715604601E-2</v>
       </c>
       <c r="AR11" s="46">
+        <v>4.2574673958771597E-2</v>
+      </c>
+      <c r="AS11" s="46">
+        <v>4.3178334184976998E-2</v>
+      </c>
+      <c r="AT11" s="46">
+        <v>4.2574673958771597E-2</v>
+      </c>
+      <c r="AU11" s="47">
+        <v>-6.0366022620544197E-4</v>
+      </c>
+      <c r="AV11" s="46">
         <v>4.0309949715604601E-2</v>
       </c>
-      <c r="AS11" s="46">
-        <v>5.0255536626916501E-2</v>
-      </c>
-      <c r="AT11" s="46">
-        <v>4.0309949715604601E-2</v>
-      </c>
-      <c r="AU11" s="47">
-        <v>-9.9455869113118708E-3</v>
-      </c>
-      <c r="AV11" s="46">
-        <v>4.1003416951412602E-2</v>
-      </c>
       <c r="AW11" s="46">
-        <v>4.0309949715604601E-2</v>
+        <v>4.2574673958771597E-2</v>
       </c>
       <c r="AX11" s="47">
-        <v>-6.9346723580796703E-4</v>
+        <v>2.2647242431669099E-3</v>
       </c>
       <c r="AY11" s="46">
-        <v>0.19223317327941999</v>
+        <v>0.20641573994867399</v>
       </c>
       <c r="AZ11" s="46">
-        <v>0.20641573994867399</v>
+        <v>0.21243610156708301</v>
       </c>
       <c r="BA11" s="46">
-        <v>0.21243610156708301</v>
+        <v>0.19420783645655901</v>
       </c>
       <c r="BB11" s="46">
-        <v>0.19420783645655901</v>
+        <v>0.19413073942791201</v>
       </c>
       <c r="BC11" s="46">
+        <v>0.19385780395456501</v>
+      </c>
+      <c r="BD11" s="46">
+        <v>0.19221597683529201</v>
+      </c>
+      <c r="BE11" s="46">
+        <v>0.19385780395456501</v>
+      </c>
+      <c r="BF11" s="47">
+        <v>1.6418271192724699E-3</v>
+      </c>
+      <c r="BG11" s="46">
         <v>0.19413073942791201</v>
       </c>
-      <c r="BD11" s="46">
-        <v>0.19420783645655901</v>
-      </c>
-      <c r="BE11" s="46">
-        <v>0.19413073942791201</v>
-      </c>
-      <c r="BF11" s="47">
-        <v>-7.7097028646833099E-5</v>
-      </c>
-      <c r="BG11" s="46">
-        <v>0.19601633469455801</v>
-      </c>
       <c r="BH11" s="46">
-        <v>0.19413073942791201</v>
+        <v>0.19385780395456501</v>
       </c>
       <c r="BI11" s="47">
-        <v>-1.8855952666459201E-3</v>
+        <v>-2.7293547334736302E-4</v>
       </c>
       <c r="BJ11" s="46">
-        <v>0.23443686294330701</v>
+        <v>0.21154833190761299</v>
       </c>
       <c r="BK11" s="46">
-        <v>0.21154833190761299</v>
+        <v>0.21578815050699701</v>
       </c>
       <c r="BL11" s="46">
-        <v>0.21578815050699701</v>
+        <v>0.22998296422487199</v>
       </c>
       <c r="BM11" s="46">
-        <v>0.22998296422487199</v>
+        <v>0.23353392135850301</v>
       </c>
       <c r="BN11" s="46">
+        <v>0.22801851072780799</v>
+      </c>
+      <c r="BO11" s="46">
+        <v>0.218446601941748</v>
+      </c>
+      <c r="BP11" s="46">
+        <v>0.22801851072780799</v>
+      </c>
+      <c r="BQ11" s="47">
+        <v>9.5719087860606008E-3</v>
+      </c>
+      <c r="BR11" s="46">
         <v>0.23353392135850301</v>
       </c>
-      <c r="BO11" s="46">
-        <v>0.22998296422487199</v>
-      </c>
-      <c r="BP11" s="46">
-        <v>0.23353392135850301</v>
-      </c>
-      <c r="BQ11" s="47">
-        <v>3.5509571336307701E-3</v>
-      </c>
-      <c r="BR11" s="46">
-        <v>0.231102591882657</v>
-      </c>
       <c r="BS11" s="46">
-        <v>0.23353392135850301</v>
+        <v>0.22801851072780799</v>
       </c>
       <c r="BT11" s="46">
-        <v>2.4313294758461202E-3</v>
+        <v>-5.5154106306948602E-3</v>
       </c>
       <c r="BU11" s="46">
-        <v>0.21000758150113699</v>
+        <v>0.17929854576561199</v>
       </c>
       <c r="BV11" s="46">
-        <v>0.17929854576561199</v>
+        <v>0.18830134919969799</v>
       </c>
       <c r="BW11" s="46">
-        <v>0.18830134919969799</v>
+        <v>0.18654173764906301</v>
       </c>
       <c r="BX11" s="46">
-        <v>0.18654173764906301</v>
+        <v>0.19487264034292301</v>
       </c>
       <c r="BY11" s="46">
+        <v>0.192090870845604</v>
+      </c>
+      <c r="BZ11" s="46">
+        <v>0.18114460909555399</v>
+      </c>
+      <c r="CA11" s="46">
+        <v>0.192090870845604</v>
+      </c>
+      <c r="CB11" s="47">
+        <v>-2.7817694973194E-3</v>
+      </c>
+      <c r="CC11" s="46">
         <v>0.19487264034292301</v>
       </c>
-      <c r="BZ11" s="46">
-        <v>0.18654173764906301</v>
-      </c>
-      <c r="CA11" s="46">
-        <v>0.19487264034292301</v>
-      </c>
-      <c r="CB11" s="47">
-        <v>8.3309026938600504E-3</v>
-      </c>
-      <c r="CC11" s="46">
-        <v>0.19426618884907099</v>
-      </c>
       <c r="CD11" s="46">
-        <v>0.19487264034292301</v>
+        <v>0.192090870845604</v>
       </c>
       <c r="CE11" s="46">
-        <v>6.0645149385232799E-4</v>
+        <v>-2.7817694973194E-3</v>
       </c>
       <c r="CF11" s="46">
-        <v>2.4429281442169999E-2</v>
+        <v>3.2249786142001698E-2</v>
       </c>
       <c r="CG11" s="46">
-        <v>3.2249786142001698E-2</v>
+        <v>2.7486801307299101E-2</v>
       </c>
       <c r="CH11" s="46">
-        <v>2.7486801307299101E-2</v>
+        <v>4.3441226575809198E-2</v>
       </c>
       <c r="CI11" s="46">
-        <v>4.3441226575809198E-2</v>
+        <v>3.8661281015579897E-2</v>
       </c>
       <c r="CJ11" s="46">
+        <v>3.5927639882204501E-2</v>
+      </c>
+      <c r="CK11" s="46">
+        <v>3.7301992846193101E-2</v>
+      </c>
+      <c r="CL11" s="46">
+        <v>3.5927639882204501E-2</v>
+      </c>
+      <c r="CM11" s="47">
+        <v>-2.7336411333754602E-3</v>
+      </c>
+      <c r="CN11" s="46">
         <v>3.8661281015579897E-2</v>
       </c>
-      <c r="CK11" s="46">
-        <v>4.3441226575809198E-2</v>
-      </c>
-      <c r="CL11" s="46">
-        <v>3.8661281015579897E-2</v>
-      </c>
-      <c r="CM11" s="47">
-        <v>-4.7799455602292804E-3</v>
-      </c>
-      <c r="CN11" s="46">
-        <v>3.6836403033586103E-2</v>
-      </c>
       <c r="CO11" s="46">
-        <v>3.8661281015579897E-2</v>
+        <v>3.5927639882204501E-2</v>
       </c>
       <c r="CP11" s="46">
-        <v>1.82487798199379E-3</v>
+        <v>-2.7336411333754602E-3</v>
       </c>
     </row>
     <row r="12" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3549,250 +3550,250 @@
         <v>35</v>
       </c>
       <c r="M12" s="44">
-        <v>5.1991762586428604E-3</v>
+        <v>3.5591246493817598E-2</v>
       </c>
       <c r="N12" s="45">
-        <v>-6.0466926752616402E-3</v>
+        <v>3.5728214500766999E-2</v>
       </c>
       <c r="O12" s="45">
-        <v>1.12458689339045E-2</v>
+        <v>-1.3696800694944201E-4</v>
       </c>
       <c r="P12" s="45">
-        <v>-3.4454074665115901E-2</v>
+        <v>-1.8278038010993199E-2</v>
       </c>
       <c r="Q12" s="45">
-        <v>2.9254898406472999E-2</v>
+        <v>-1.7313208482824399E-2</v>
       </c>
       <c r="R12" s="46">
-        <v>0.45179809358752199</v>
+        <v>0.463187748156551</v>
       </c>
       <c r="S12" s="46">
-        <v>0.463187748156551</v>
+        <v>0.45247581104154799</v>
       </c>
       <c r="T12" s="46">
-        <v>0.45247581104154799</v>
+        <v>0.461059907834101</v>
       </c>
       <c r="U12" s="46">
-        <v>0.461059907834101</v>
+        <v>0.46625908409274402</v>
       </c>
       <c r="V12" s="46">
+        <v>0.48463272813575398</v>
+      </c>
+      <c r="W12" s="46">
+        <v>0.44904148164193702</v>
+      </c>
+      <c r="X12" s="46">
+        <v>0.48463272813575398</v>
+      </c>
+      <c r="Y12" s="46">
+        <v>3.5591246493817598E-2</v>
+      </c>
+      <c r="Z12" s="46">
         <v>0.46625908409274402</v>
       </c>
-      <c r="W12" s="46">
-        <v>0.461059907834101</v>
-      </c>
-      <c r="X12" s="46">
-        <v>0.46625908409274402</v>
-      </c>
-      <c r="Y12" s="46">
-        <v>5.1991762586428604E-3</v>
-      </c>
-      <c r="Z12" s="46">
-        <v>0.46262944619540702</v>
-      </c>
       <c r="AA12" s="46">
-        <v>0.46625908409274402</v>
+        <v>0.48463272813575398</v>
       </c>
       <c r="AB12" s="46">
-        <v>3.6296378973367802E-3</v>
+        <v>1.8373644043009899E-2</v>
       </c>
       <c r="AC12" s="46">
-        <v>0.38355719237434999</v>
+        <v>0.39387407827566601</v>
       </c>
       <c r="AD12" s="46">
-        <v>0.39387407827566601</v>
+        <v>0.39476380193511701</v>
       </c>
       <c r="AE12" s="46">
-        <v>0.39476380193511701</v>
+        <v>0.41647465437788</v>
       </c>
       <c r="AF12" s="46">
-        <v>0.41647465437788</v>
+        <v>0.41042796170261903</v>
       </c>
       <c r="AG12" s="46">
+        <v>0.42292630829476702</v>
+      </c>
+      <c r="AH12" s="46">
+        <v>0.387198093794</v>
+      </c>
+      <c r="AI12" s="46">
+        <v>0.42292630829476702</v>
+      </c>
+      <c r="AJ12" s="46">
+        <v>3.5728214500766999E-2</v>
+      </c>
+      <c r="AK12" s="46">
         <v>0.41042796170261903</v>
       </c>
-      <c r="AH12" s="46">
-        <v>0.41647465437788</v>
-      </c>
-      <c r="AI12" s="46">
-        <v>0.41042796170261903</v>
-      </c>
-      <c r="AJ12" s="46">
-        <v>-6.0466926752616402E-3</v>
-      </c>
-      <c r="AK12" s="46">
-        <v>0.39801891040072002</v>
-      </c>
       <c r="AL12" s="46">
-        <v>0.41042796170261903</v>
+        <v>0.42292630829476702</v>
       </c>
       <c r="AM12" s="46">
-        <v>1.2409051301898099E-2</v>
+        <v>1.24983465921483E-2</v>
       </c>
       <c r="AN12" s="46">
-        <v>6.8240901213171598E-2</v>
+        <v>6.9313669880884901E-2</v>
       </c>
       <c r="AO12" s="46">
-        <v>6.9313669880884901E-2</v>
+        <v>5.77120091064314E-2</v>
       </c>
       <c r="AP12" s="46">
-        <v>5.77120091064314E-2</v>
+        <v>4.4585253456221198E-2</v>
       </c>
       <c r="AQ12" s="46">
-        <v>4.4585253456221198E-2</v>
+        <v>5.5831122390125699E-2</v>
       </c>
       <c r="AR12" s="46">
+        <v>6.1706419840987299E-2</v>
+      </c>
+      <c r="AS12" s="46">
+        <v>6.18433878479367E-2</v>
+      </c>
+      <c r="AT12" s="46">
+        <v>6.1706419840987299E-2</v>
+      </c>
+      <c r="AU12" s="46">
+        <v>-1.3696800694944201E-4</v>
+      </c>
+      <c r="AV12" s="46">
         <v>5.5831122390125699E-2</v>
       </c>
-      <c r="AS12" s="46">
-        <v>4.4585253456221198E-2</v>
-      </c>
-      <c r="AT12" s="46">
-        <v>5.5831122390125699E-2</v>
-      </c>
-      <c r="AU12" s="46">
-        <v>1.12458689339045E-2</v>
-      </c>
-      <c r="AV12" s="46">
-        <v>6.4610535794687105E-2</v>
-      </c>
       <c r="AW12" s="46">
-        <v>5.5831122390125699E-2</v>
+        <v>6.1706419840987299E-2</v>
       </c>
       <c r="AX12" s="47">
-        <v>-8.7794134045613408E-3</v>
+        <v>5.8752974508615701E-3</v>
       </c>
       <c r="AY12" s="46">
-        <v>0.38572357019064102</v>
+        <v>0.37787861599546202</v>
       </c>
       <c r="AZ12" s="46">
-        <v>0.37787861599546202</v>
+        <v>0.39590210586226499</v>
       </c>
       <c r="BA12" s="46">
-        <v>0.39590210586226499</v>
+        <v>0.39251152073732698</v>
       </c>
       <c r="BB12" s="46">
-        <v>0.39251152073732698</v>
+        <v>0.35805744607221102</v>
       </c>
       <c r="BC12" s="46">
+        <v>0.36133855464578102</v>
+      </c>
+      <c r="BD12" s="46">
+        <v>0.379616592656775</v>
+      </c>
+      <c r="BE12" s="46">
+        <v>0.36133855464578102</v>
+      </c>
+      <c r="BF12" s="47">
+        <v>-1.8278038010993199E-2</v>
+      </c>
+      <c r="BG12" s="46">
         <v>0.35805744607221102</v>
       </c>
-      <c r="BD12" s="46">
-        <v>0.39251152073732698</v>
-      </c>
-      <c r="BE12" s="46">
-        <v>0.35805744607221102</v>
-      </c>
-      <c r="BF12" s="47">
-        <v>-3.4454074665115901E-2</v>
-      </c>
-      <c r="BG12" s="46">
-        <v>0.37010355695632602</v>
-      </c>
       <c r="BH12" s="46">
-        <v>0.35805744607221102</v>
+        <v>0.36133855464578102</v>
       </c>
       <c r="BI12" s="46">
-        <v>-1.20461108841146E-2</v>
+        <v>3.28110857357006E-3</v>
       </c>
       <c r="BJ12" s="46">
-        <v>0.16247833622183699</v>
+        <v>0.158933635847986</v>
       </c>
       <c r="BK12" s="46">
+        <v>0.15162208309618699</v>
+      </c>
+      <c r="BL12" s="46">
+        <v>0.14642857142857099</v>
+      </c>
+      <c r="BM12" s="46">
+        <v>0.17568346983504399</v>
+      </c>
+      <c r="BN12" s="46">
+        <v>0.15402871721846401</v>
+      </c>
+      <c r="BO12" s="46">
+        <v>0.17134192570128901</v>
+      </c>
+      <c r="BP12" s="46">
+        <v>0.15402871721846401</v>
+      </c>
+      <c r="BQ12" s="47">
+        <v>-1.7313208482824399E-2</v>
+      </c>
+      <c r="BR12" s="46">
+        <v>0.17568346983504399</v>
+      </c>
+      <c r="BS12" s="46">
+        <v>0.15402871721846401</v>
+      </c>
+      <c r="BT12" s="47">
+        <v>-2.1654752616580002E-2</v>
+      </c>
+      <c r="BU12" s="46">
         <v>0.158933635847986</v>
       </c>
-      <c r="BL12" s="46">
-        <v>0.15162208309618699</v>
-      </c>
-      <c r="BM12" s="46">
+      <c r="BV12" s="46">
+        <v>0.13921457029026801</v>
+      </c>
+      <c r="BW12" s="46">
         <v>0.14642857142857099</v>
       </c>
-      <c r="BN12" s="46">
-        <v>0.17568346983504399</v>
-      </c>
-      <c r="BO12" s="46">
-        <v>0.14642857142857099</v>
-      </c>
-      <c r="BP12" s="46">
-        <v>0.17568346983504399</v>
-      </c>
-      <c r="BQ12" s="47">
-        <v>2.9254898406472999E-2</v>
-      </c>
-      <c r="BR12" s="46">
-        <v>0.16726699684826701</v>
-      </c>
-      <c r="BS12" s="46">
-        <v>0.17568346983504399</v>
-      </c>
-      <c r="BT12" s="47">
-        <v>8.4164729867778603E-3</v>
-      </c>
-      <c r="BU12" s="46">
-        <v>0.16247833622183699</v>
-      </c>
-      <c r="BV12" s="46">
-        <v>0.158933635847986</v>
-      </c>
-      <c r="BW12" s="46">
-        <v>0.13921457029026801</v>
-      </c>
       <c r="BX12" s="46">
-        <v>0.14642857142857099</v>
+        <v>0.16080286076825501</v>
       </c>
       <c r="BY12" s="46">
+        <v>0.15402871721846401</v>
+      </c>
+      <c r="BZ12" s="46">
+        <v>0.15509585183580599</v>
+      </c>
+      <c r="CA12" s="46">
+        <v>0.15402871721846401</v>
+      </c>
+      <c r="CB12" s="46">
+        <v>-6.7741435497902496E-3</v>
+      </c>
+      <c r="CC12" s="46">
         <v>0.16080286076825501</v>
       </c>
-      <c r="BZ12" s="46">
-        <v>0.14642857142857099</v>
-      </c>
-      <c r="CA12" s="46">
-        <v>0.16080286076825501</v>
-      </c>
-      <c r="CB12" s="46">
-        <v>1.4374289339683301E-2</v>
-      </c>
-      <c r="CC12" s="46">
-        <v>0.16726699684826701</v>
-      </c>
       <c r="CD12" s="46">
-        <v>0.16080286076825501</v>
+        <v>0.15402871721846401</v>
       </c>
       <c r="CE12" s="47">
-        <v>-6.4641360800118397E-3</v>
+        <v>-6.7741435497902496E-3</v>
       </c>
       <c r="CF12" s="46">
         <v>0</v>
       </c>
       <c r="CG12" s="46">
-        <v>0</v>
+        <v>1.24075128059192E-2</v>
       </c>
       <c r="CH12" s="46">
-        <v>1.24075128059192E-2</v>
+        <v>0</v>
       </c>
       <c r="CI12" s="46">
-        <v>0</v>
+        <v>1.48806090667897E-2</v>
       </c>
       <c r="CJ12" s="46">
+        <v>0</v>
+      </c>
+      <c r="CK12" s="46">
+        <v>1.6246073865482501E-2</v>
+      </c>
+      <c r="CL12" s="46">
+        <v>0</v>
+      </c>
+      <c r="CM12" s="46">
+        <v>-1.48806090667897E-2</v>
+      </c>
+      <c r="CN12" s="46">
         <v>1.48806090667897E-2</v>
       </c>
-      <c r="CK12" s="46">
-        <v>0</v>
-      </c>
-      <c r="CL12" s="46">
-        <v>1.48806090667897E-2</v>
-      </c>
-      <c r="CM12" s="46">
-        <v>1.48806090667897E-2</v>
-      </c>
-      <c r="CN12" s="46">
-        <v>0</v>
-      </c>
       <c r="CO12" s="46">
-        <v>1.48806090667897E-2</v>
+        <v>0</v>
       </c>
       <c r="CP12" s="47">
-        <v>1.48806090667897E-2</v>
+        <v>-1.48806090667897E-2</v>
       </c>
     </row>
     <row r="13" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3833,217 +3834,217 @@
         <v>35</v>
       </c>
       <c r="M13" s="44">
-        <v>2.8139270743727102E-2</v>
+        <v>-8.5748078060319394E-2</v>
       </c>
       <c r="N13" s="45">
-        <v>-2.8273714886927401E-2</v>
+        <v>-5.9136605558840899E-2</v>
       </c>
       <c r="O13" s="45">
+        <v>-2.6611472501478401E-2</v>
+      </c>
+      <c r="P13" s="45">
+        <v>-1.24186871673566E-2</v>
+      </c>
+      <c r="Q13" s="45">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="R13" s="46">
+        <v>0.49089805825242699</v>
+      </c>
+      <c r="S13" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="46">
+        <v>0.443920335429769</v>
+      </c>
+      <c r="U13" s="46">
+        <v>0.47205960617349702</v>
+      </c>
+      <c r="V13" s="46">
+        <v>0.46244825547013602</v>
+      </c>
+      <c r="W13" s="46">
+        <v>0.54819633353045505</v>
+      </c>
+      <c r="X13" s="46">
+        <v>0.46244825547013602</v>
+      </c>
+      <c r="Y13" s="46">
+        <v>-8.5748078060319394E-2</v>
+      </c>
+      <c r="Z13" s="46">
+        <v>0.47205960617349702</v>
+      </c>
+      <c r="AA13" s="46">
+        <v>0.46244825547013602</v>
+      </c>
+      <c r="AB13" s="46">
+        <v>-9.6113507033604995E-3</v>
+      </c>
+      <c r="AC13" s="46">
+        <v>0.393810679611651</v>
+      </c>
+      <c r="AD13" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="AE13" s="46">
+        <v>0.443920335429769</v>
+      </c>
+      <c r="AF13" s="46">
+        <v>0.41564662054284202</v>
+      </c>
+      <c r="AG13" s="46">
+        <v>0.40449438202247201</v>
+      </c>
+      <c r="AH13" s="46">
+        <v>0.46363098758131299</v>
+      </c>
+      <c r="AI13" s="46">
+        <v>0.40449438202247201</v>
+      </c>
+      <c r="AJ13" s="46">
+        <v>-5.9136605558840899E-2</v>
+      </c>
+      <c r="AK13" s="46">
+        <v>0.41564662054284202</v>
+      </c>
+      <c r="AL13" s="46">
+        <v>0.40449438202247201</v>
+      </c>
+      <c r="AM13" s="46">
+        <v>-1.11522385203701E-2</v>
+      </c>
+      <c r="AN13" s="46">
+        <v>9.7087378640776698E-2</v>
+      </c>
+      <c r="AO13" s="46">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="46">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="46">
         <v>5.6412985630654597E-2</v>
       </c>
-      <c r="P13" s="45">
-        <v>-4.3827117104753698E-2</v>
-      </c>
-      <c r="Q13" s="45">
-        <v>1.5687846361026599E-2</v>
-      </c>
-      <c r="R13" s="46">
-        <v>0.42754662840746099</v>
-      </c>
-      <c r="S13" s="46">
-        <v>0.49089805825242699</v>
-      </c>
-      <c r="T13" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="U13" s="46">
-        <v>0.443920335429769</v>
-      </c>
-      <c r="V13" s="46">
-        <v>0.47205960617349702</v>
-      </c>
-      <c r="W13" s="46">
-        <v>0.443920335429769</v>
-      </c>
-      <c r="X13" s="46">
-        <v>0.47205960617349702</v>
-      </c>
-      <c r="Y13" s="46">
-        <v>2.8139270743727102E-2</v>
-      </c>
-      <c r="Z13" s="46">
-        <v>0.51241134751773099</v>
-      </c>
-      <c r="AA13" s="46">
-        <v>0.47205960617349702</v>
-      </c>
-      <c r="AB13" s="46">
-        <v>-4.0351741344233999E-2</v>
-      </c>
-      <c r="AC13" s="46">
-        <v>0.42754662840746099</v>
-      </c>
-      <c r="AD13" s="46">
-        <v>0.393810679611651</v>
-      </c>
-      <c r="AE13" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" s="46">
-        <v>0.443920335429769</v>
-      </c>
-      <c r="AG13" s="46">
-        <v>0.41564662054284202</v>
-      </c>
-      <c r="AH13" s="46">
-        <v>0.443920335429769</v>
-      </c>
-      <c r="AI13" s="46">
-        <v>0.41564662054284202</v>
-      </c>
-      <c r="AJ13" s="46">
-        <v>-2.8273714886927401E-2</v>
-      </c>
-      <c r="AK13" s="46">
-        <v>0.51241134751773099</v>
-      </c>
-      <c r="AL13" s="46">
-        <v>0.41564662054284202</v>
-      </c>
-      <c r="AM13" s="46">
-        <v>-9.6764726974888596E-2</v>
-      </c>
-      <c r="AN13" s="46">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="46">
-        <v>9.7087378640776698E-2</v>
-      </c>
-      <c r="AP13" s="46">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="46">
-        <v>0</v>
-      </c>
       <c r="AR13" s="46">
+        <v>5.7953873447664103E-2</v>
+      </c>
+      <c r="AS13" s="46">
+        <v>8.4565345949142501E-2</v>
+      </c>
+      <c r="AT13" s="46">
+        <v>5.7953873447664103E-2</v>
+      </c>
+      <c r="AU13" s="46">
+        <v>-2.6611472501478401E-2</v>
+      </c>
+      <c r="AV13" s="46">
         <v>5.6412985630654597E-2</v>
       </c>
-      <c r="AS13" s="46">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="46">
-        <v>5.6412985630654597E-2</v>
-      </c>
-      <c r="AU13" s="46">
-        <v>5.6412985630654597E-2</v>
-      </c>
-      <c r="AV13" s="46">
-        <v>0</v>
-      </c>
       <c r="AW13" s="46">
-        <v>5.6412985630654597E-2</v>
+        <v>5.7953873447664103E-2</v>
       </c>
       <c r="AX13" s="47">
-        <v>5.6412985630654597E-2</v>
+        <v>1.5408878170095001E-3</v>
       </c>
       <c r="AY13" s="46">
-        <v>0.42754662840746099</v>
+        <v>0.442354368932039</v>
       </c>
       <c r="AZ13" s="46">
-        <v>0.442354368932039</v>
+        <v>0.39113924050632898</v>
       </c>
       <c r="BA13" s="46">
-        <v>0.39113924050632898</v>
+        <v>0.470649895178197</v>
       </c>
       <c r="BB13" s="46">
-        <v>0.470649895178197</v>
+        <v>0.42682277807344299</v>
       </c>
       <c r="BC13" s="46">
+        <v>0.43938497930218801</v>
+      </c>
+      <c r="BD13" s="46">
+        <v>0.45180366646954501</v>
+      </c>
+      <c r="BE13" s="46">
+        <v>0.43938497930218801</v>
+      </c>
+      <c r="BF13" s="47">
+        <v>-1.24186871673566E-2</v>
+      </c>
+      <c r="BG13" s="46">
         <v>0.42682277807344299</v>
       </c>
-      <c r="BD13" s="46">
-        <v>0.470649895178197</v>
-      </c>
-      <c r="BE13" s="46">
-        <v>0.42682277807344299</v>
-      </c>
-      <c r="BF13" s="47">
-        <v>-4.3827117104753698E-2</v>
-      </c>
-      <c r="BG13" s="46">
-        <v>0.40602836879432602</v>
-      </c>
       <c r="BH13" s="46">
-        <v>0.42682277807344299</v>
+        <v>0.43938497930218801</v>
       </c>
       <c r="BI13" s="47">
-        <v>2.0794409279117101E-2</v>
+        <v>1.2562201228744701E-2</v>
       </c>
       <c r="BJ13" s="46">
-        <v>0.14490674318507901</v>
+        <v>6.6747572815534006E-2</v>
       </c>
       <c r="BK13" s="46">
+        <v>0.10886075949367099</v>
+      </c>
+      <c r="BL13" s="46">
+        <v>8.5429769392033506E-2</v>
+      </c>
+      <c r="BM13" s="46">
+        <v>0.10111761575306</v>
+      </c>
+      <c r="BN13" s="46">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="BO13" s="46">
+        <v>0</v>
+      </c>
+      <c r="BP13" s="46">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="BQ13" s="47">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="BR13" s="46">
+        <v>0.10111761575306</v>
+      </c>
+      <c r="BS13" s="46">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="BT13" s="46">
+        <v>-2.9508505253842002E-3</v>
+      </c>
+      <c r="BU13" s="46">
         <v>6.6747572815534006E-2</v>
       </c>
-      <c r="BL13" s="46">
+      <c r="BV13" s="46">
         <v>0.10886075949367099</v>
       </c>
-      <c r="BM13" s="46">
+      <c r="BW13" s="46">
         <v>8.5429769392033506E-2</v>
       </c>
-      <c r="BN13" s="46">
+      <c r="BX13" s="46">
         <v>0.10111761575306</v>
       </c>
-      <c r="BO13" s="46">
-        <v>8.5429769392033506E-2</v>
-      </c>
-      <c r="BP13" s="46">
+      <c r="BY13" s="46">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="BZ13" s="46">
+        <v>0</v>
+      </c>
+      <c r="CA13" s="46">
+        <v>9.8166765227675895E-2</v>
+      </c>
+      <c r="CB13" s="47">
+        <v>-2.9508505253842002E-3</v>
+      </c>
+      <c r="CC13" s="46">
         <v>0.10111761575306</v>
       </c>
-      <c r="BQ13" s="47">
-        <v>1.5687846361026599E-2</v>
-      </c>
-      <c r="BR13" s="46">
-        <v>8.1560283687943297E-2</v>
-      </c>
-      <c r="BS13" s="46">
-        <v>0.10111761575306</v>
-      </c>
-      <c r="BT13" s="46">
-        <v>1.9557332065116902E-2</v>
-      </c>
-      <c r="BU13" s="46">
-        <v>0.14490674318507901</v>
-      </c>
-      <c r="BV13" s="46">
-        <v>6.6747572815534006E-2</v>
-      </c>
-      <c r="BW13" s="46">
-        <v>0.10886075949367099</v>
-      </c>
-      <c r="BX13" s="46">
-        <v>8.5429769392033506E-2</v>
-      </c>
-      <c r="BY13" s="46">
-        <v>0.10111761575306</v>
-      </c>
-      <c r="BZ13" s="46">
-        <v>8.5429769392033506E-2</v>
-      </c>
-      <c r="CA13" s="46">
-        <v>0.10111761575306</v>
-      </c>
-      <c r="CB13" s="47">
-        <v>1.5687846361026599E-2</v>
-      </c>
-      <c r="CC13" s="46">
-        <v>8.1560283687943297E-2</v>
-      </c>
       <c r="CD13" s="46">
-        <v>0.10111761575306</v>
+        <v>9.8166765227675895E-2</v>
       </c>
       <c r="CE13" s="46">
-        <v>1.9557332065116902E-2</v>
+        <v>-2.9508505253842002E-3</v>
       </c>
       <c r="CF13" s="46">
         <v>0</v>
@@ -4117,217 +4118,217 @@
         <v>91</v>
       </c>
       <c r="M14" s="44">
-        <v>-2.7799390228398599E-2</v>
+        <v>-4.59553657846134E-2</v>
       </c>
       <c r="N14" s="45">
-        <v>-4.21745592562544E-2</v>
+        <v>-1.6221064384649798E-2</v>
       </c>
       <c r="O14" s="45">
-        <v>1.4375169027855799E-2</v>
+        <v>-2.9734301399963602E-2</v>
       </c>
       <c r="P14" s="45">
-        <v>1.38546210193218E-2</v>
+        <v>2.0318547205939098E-2</v>
       </c>
       <c r="Q14" s="45">
-        <v>1.39447692090768E-2</v>
+        <v>2.5636818578674201E-2</v>
       </c>
       <c r="R14" s="46">
-        <v>0.33734439834024899</v>
+        <v>0.319872476089267</v>
       </c>
       <c r="S14" s="46">
-        <v>0.319872476089267</v>
+        <v>0.32198883275724499</v>
       </c>
       <c r="T14" s="46">
-        <v>0.32198883275724499</v>
+        <v>0.33081380700428298</v>
       </c>
       <c r="U14" s="46">
-        <v>0.33081380700428298</v>
+        <v>0.30301441677588498</v>
       </c>
       <c r="V14" s="46">
+        <v>0.30924709449216797</v>
+      </c>
+      <c r="W14" s="46">
+        <v>0.35520246027678098</v>
+      </c>
+      <c r="X14" s="46">
+        <v>0.30924709449216797</v>
+      </c>
+      <c r="Y14" s="46">
+        <v>-4.59553657846134E-2</v>
+      </c>
+      <c r="Z14" s="46">
         <v>0.30301441677588498</v>
       </c>
-      <c r="W14" s="46">
-        <v>0.33081380700428298</v>
-      </c>
-      <c r="X14" s="46">
-        <v>0.30301441677588498</v>
-      </c>
-      <c r="Y14" s="46">
-        <v>-2.7799390228398599E-2</v>
-      </c>
-      <c r="Z14" s="46">
-        <v>0.33496452165402502</v>
-      </c>
       <c r="AA14" s="46">
-        <v>0.30301441677588498</v>
+        <v>0.30924709449216797</v>
       </c>
       <c r="AB14" s="46">
-        <v>-3.1950104878140297E-2</v>
+        <v>6.2326777162831099E-3</v>
       </c>
       <c r="AC14" s="46">
-        <v>0.28153526970954401</v>
+        <v>0.274176408076514</v>
       </c>
       <c r="AD14" s="46">
-        <v>0.274176408076514</v>
+        <v>0.28263759638393998</v>
       </c>
       <c r="AE14" s="46">
-        <v>0.28263759638393998</v>
+        <v>0.305870496346687</v>
       </c>
       <c r="AF14" s="46">
-        <v>0.305870496346687</v>
+        <v>0.26369593709043199</v>
       </c>
       <c r="AG14" s="46">
+        <v>0.27311773623041902</v>
+      </c>
+      <c r="AH14" s="46">
+        <v>0.289338800615069</v>
+      </c>
+      <c r="AI14" s="46">
+        <v>0.27311773623041902</v>
+      </c>
+      <c r="AJ14" s="46">
+        <v>-1.6221064384649798E-2</v>
+      </c>
+      <c r="AK14" s="46">
         <v>0.26369593709043199</v>
       </c>
-      <c r="AH14" s="46">
-        <v>0.305870496346687</v>
-      </c>
-      <c r="AI14" s="46">
-        <v>0.26369593709043199</v>
-      </c>
-      <c r="AJ14" s="46">
-        <v>-4.21745592562544E-2</v>
-      </c>
-      <c r="AK14" s="46">
-        <v>0.289943724002936</v>
-      </c>
       <c r="AL14" s="46">
-        <v>0.26369593709043199</v>
+        <v>0.27311773623041902</v>
       </c>
       <c r="AM14" s="46">
-        <v>-2.62477869125037E-2</v>
+        <v>9.4217991399869194E-3</v>
       </c>
       <c r="AN14" s="46">
-        <v>5.5809128630705397E-2</v>
+        <v>4.5696068012752403E-2</v>
       </c>
       <c r="AO14" s="46">
-        <v>4.5696068012752403E-2</v>
+        <v>3.9351236373305003E-2</v>
       </c>
       <c r="AP14" s="46">
-        <v>3.9351236373305003E-2</v>
+        <v>2.4943310657596401E-2</v>
       </c>
       <c r="AQ14" s="46">
-        <v>2.4943310657596401E-2</v>
+        <v>3.9318479685452198E-2</v>
       </c>
       <c r="AR14" s="46">
+        <v>3.6129358261748401E-2</v>
+      </c>
+      <c r="AS14" s="46">
+        <v>6.5863659661711899E-2</v>
+      </c>
+      <c r="AT14" s="46">
+        <v>3.6129358261748401E-2</v>
+      </c>
+      <c r="AU14" s="47">
+        <v>-2.9734301399963602E-2</v>
+      </c>
+      <c r="AV14" s="46">
         <v>3.9318479685452198E-2</v>
       </c>
-      <c r="AS14" s="46">
-        <v>2.4943310657596401E-2</v>
-      </c>
-      <c r="AT14" s="46">
-        <v>3.9318479685452198E-2</v>
-      </c>
-      <c r="AU14" s="47">
-        <v>1.4375169027855799E-2</v>
-      </c>
-      <c r="AV14" s="46">
-        <v>4.5020797651088802E-2</v>
-      </c>
       <c r="AW14" s="46">
-        <v>3.9318479685452198E-2</v>
+        <v>3.6129358261748401E-2</v>
       </c>
       <c r="AX14" s="47">
-        <v>-5.7023179656366498E-3</v>
+        <v>-3.1891214237038E-3</v>
       </c>
       <c r="AY14" s="46">
-        <v>0.38319502074688799</v>
+        <v>0.475823591923486</v>
       </c>
       <c r="AZ14" s="46">
-        <v>0.475823591923486</v>
+        <v>0.471151289550651</v>
       </c>
       <c r="BA14" s="46">
-        <v>0.471151289550651</v>
+        <v>0.49256739732930199</v>
       </c>
       <c r="BB14" s="46">
-        <v>0.49256739732930199</v>
+        <v>0.50642201834862399</v>
       </c>
       <c r="BC14" s="46">
+        <v>0.49494694290045499</v>
+      </c>
+      <c r="BD14" s="46">
+        <v>0.47462839569451598</v>
+      </c>
+      <c r="BE14" s="46">
+        <v>0.49494694290045499</v>
+      </c>
+      <c r="BF14" s="46">
+        <v>2.0318547205939098E-2</v>
+      </c>
+      <c r="BG14" s="46">
         <v>0.50642201834862399</v>
       </c>
-      <c r="BD14" s="46">
-        <v>0.49256739732930199</v>
-      </c>
-      <c r="BE14" s="46">
-        <v>0.50642201834862399</v>
-      </c>
-      <c r="BF14" s="46">
-        <v>1.38546210193218E-2</v>
-      </c>
-      <c r="BG14" s="46">
-        <v>0.49253731343283602</v>
-      </c>
       <c r="BH14" s="46">
-        <v>0.50642201834862399</v>
+        <v>0.49494694290045499</v>
       </c>
       <c r="BI14" s="46">
-        <v>1.3884704915788099E-2</v>
+        <v>-1.14750754481691E-2</v>
       </c>
       <c r="BJ14" s="46">
-        <v>0.27946058091286302</v>
+        <v>0.204303931987248</v>
       </c>
       <c r="BK14" s="46">
+        <v>0.20685987769210301</v>
+      </c>
+      <c r="BL14" s="46">
+        <v>0.176618795666415</v>
+      </c>
+      <c r="BM14" s="46">
+        <v>0.190563564875491</v>
+      </c>
+      <c r="BN14" s="46">
+        <v>0.19580596260737701</v>
+      </c>
+      <c r="BO14" s="46">
+        <v>0.17016914402870301</v>
+      </c>
+      <c r="BP14" s="46">
+        <v>0.19580596260737701</v>
+      </c>
+      <c r="BQ14" s="47">
+        <v>2.5636818578674201E-2</v>
+      </c>
+      <c r="BR14" s="46">
+        <v>0.190563564875491</v>
+      </c>
+      <c r="BS14" s="46">
+        <v>0.19580596260737701</v>
+      </c>
+      <c r="BT14" s="47">
+        <v>5.24239773188598E-3</v>
+      </c>
+      <c r="BU14" s="46">
         <v>0.204303931987248</v>
       </c>
-      <c r="BL14" s="46">
+      <c r="BV14" s="46">
         <v>0.20685987769210301</v>
       </c>
-      <c r="BM14" s="46">
+      <c r="BW14" s="46">
         <v>0.176618795666415</v>
       </c>
-      <c r="BN14" s="46">
+      <c r="BX14" s="46">
         <v>0.190563564875491</v>
       </c>
-      <c r="BO14" s="46">
-        <v>0.176618795666415</v>
-      </c>
-      <c r="BP14" s="46">
+      <c r="BY14" s="46">
+        <v>0.19580596260737701</v>
+      </c>
+      <c r="BZ14" s="46">
+        <v>0.17016914402870301</v>
+      </c>
+      <c r="CA14" s="46">
+        <v>0.19580596260737701</v>
+      </c>
+      <c r="CB14" s="47">
+        <v>5.24239773188598E-3</v>
+      </c>
+      <c r="CC14" s="46">
         <v>0.190563564875491</v>
       </c>
-      <c r="BQ14" s="47">
-        <v>1.39447692090768E-2</v>
-      </c>
-      <c r="BR14" s="46">
-        <v>0.17249816491313899</v>
-      </c>
-      <c r="BS14" s="46">
-        <v>0.190563564875491</v>
-      </c>
-      <c r="BT14" s="47">
-        <v>1.8065399962352301E-2</v>
-      </c>
-      <c r="BU14" s="46">
-        <v>0.27946058091286302</v>
-      </c>
-      <c r="BV14" s="46">
-        <v>0.204303931987248</v>
-      </c>
-      <c r="BW14" s="46">
-        <v>0.20685987769210301</v>
-      </c>
-      <c r="BX14" s="46">
-        <v>0.176618795666415</v>
-      </c>
-      <c r="BY14" s="46">
-        <v>0.190563564875491</v>
-      </c>
-      <c r="BZ14" s="46">
-        <v>0.176618795666415</v>
-      </c>
-      <c r="CA14" s="46">
-        <v>0.190563564875491</v>
-      </c>
-      <c r="CB14" s="47">
-        <v>1.39447692090768E-2</v>
-      </c>
-      <c r="CC14" s="46">
-        <v>0.17249816491313899</v>
-      </c>
       <c r="CD14" s="46">
-        <v>0.190563564875491</v>
+        <v>0.19580596260737701</v>
       </c>
       <c r="CE14" s="47">
-        <v>1.8065399962352301E-2</v>
+        <v>5.24239773188598E-3</v>
       </c>
       <c r="CF14" s="46">
         <v>0</v>
@@ -4401,217 +4402,217 @@
         <v>91</v>
       </c>
       <c r="M15" s="44">
-        <v>3.0956134924987399E-2</v>
+        <v>5.14643993792578E-2</v>
       </c>
       <c r="N15" s="45">
-        <v>2.40138382286047E-2</v>
+        <v>2.2893158683816001E-2</v>
       </c>
       <c r="O15" s="45">
-        <v>6.9422966963826301E-3</v>
+        <v>2.8571240695441799E-2</v>
       </c>
       <c r="P15" s="45">
-        <v>-7.4392900262299499E-3</v>
+        <v>-5.1020542360398803E-2</v>
       </c>
       <c r="Q15" s="45">
-        <v>-2.35168448987574E-2</v>
+        <v>-4.4385701885898997E-4</v>
       </c>
       <c r="R15" s="46">
-        <v>0.36448801742919401</v>
+        <v>0.35100698725852902</v>
       </c>
       <c r="S15" s="46">
-        <v>0.35100698725852902</v>
+        <v>0.35317611259033899</v>
       </c>
       <c r="T15" s="46">
-        <v>0.35317611259033899</v>
+        <v>0.33813202247190999</v>
       </c>
       <c r="U15" s="46">
-        <v>0.33813202247190999</v>
+        <v>0.36908815739689699</v>
       </c>
       <c r="V15" s="46">
+        <v>0.39797864225781798</v>
+      </c>
+      <c r="W15" s="46">
+        <v>0.34651424287856097</v>
+      </c>
+      <c r="X15" s="46">
+        <v>0.39797864225781798</v>
+      </c>
+      <c r="Y15" s="46">
+        <v>5.14643993792578E-2</v>
+      </c>
+      <c r="Z15" s="46">
         <v>0.36908815739689699</v>
       </c>
-      <c r="W15" s="46">
-        <v>0.33813202247190999</v>
-      </c>
-      <c r="X15" s="46">
-        <v>0.36908815739689699</v>
-      </c>
-      <c r="Y15" s="46">
-        <v>3.0956134924987399E-2</v>
-      </c>
-      <c r="Z15" s="46">
-        <v>0.36971046770601301</v>
-      </c>
       <c r="AA15" s="46">
-        <v>0.36908815739689699</v>
+        <v>0.39797864225781798</v>
       </c>
       <c r="AB15" s="46">
-        <v>-6.2231030911585905E-4</v>
+        <v>2.8890484860920999E-2</v>
       </c>
       <c r="AC15" s="46">
-        <v>0.3</v>
+        <v>0.30004110152075603</v>
       </c>
       <c r="AD15" s="46">
-        <v>0.30004110152075603</v>
+        <v>0.28756181057436297</v>
       </c>
       <c r="AE15" s="46">
-        <v>0.28756181057436297</v>
+        <v>0.27545646067415702</v>
       </c>
       <c r="AF15" s="46">
-        <v>0.27545646067415702</v>
+        <v>0.299470298902762</v>
       </c>
       <c r="AG15" s="46">
+        <v>0.31693363844393602</v>
+      </c>
+      <c r="AH15" s="46">
+        <v>0.29404047976011999</v>
+      </c>
+      <c r="AI15" s="46">
+        <v>0.31693363844393602</v>
+      </c>
+      <c r="AJ15" s="46">
+        <v>2.2893158683816001E-2</v>
+      </c>
+      <c r="AK15" s="46">
         <v>0.299470298902762</v>
       </c>
-      <c r="AH15" s="46">
-        <v>0.27545646067415702</v>
-      </c>
-      <c r="AI15" s="46">
-        <v>0.299470298902762</v>
-      </c>
-      <c r="AJ15" s="46">
-        <v>2.40138382286047E-2</v>
-      </c>
-      <c r="AK15" s="46">
-        <v>0.30493689680772101</v>
-      </c>
       <c r="AL15" s="46">
-        <v>0.299470298902762</v>
+        <v>0.31693363844393602</v>
       </c>
       <c r="AM15" s="46">
-        <v>-5.4665979049588502E-3</v>
+        <v>1.7463339541173899E-2</v>
       </c>
       <c r="AN15" s="46">
-        <v>6.4488017429193897E-2</v>
+        <v>5.0965885737772297E-2</v>
       </c>
       <c r="AO15" s="46">
-        <v>5.0965885737772297E-2</v>
+        <v>6.5614302015975706E-2</v>
       </c>
       <c r="AP15" s="46">
-        <v>6.5614302015975706E-2</v>
+        <v>6.2675561797752799E-2</v>
       </c>
       <c r="AQ15" s="46">
-        <v>6.2675561797752799E-2</v>
+        <v>6.9617858494135404E-2</v>
       </c>
       <c r="AR15" s="46">
+        <v>8.1045003813882494E-2</v>
+      </c>
+      <c r="AS15" s="46">
+        <v>5.2473763118440798E-2</v>
+      </c>
+      <c r="AT15" s="46">
+        <v>8.1045003813882494E-2</v>
+      </c>
+      <c r="AU15" s="46">
+        <v>2.8571240695441799E-2</v>
+      </c>
+      <c r="AV15" s="46">
         <v>6.9617858494135404E-2</v>
       </c>
-      <c r="AS15" s="46">
-        <v>6.2675561797752799E-2</v>
-      </c>
-      <c r="AT15" s="46">
-        <v>6.9617858494135404E-2</v>
-      </c>
-      <c r="AU15" s="46">
-        <v>6.9422966963826301E-3</v>
-      </c>
-      <c r="AV15" s="46">
-        <v>6.4773570898292498E-2</v>
-      </c>
       <c r="AW15" s="46">
-        <v>6.9617858494135404E-2</v>
+        <v>8.1045003813882494E-2</v>
       </c>
       <c r="AX15" s="46">
-        <v>4.8442875958429497E-3</v>
+        <v>1.14271453197471E-2</v>
       </c>
       <c r="AY15" s="46">
-        <v>0.491067538126362</v>
+        <v>0.49177969584874598</v>
       </c>
       <c r="AZ15" s="46">
-        <v>0.49177969584874598</v>
+        <v>0.48269303917839501</v>
       </c>
       <c r="BA15" s="46">
-        <v>0.48269303917839501</v>
+        <v>0.465063202247191</v>
       </c>
       <c r="BB15" s="46">
-        <v>0.465063202247191</v>
+        <v>0.45762391222096099</v>
       </c>
       <c r="BC15" s="46">
+        <v>0.43211289092296001</v>
+      </c>
+      <c r="BD15" s="46">
+        <v>0.483133433283358</v>
+      </c>
+      <c r="BE15" s="46">
+        <v>0.43211289092296001</v>
+      </c>
+      <c r="BF15" s="47">
+        <v>-5.1020542360398803E-2</v>
+      </c>
+      <c r="BG15" s="46">
         <v>0.45762391222096099</v>
       </c>
-      <c r="BD15" s="46">
-        <v>0.465063202247191</v>
-      </c>
-      <c r="BE15" s="46">
-        <v>0.45762391222096099</v>
-      </c>
-      <c r="BF15" s="47">
-        <v>-7.4392900262299499E-3</v>
-      </c>
-      <c r="BG15" s="46">
-        <v>0.456570155902004</v>
-      </c>
       <c r="BH15" s="46">
-        <v>0.45762391222096099</v>
+        <v>0.43211289092296001</v>
       </c>
       <c r="BI15" s="47">
-        <v>1.0537563189565999E-3</v>
+        <v>-2.55110212980015E-2</v>
       </c>
       <c r="BJ15" s="46">
-        <v>0.14444444444444399</v>
+        <v>0.157213316892725</v>
       </c>
       <c r="BK15" s="46">
+        <v>0.164130848231267</v>
+      </c>
+      <c r="BL15" s="46">
+        <v>0.19680477528089901</v>
+      </c>
+      <c r="BM15" s="46">
+        <v>0.17328793038214199</v>
+      </c>
+      <c r="BN15" s="46">
+        <v>0.169908466819222</v>
+      </c>
+      <c r="BO15" s="46">
+        <v>0.17035232383808099</v>
+      </c>
+      <c r="BP15" s="46">
+        <v>0.169908466819222</v>
+      </c>
+      <c r="BQ15" s="46">
+        <v>-4.4385701885898997E-4</v>
+      </c>
+      <c r="BR15" s="46">
+        <v>0.17328793038214199</v>
+      </c>
+      <c r="BS15" s="46">
+        <v>0.169908466819222</v>
+      </c>
+      <c r="BT15" s="47">
+        <v>-3.3794635629195401E-3</v>
+      </c>
+      <c r="BU15" s="46">
         <v>0.157213316892725</v>
       </c>
-      <c r="BL15" s="46">
+      <c r="BV15" s="46">
         <v>0.164130848231267</v>
       </c>
-      <c r="BM15" s="46">
-        <v>0.19680477528089901</v>
-      </c>
-      <c r="BN15" s="46">
+      <c r="BW15" s="46">
+        <v>0.17169943820224701</v>
+      </c>
+      <c r="BX15" s="46">
         <v>0.17328793038214199</v>
       </c>
-      <c r="BO15" s="46">
-        <v>0.19680477528089901</v>
-      </c>
-      <c r="BP15" s="46">
+      <c r="BY15" s="46">
+        <v>0.169908466819222</v>
+      </c>
+      <c r="BZ15" s="46">
+        <v>0.17035232383808099</v>
+      </c>
+      <c r="CA15" s="46">
+        <v>0.169908466819222</v>
+      </c>
+      <c r="CB15" s="47">
+        <v>-3.3794635629195401E-3</v>
+      </c>
+      <c r="CC15" s="46">
         <v>0.17328793038214199</v>
       </c>
-      <c r="BQ15" s="46">
-        <v>-2.35168448987574E-2</v>
-      </c>
-      <c r="BR15" s="46">
-        <v>0.17371937639198201</v>
-      </c>
-      <c r="BS15" s="46">
-        <v>0.17328793038214199</v>
-      </c>
-      <c r="BT15" s="47">
-        <v>-4.3144600984065801E-4</v>
-      </c>
-      <c r="BU15" s="46">
-        <v>0.14444444444444399</v>
-      </c>
-      <c r="BV15" s="46">
-        <v>0.157213316892725</v>
-      </c>
-      <c r="BW15" s="46">
-        <v>0.164130848231267</v>
-      </c>
-      <c r="BX15" s="46">
-        <v>0.17169943820224701</v>
-      </c>
-      <c r="BY15" s="46">
-        <v>0.17328793038214199</v>
-      </c>
-      <c r="BZ15" s="46">
-        <v>0.17169943820224701</v>
-      </c>
-      <c r="CA15" s="46">
-        <v>0.17328793038214199</v>
-      </c>
-      <c r="CB15" s="47">
-        <v>1.5884921798943201E-3</v>
-      </c>
-      <c r="CC15" s="46">
-        <v>0.17371937639198201</v>
-      </c>
       <c r="CD15" s="46">
-        <v>0.17328793038214199</v>
+        <v>0.169908466819222</v>
       </c>
       <c r="CE15" s="47">
-        <v>-4.3144600984065801E-4</v>
+        <v>-3.3794635629195401E-3</v>
       </c>
       <c r="CF15" s="46">
         <v>0</v>
@@ -4620,22 +4621,22 @@
         <v>0</v>
       </c>
       <c r="CH15" s="46">
-        <v>0</v>
+        <v>2.5105337078651702E-2</v>
       </c>
       <c r="CI15" s="46">
-        <v>2.5105337078651702E-2</v>
+        <v>0</v>
       </c>
       <c r="CJ15" s="46">
         <v>0</v>
       </c>
       <c r="CK15" s="46">
-        <v>2.5105337078651702E-2</v>
+        <v>0</v>
       </c>
       <c r="CL15" s="46">
         <v>0</v>
       </c>
       <c r="CM15" s="47">
-        <v>-2.5105337078651702E-2</v>
+        <v>0</v>
       </c>
       <c r="CN15" s="46">
         <v>0</v>
@@ -4685,217 +4686,217 @@
         <v>91</v>
       </c>
       <c r="M16" s="44">
-        <v>-2.3381311654927499E-3</v>
+        <v>1.32762611619074E-2</v>
       </c>
       <c r="N16" s="45">
-        <v>8.6952587766919703E-3</v>
+        <v>1.07586279116952E-2</v>
       </c>
       <c r="O16" s="45">
-        <v>-1.1033389942184699E-2</v>
+        <v>2.51763325021218E-3</v>
       </c>
       <c r="P16" s="45">
-        <v>-7.3421912265560496E-2</v>
+        <v>-3.9810021227531599E-2</v>
       </c>
       <c r="Q16" s="45">
-        <v>7.5760043431053206E-2</v>
+        <v>2.6533760065624301E-2</v>
       </c>
       <c r="R16" s="46">
-        <v>0.41892233746521601</v>
+        <v>0.42701698513800401</v>
       </c>
       <c r="S16" s="46">
-        <v>0.42701698513800401</v>
+        <v>0.39176592439150698</v>
       </c>
       <c r="T16" s="46">
-        <v>0.39176592439150698</v>
+        <v>0.39478827361563501</v>
       </c>
       <c r="U16" s="46">
-        <v>0.39478827361563501</v>
+        <v>0.39245014245014198</v>
       </c>
       <c r="V16" s="46">
+        <v>0.404013377926421</v>
+      </c>
+      <c r="W16" s="46">
+        <v>0.390737116764514</v>
+      </c>
+      <c r="X16" s="46">
+        <v>0.404013377926421</v>
+      </c>
+      <c r="Y16" s="46">
+        <v>1.32762611619074E-2</v>
+      </c>
+      <c r="Z16" s="46">
         <v>0.39245014245014198</v>
       </c>
-      <c r="W16" s="46">
-        <v>0.39478827361563501</v>
-      </c>
-      <c r="X16" s="46">
-        <v>0.39245014245014198</v>
-      </c>
-      <c r="Y16" s="46">
-        <v>-2.3381311654927499E-3</v>
-      </c>
-      <c r="Z16" s="46">
-        <v>0.37278525868178602</v>
-      </c>
       <c r="AA16" s="46">
-        <v>0.39245014245014198</v>
+        <v>0.404013377926421</v>
       </c>
       <c r="AB16" s="46">
-        <v>1.9664883768356501E-2</v>
+        <v>1.1563235476279E-2</v>
       </c>
       <c r="AC16" s="46">
-        <v>0.334176574753352</v>
+        <v>0.33678343949044598</v>
       </c>
       <c r="AD16" s="46">
-        <v>0.33678343949044598</v>
+        <v>0.31330916623511101</v>
       </c>
       <c r="AE16" s="46">
-        <v>0.31330916623511101</v>
+        <v>0.310749185667752</v>
       </c>
       <c r="AF16" s="46">
-        <v>0.310749185667752</v>
+        <v>0.31944444444444398</v>
       </c>
       <c r="AG16" s="46">
+        <v>0.32876254180601999</v>
+      </c>
+      <c r="AH16" s="46">
+        <v>0.31800391389432497</v>
+      </c>
+      <c r="AI16" s="46">
+        <v>0.32876254180601999</v>
+      </c>
+      <c r="AJ16" s="46">
+        <v>1.07586279116952E-2</v>
+      </c>
+      <c r="AK16" s="46">
         <v>0.31944444444444398</v>
       </c>
-      <c r="AH16" s="46">
-        <v>0.310749185667752</v>
-      </c>
-      <c r="AI16" s="46">
-        <v>0.31944444444444398</v>
-      </c>
-      <c r="AJ16" s="46">
-        <v>8.6952587766919703E-3</v>
-      </c>
-      <c r="AK16" s="46">
-        <v>0.30297661233168</v>
-      </c>
       <c r="AL16" s="46">
-        <v>0.31944444444444398</v>
+        <v>0.32876254180601999</v>
       </c>
       <c r="AM16" s="46">
-        <v>1.6467832112764799E-2</v>
+        <v>9.3180973615756297E-3</v>
       </c>
       <c r="AN16" s="46">
-        <v>8.4745762711864403E-2</v>
+        <v>9.0233545647558394E-2</v>
       </c>
       <c r="AO16" s="46">
-        <v>9.0233545647558394E-2</v>
+        <v>7.8456758156395606E-2</v>
       </c>
       <c r="AP16" s="46">
-        <v>7.8456758156395606E-2</v>
+        <v>8.4039087947882701E-2</v>
       </c>
       <c r="AQ16" s="46">
-        <v>8.4039087947882701E-2</v>
+        <v>7.3005698005698005E-2</v>
       </c>
       <c r="AR16" s="46">
+        <v>7.5250836120401302E-2</v>
+      </c>
+      <c r="AS16" s="46">
+        <v>7.2733202870189195E-2</v>
+      </c>
+      <c r="AT16" s="46">
+        <v>7.5250836120401302E-2</v>
+      </c>
+      <c r="AU16" s="47">
+        <v>2.51763325021218E-3</v>
+      </c>
+      <c r="AV16" s="46">
         <v>7.3005698005698005E-2</v>
       </c>
-      <c r="AS16" s="46">
-        <v>8.4039087947882701E-2</v>
-      </c>
-      <c r="AT16" s="46">
-        <v>7.3005698005698005E-2</v>
-      </c>
-      <c r="AU16" s="47">
-        <v>-1.1033389942184699E-2</v>
-      </c>
-      <c r="AV16" s="46">
-        <v>6.9808646350106293E-2</v>
-      </c>
       <c r="AW16" s="46">
-        <v>7.3005698005698005E-2</v>
+        <v>7.5250836120401302E-2</v>
       </c>
       <c r="AX16" s="47">
-        <v>3.1970516555917001E-3</v>
+        <v>2.24513811470334E-3</v>
       </c>
       <c r="AY16" s="46">
-        <v>0.45130280799392902</v>
+        <v>0.42170912951167699</v>
       </c>
       <c r="AZ16" s="46">
-        <v>0.42170912951167699</v>
+        <v>0.45157949249093698</v>
       </c>
       <c r="BA16" s="46">
-        <v>0.45157949249093698</v>
+        <v>0.47263843648208498</v>
       </c>
       <c r="BB16" s="46">
-        <v>0.47263843648208498</v>
+        <v>0.39921652421652398</v>
       </c>
       <c r="BC16" s="46">
+        <v>0.393979933110368</v>
+      </c>
+      <c r="BD16" s="46">
+        <v>0.43378995433790002</v>
+      </c>
+      <c r="BE16" s="46">
+        <v>0.393979933110368</v>
+      </c>
+      <c r="BF16" s="47">
+        <v>-3.9810021227531599E-2</v>
+      </c>
+      <c r="BG16" s="46">
         <v>0.39921652421652398</v>
       </c>
-      <c r="BD16" s="46">
-        <v>0.47263843648208498</v>
-      </c>
-      <c r="BE16" s="46">
-        <v>0.39921652421652398</v>
-      </c>
-      <c r="BF16" s="47">
-        <v>-7.3421912265560496E-2</v>
-      </c>
-      <c r="BG16" s="46">
-        <v>0.421686746987952</v>
-      </c>
       <c r="BH16" s="46">
-        <v>0.39921652421652398</v>
+        <v>0.393979933110368</v>
       </c>
       <c r="BI16" s="46">
-        <v>-2.24702227714276E-2</v>
+        <v>-5.2365911061563204E-3</v>
       </c>
       <c r="BJ16" s="46">
-        <v>0.12977485454085499</v>
+        <v>0.15127388535031799</v>
       </c>
       <c r="BK16" s="46">
+        <v>0.15665458311755601</v>
+      </c>
+      <c r="BL16" s="46">
+        <v>0.13257328990228001</v>
+      </c>
+      <c r="BM16" s="46">
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="BN16" s="46">
+        <v>0.202006688963211</v>
+      </c>
+      <c r="BO16" s="46">
+        <v>0.17547292889758601</v>
+      </c>
+      <c r="BP16" s="46">
+        <v>0.202006688963211</v>
+      </c>
+      <c r="BQ16" s="46">
+        <v>2.6533760065624301E-2</v>
+      </c>
+      <c r="BR16" s="46">
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="BS16" s="46">
+        <v>0.202006688963211</v>
+      </c>
+      <c r="BT16" s="46">
+        <v>-6.3266443701226497E-3</v>
+      </c>
+      <c r="BU16" s="46">
         <v>0.15127388535031799</v>
       </c>
-      <c r="BL16" s="46">
+      <c r="BV16" s="46">
         <v>0.15665458311755601</v>
       </c>
-      <c r="BM16" s="46">
+      <c r="BW16" s="46">
         <v>0.13257328990228001</v>
       </c>
-      <c r="BN16" s="46">
+      <c r="BX16" s="46">
         <v>0.20833333333333301</v>
       </c>
-      <c r="BO16" s="46">
-        <v>0.13257328990228001</v>
-      </c>
-      <c r="BP16" s="46">
+      <c r="BY16" s="46">
+        <v>0.202006688963211</v>
+      </c>
+      <c r="BZ16" s="46">
+        <v>0.17547292889758601</v>
+      </c>
+      <c r="CA16" s="46">
+        <v>0.202006688963211</v>
+      </c>
+      <c r="CB16" s="46">
+        <v>-6.3266443701226497E-3</v>
+      </c>
+      <c r="CC16" s="46">
         <v>0.20833333333333301</v>
       </c>
-      <c r="BQ16" s="46">
-        <v>7.5760043431053206E-2</v>
-      </c>
-      <c r="BR16" s="46">
-        <v>0.205527994330262</v>
-      </c>
-      <c r="BS16" s="46">
-        <v>0.20833333333333301</v>
-      </c>
-      <c r="BT16" s="46">
-        <v>2.8053390030711202E-3</v>
-      </c>
-      <c r="BU16" s="46">
-        <v>0.12977485454085499</v>
-      </c>
-      <c r="BV16" s="46">
-        <v>0.15127388535031799</v>
-      </c>
-      <c r="BW16" s="46">
-        <v>0.15665458311755601</v>
-      </c>
-      <c r="BX16" s="46">
-        <v>0.13257328990228001</v>
-      </c>
-      <c r="BY16" s="46">
-        <v>0.20833333333333301</v>
-      </c>
-      <c r="BZ16" s="46">
-        <v>0.13257328990228001</v>
-      </c>
-      <c r="CA16" s="46">
-        <v>0.20833333333333301</v>
-      </c>
-      <c r="CB16" s="46">
-        <v>7.5760043431053206E-2</v>
-      </c>
-      <c r="CC16" s="46">
-        <v>0.205527994330262</v>
-      </c>
       <c r="CD16" s="46">
-        <v>0.20833333333333301</v>
+        <v>0.202006688963211</v>
       </c>
       <c r="CE16" s="46">
-        <v>2.8053390030711202E-3</v>
+        <v>-6.3266443701226497E-3</v>
       </c>
       <c r="CF16" s="46">
         <v>0</v>
@@ -4969,250 +4970,250 @@
         <v>35</v>
       </c>
       <c r="M17" s="44">
-        <v>-1.1165519506899401E-3</v>
+        <v>5.9689599120060797E-5</v>
       </c>
       <c r="N17" s="45">
-        <v>5.5354750301979698E-3</v>
+        <v>-1.68923498422804E-3</v>
       </c>
       <c r="O17" s="45">
-        <v>-6.6520269808878797E-3</v>
+        <v>1.74892458334813E-3</v>
       </c>
       <c r="P17" s="45">
-        <v>1.7866240609120902E-2</v>
+        <v>1.95401849485939E-2</v>
       </c>
       <c r="Q17" s="45">
-        <v>-1.6749688658430899E-2</v>
+        <v>-1.9599874547713898E-2</v>
       </c>
       <c r="R17" s="46">
-        <v>0.36753933803581101</v>
+        <v>0.35560344827586199</v>
       </c>
       <c r="S17" s="46">
-        <v>0.35560344827586199</v>
+        <v>0.36121428571428599</v>
       </c>
       <c r="T17" s="46">
-        <v>0.36121428571428599</v>
+        <v>0.35476455320726702</v>
       </c>
       <c r="U17" s="46">
-        <v>0.35476455320726702</v>
+        <v>0.35364800125657703</v>
       </c>
       <c r="V17" s="46">
+        <v>0.35829268292682898</v>
+      </c>
+      <c r="W17" s="46">
+        <v>0.35823299332770903</v>
+      </c>
+      <c r="X17" s="46">
+        <v>0.35829268292682898</v>
+      </c>
+      <c r="Y17" s="46">
+        <v>5.9689599120060797E-5</v>
+      </c>
+      <c r="Z17" s="46">
         <v>0.35364800125657703</v>
       </c>
-      <c r="W17" s="46">
-        <v>0.35476455320726702</v>
-      </c>
-      <c r="X17" s="46">
-        <v>0.35364800125657703</v>
-      </c>
-      <c r="Y17" s="46">
-        <v>-1.1165519506899401E-3</v>
-      </c>
-      <c r="Z17" s="46">
-        <v>0.35948975647468101</v>
-      </c>
       <c r="AA17" s="46">
-        <v>0.35364800125657703</v>
+        <v>0.35829268292682898</v>
       </c>
       <c r="AB17" s="46">
-        <v>-5.8417552181037101E-3</v>
+        <v>4.6446816702518396E-3</v>
       </c>
       <c r="AC17" s="46">
-        <v>0.22951709169831799</v>
+        <v>0.22844827586206901</v>
       </c>
       <c r="AD17" s="46">
-        <v>0.22844827586206901</v>
+        <v>0.22885714285714301</v>
       </c>
       <c r="AE17" s="46">
-        <v>0.22885714285714301</v>
+        <v>0.2293659621802</v>
       </c>
       <c r="AF17" s="46">
-        <v>0.2293659621802</v>
+        <v>0.234901437210398</v>
       </c>
       <c r="AG17" s="46">
+        <v>0.23406504065040701</v>
+      </c>
+      <c r="AH17" s="46">
+        <v>0.235754275634635</v>
+      </c>
+      <c r="AI17" s="46">
+        <v>0.23406504065040701</v>
+      </c>
+      <c r="AJ17" s="46">
+        <v>-1.68923498422804E-3</v>
+      </c>
+      <c r="AK17" s="46">
         <v>0.234901437210398</v>
       </c>
-      <c r="AH17" s="46">
-        <v>0.2293659621802</v>
-      </c>
-      <c r="AI17" s="46">
-        <v>0.234901437210398</v>
-      </c>
-      <c r="AJ17" s="46">
-        <v>5.5354750301979698E-3</v>
-      </c>
-      <c r="AK17" s="46">
-        <v>0.23270197139543899</v>
-      </c>
       <c r="AL17" s="46">
-        <v>0.234901437210398</v>
+        <v>0.23406504065040701</v>
       </c>
       <c r="AM17" s="46">
-        <v>2.19946581495944E-3</v>
+        <v>-8.3639655999168095E-4</v>
       </c>
       <c r="AN17" s="46">
-        <v>0.13802224633749299</v>
+        <v>0.12715517241379301</v>
       </c>
       <c r="AO17" s="46">
-        <v>0.12715517241379301</v>
+        <v>0.13235714285714301</v>
       </c>
       <c r="AP17" s="46">
-        <v>0.13235714285714301</v>
+        <v>0.12539859102706699</v>
       </c>
       <c r="AQ17" s="46">
-        <v>0.12539859102706699</v>
+        <v>0.118746564046179</v>
       </c>
       <c r="AR17" s="46">
+        <v>0.12422764227642299</v>
+      </c>
+      <c r="AS17" s="46">
+        <v>0.122478717693075</v>
+      </c>
+      <c r="AT17" s="46">
+        <v>0.12422764227642299</v>
+      </c>
+      <c r="AU17" s="47">
+        <v>1.74892458334813E-3</v>
+      </c>
+      <c r="AV17" s="46">
         <v>0.118746564046179</v>
       </c>
-      <c r="AS17" s="46">
-        <v>0.12539859102706699</v>
-      </c>
-      <c r="AT17" s="46">
-        <v>0.118746564046179</v>
-      </c>
-      <c r="AU17" s="47">
-        <v>-6.6520269808878797E-3</v>
-      </c>
-      <c r="AV17" s="46">
-        <v>0.12678778507924199</v>
-      </c>
       <c r="AW17" s="46">
-        <v>0.118746564046179</v>
+        <v>0.12422764227642299</v>
       </c>
       <c r="AX17" s="46">
-        <v>-8.0412210330631506E-3</v>
+        <v>5.4810782302435303E-3</v>
       </c>
       <c r="AY17" s="46">
-        <v>0.32175800325556198</v>
+        <v>0.33548850574712602</v>
       </c>
       <c r="AZ17" s="46">
-        <v>0.33548850574712602</v>
+        <v>0.310428571428571</v>
       </c>
       <c r="BA17" s="46">
-        <v>0.310428571428571</v>
+        <v>0.310493140526511</v>
       </c>
       <c r="BB17" s="46">
-        <v>0.310493140526511</v>
+        <v>0.32835938113563201</v>
       </c>
       <c r="BC17" s="46">
+        <v>0.32447154471544698</v>
+      </c>
+      <c r="BD17" s="46">
+        <v>0.30493135976685298</v>
+      </c>
+      <c r="BE17" s="46">
+        <v>0.32447154471544698</v>
+      </c>
+      <c r="BF17" s="46">
+        <v>1.95401849485939E-2</v>
+      </c>
+      <c r="BG17" s="46">
         <v>0.32835938113563201</v>
       </c>
-      <c r="BD17" s="46">
-        <v>0.310493140526511</v>
-      </c>
-      <c r="BE17" s="46">
-        <v>0.32835938113563201</v>
-      </c>
-      <c r="BF17" s="46">
-        <v>1.7866240609120902E-2</v>
-      </c>
-      <c r="BG17" s="46">
-        <v>0.326014688828759</v>
-      </c>
       <c r="BH17" s="46">
-        <v>0.32835938113563201</v>
+        <v>0.32447154471544698</v>
       </c>
       <c r="BI17" s="46">
-        <v>2.3446923068726798E-3</v>
+        <v>-3.8878364201847E-3</v>
       </c>
       <c r="BJ17" s="46">
-        <v>0.31070265870862701</v>
+        <v>0.30890804597701099</v>
       </c>
       <c r="BK17" s="46">
-        <v>0.30890804597701099</v>
+        <v>0.32835714285714301</v>
       </c>
       <c r="BL17" s="46">
-        <v>0.32835714285714301</v>
+        <v>0.33474230626622198</v>
       </c>
       <c r="BM17" s="46">
-        <v>0.33474230626622198</v>
+        <v>0.31799261760779102</v>
       </c>
       <c r="BN17" s="46">
+        <v>0.31723577235772399</v>
+      </c>
+      <c r="BO17" s="46">
+        <v>0.33683564690543799</v>
+      </c>
+      <c r="BP17" s="46">
+        <v>0.31723577235772399</v>
+      </c>
+      <c r="BQ17" s="47">
+        <v>-1.9599874547713898E-2</v>
+      </c>
+      <c r="BR17" s="46">
         <v>0.31799261760779102</v>
       </c>
-      <c r="BO17" s="46">
-        <v>0.33474230626622198</v>
-      </c>
-      <c r="BP17" s="46">
-        <v>0.31799261760779102</v>
-      </c>
-      <c r="BQ17" s="47">
-        <v>-1.6749688658430899E-2</v>
-      </c>
-      <c r="BR17" s="46">
-        <v>0.31449555469655999</v>
-      </c>
       <c r="BS17" s="46">
-        <v>0.31799261760779102</v>
+        <v>0.31723577235772399</v>
       </c>
       <c r="BT17" s="47">
-        <v>3.4970629112310902E-3</v>
+        <v>-7.5684525006719495E-4</v>
       </c>
       <c r="BU17" s="46">
-        <v>0.30256375474769398</v>
+        <v>0.30172413793103398</v>
       </c>
       <c r="BV17" s="46">
-        <v>0.30172413793103398</v>
+        <v>0.316857142857143</v>
       </c>
       <c r="BW17" s="46">
-        <v>0.316857142857143</v>
+        <v>0.31931776047460098</v>
       </c>
       <c r="BX17" s="46">
-        <v>0.31931776047460098</v>
+        <v>0.30927511191392398</v>
       </c>
       <c r="BY17" s="46">
+        <v>0.30666666666666698</v>
+      </c>
+      <c r="BZ17" s="46">
+        <v>0.32318429327402398</v>
+      </c>
+      <c r="CA17" s="46">
+        <v>0.30666666666666698</v>
+      </c>
+      <c r="CB17" s="47">
+        <v>-2.6084452472577798E-3</v>
+      </c>
+      <c r="CC17" s="46">
         <v>0.30927511191392398</v>
       </c>
-      <c r="BZ17" s="46">
-        <v>0.31931776047460098</v>
-      </c>
-      <c r="CA17" s="46">
-        <v>0.30927511191392398</v>
-      </c>
-      <c r="CB17" s="47">
-        <v>-1.0042648560677001E-2</v>
-      </c>
-      <c r="CC17" s="46">
-        <v>0.29887901043679899</v>
-      </c>
       <c r="CD17" s="46">
-        <v>0.30927511191392398</v>
+        <v>0.30666666666666698</v>
       </c>
       <c r="CE17" s="47">
-        <v>1.0396101477125099E-2</v>
+        <v>-2.6084452472577798E-3</v>
       </c>
       <c r="CF17" s="46">
-        <v>8.1389039609332595E-3</v>
+        <v>7.1839080459770097E-3</v>
       </c>
       <c r="CG17" s="46">
-        <v>7.1839080459770097E-3</v>
+        <v>1.15E-2</v>
       </c>
       <c r="CH17" s="46">
-        <v>1.15E-2</v>
+        <v>1.54245457916203E-2</v>
       </c>
       <c r="CI17" s="46">
-        <v>1.54245457916203E-2</v>
+        <v>8.7175056938663294E-3</v>
       </c>
       <c r="CJ17" s="46">
+        <v>1.05691056910569E-2</v>
+      </c>
+      <c r="CK17" s="46">
+        <v>1.3651353631413499E-2</v>
+      </c>
+      <c r="CL17" s="46">
+        <v>1.05691056910569E-2</v>
+      </c>
+      <c r="CM17" s="46">
+        <v>1.8515999971905801E-3</v>
+      </c>
+      <c r="CN17" s="46">
         <v>8.7175056938663294E-3</v>
       </c>
-      <c r="CK17" s="46">
-        <v>1.54245457916203E-2</v>
-      </c>
-      <c r="CL17" s="46">
-        <v>8.7175056938663294E-3</v>
-      </c>
-      <c r="CM17" s="46">
-        <v>-6.7070400977539898E-3</v>
-      </c>
-      <c r="CN17" s="46">
-        <v>1.56165442597603E-2</v>
-      </c>
       <c r="CO17" s="46">
-        <v>8.7175056938663294E-3</v>
+        <v>1.05691056910569E-2</v>
       </c>
       <c r="CP17" s="46">
-        <v>-6.8990385658940102E-3</v>
+        <v>1.8515999971905801E-3</v>
       </c>
     </row>
     <row r="18" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5253,250 +5254,250 @@
         <v>91</v>
       </c>
       <c r="M18" s="44">
-        <v>6.5544447008488698E-3</v>
+        <v>7.7065750586513505E-4</v>
       </c>
       <c r="N18" s="45">
-        <v>1.6200253216663899E-5</v>
+        <v>1.3739361486040399E-2</v>
       </c>
       <c r="O18" s="45">
-        <v>6.5382444476321799E-3</v>
+        <v>-1.29687039801753E-2</v>
       </c>
       <c r="P18" s="45">
-        <v>-7.3659698011064303E-3</v>
+        <v>-9.1794633517158497E-3</v>
       </c>
       <c r="Q18" s="45">
-        <v>8.1152510025755996E-4</v>
+        <v>8.4088058458506899E-3</v>
       </c>
       <c r="R18" s="46">
-        <v>0.366097801115852</v>
+        <v>0.343337234576158</v>
       </c>
       <c r="S18" s="46">
-        <v>0.343337234576158</v>
+        <v>0.37744542639172102</v>
       </c>
       <c r="T18" s="46">
-        <v>0.37744542639172102</v>
+        <v>0.32654708520179399</v>
       </c>
       <c r="U18" s="46">
-        <v>0.32654708520179399</v>
+        <v>0.33310152990264302</v>
       </c>
       <c r="V18" s="46">
+        <v>0.33722826086956498</v>
+      </c>
+      <c r="W18" s="46">
+        <v>0.33645760336370001</v>
+      </c>
+      <c r="X18" s="46">
+        <v>0.33722826086956498</v>
+      </c>
+      <c r="Y18" s="46">
+        <v>7.7065750586513505E-4</v>
+      </c>
+      <c r="Z18" s="46">
         <v>0.33310152990264302</v>
       </c>
-      <c r="W18" s="46">
-        <v>0.32654708520179399</v>
-      </c>
-      <c r="X18" s="46">
-        <v>0.33310152990264302</v>
-      </c>
-      <c r="Y18" s="46">
-        <v>6.5544447008488698E-3</v>
-      </c>
-      <c r="Z18" s="46">
-        <v>0.33086627417998299</v>
-      </c>
       <c r="AA18" s="46">
-        <v>0.33310152990264302</v>
+        <v>0.33722826086956498</v>
       </c>
       <c r="AB18" s="46">
-        <v>2.2352557226594199E-3</v>
+        <v>4.1267309669226204E-3</v>
       </c>
       <c r="AC18" s="46">
-        <v>0.124466688546111</v>
+        <v>0.14002675137936799</v>
       </c>
       <c r="AD18" s="46">
-        <v>0.14002675137936799</v>
+        <v>0.115492106654581</v>
       </c>
       <c r="AE18" s="46">
-        <v>0.115492106654581</v>
+        <v>0.12941704035874399</v>
       </c>
       <c r="AF18" s="46">
-        <v>0.12941704035874399</v>
+        <v>0.12943324061196099</v>
       </c>
       <c r="AG18" s="46">
+        <v>0.13523550724637701</v>
+      </c>
+      <c r="AH18" s="46">
+        <v>0.121496145760336</v>
+      </c>
+      <c r="AI18" s="46">
+        <v>0.13523550724637701</v>
+      </c>
+      <c r="AJ18" s="46">
+        <v>1.3739361486040399E-2</v>
+      </c>
+      <c r="AK18" s="46">
         <v>0.12943324061196099</v>
       </c>
-      <c r="AH18" s="46">
-        <v>0.12941704035874399</v>
-      </c>
-      <c r="AI18" s="46">
-        <v>0.12943324061196099</v>
-      </c>
-      <c r="AJ18" s="46">
-        <v>1.6200253216663899E-5</v>
-      </c>
-      <c r="AK18" s="46">
-        <v>0.13406223717409599</v>
-      </c>
       <c r="AL18" s="46">
-        <v>0.12943324061196099</v>
+        <v>0.13523550724637701</v>
       </c>
       <c r="AM18" s="46">
-        <v>-4.6289965621348099E-3</v>
+        <v>5.8022666344157399E-3</v>
       </c>
       <c r="AN18" s="46">
-        <v>0.24163111256974101</v>
+        <v>0.20331048319678999</v>
       </c>
       <c r="AO18" s="46">
-        <v>0.20331048319678999</v>
+        <v>0.26195331973713998</v>
       </c>
       <c r="AP18" s="46">
-        <v>0.26195331973713998</v>
+        <v>0.197130044843049</v>
       </c>
       <c r="AQ18" s="46">
-        <v>0.197130044843049</v>
+        <v>0.20366828929068201</v>
       </c>
       <c r="AR18" s="46">
+        <v>0.201992753623188</v>
+      </c>
+      <c r="AS18" s="46">
+        <v>0.21496145760336399</v>
+      </c>
+      <c r="AT18" s="46">
+        <v>0.201992753623188</v>
+      </c>
+      <c r="AU18" s="46">
+        <v>-1.29687039801753E-2</v>
+      </c>
+      <c r="AV18" s="46">
         <v>0.20366828929068201</v>
       </c>
-      <c r="AS18" s="46">
-        <v>0.197130044843049</v>
-      </c>
-      <c r="AT18" s="46">
-        <v>0.20366828929068201</v>
-      </c>
-      <c r="AU18" s="46">
-        <v>6.5382444476321799E-3</v>
-      </c>
-      <c r="AV18" s="46">
-        <v>0.196804037005887</v>
-      </c>
       <c r="AW18" s="46">
-        <v>0.20366828929068201</v>
+        <v>0.201992753623188</v>
       </c>
       <c r="AX18" s="47">
-        <v>6.8642522847941999E-3</v>
+        <v>-1.67553566749309E-3</v>
       </c>
       <c r="AY18" s="46">
-        <v>0.22604200853298301</v>
+        <v>0.229142283899014</v>
       </c>
       <c r="AZ18" s="46">
-        <v>0.229142283899014</v>
+        <v>0.212780421481985</v>
       </c>
       <c r="BA18" s="46">
-        <v>0.212780421481985</v>
+        <v>0.25067264573990999</v>
       </c>
       <c r="BB18" s="46">
-        <v>0.25067264573990999</v>
+        <v>0.24330667593880401</v>
       </c>
       <c r="BC18" s="46">
+        <v>0.242572463768116</v>
+      </c>
+      <c r="BD18" s="46">
+        <v>0.25175192711983202</v>
+      </c>
+      <c r="BE18" s="46">
+        <v>0.242572463768116</v>
+      </c>
+      <c r="BF18" s="47">
+        <v>-9.1794633517158497E-3</v>
+      </c>
+      <c r="BG18" s="46">
         <v>0.24330667593880401</v>
       </c>
-      <c r="BD18" s="46">
-        <v>0.25067264573990999</v>
-      </c>
-      <c r="BE18" s="46">
-        <v>0.24330667593880401</v>
-      </c>
-      <c r="BF18" s="47">
-        <v>-7.3659698011064303E-3</v>
-      </c>
-      <c r="BG18" s="46">
-        <v>0.24423885618166499</v>
-      </c>
       <c r="BH18" s="46">
-        <v>0.24330667593880401</v>
+        <v>0.242572463768116</v>
       </c>
       <c r="BI18" s="47">
-        <v>-9.3218024286137501E-4</v>
+        <v>-7.3421217068794797E-4</v>
       </c>
       <c r="BJ18" s="46">
-        <v>0.407860190351165</v>
+        <v>0.42752048152482902</v>
       </c>
       <c r="BK18" s="46">
-        <v>0.42752048152482902</v>
+        <v>0.40977415212629398</v>
       </c>
       <c r="BL18" s="46">
-        <v>0.40977415212629398</v>
+        <v>0.42278026905829602</v>
       </c>
       <c r="BM18" s="46">
-        <v>0.42278026905829602</v>
+        <v>0.42359179415855402</v>
       </c>
       <c r="BN18" s="46">
+        <v>0.42019927536231899</v>
+      </c>
+      <c r="BO18" s="46">
+        <v>0.41179046951646803</v>
+      </c>
+      <c r="BP18" s="46">
+        <v>0.42019927536231899</v>
+      </c>
+      <c r="BQ18" s="46">
+        <v>8.4088058458506899E-3</v>
+      </c>
+      <c r="BR18" s="46">
         <v>0.42359179415855402</v>
       </c>
-      <c r="BO18" s="46">
-        <v>0.42278026905829602</v>
-      </c>
-      <c r="BP18" s="46">
-        <v>0.42359179415855402</v>
-      </c>
-      <c r="BQ18" s="46">
-        <v>8.1152510025755996E-4</v>
-      </c>
-      <c r="BR18" s="46">
-        <v>0.42489486963835199</v>
-      </c>
       <c r="BS18" s="46">
-        <v>0.42359179415855402</v>
+        <v>0.42019927536231899</v>
       </c>
       <c r="BT18" s="46">
-        <v>-1.30307547979802E-3</v>
+        <v>-3.3925187962346999E-3</v>
       </c>
       <c r="BU18" s="46">
-        <v>0.38004594683295001</v>
+        <v>0.38246112690185602</v>
       </c>
       <c r="BV18" s="46">
-        <v>0.38246112690185602</v>
+        <v>0.376614547926581</v>
       </c>
       <c r="BW18" s="46">
-        <v>0.376614547926581</v>
+        <v>0.385291479820628</v>
       </c>
       <c r="BX18" s="46">
-        <v>0.385291479820628</v>
+        <v>0.39082058414464499</v>
       </c>
       <c r="BY18" s="46">
+        <v>0.386865942028985</v>
+      </c>
+      <c r="BZ18" s="46">
+        <v>0.37675192711983202</v>
+      </c>
+      <c r="CA18" s="46">
+        <v>0.386865942028985</v>
+      </c>
+      <c r="CB18" s="47">
+        <v>-3.9546421156598198E-3</v>
+      </c>
+      <c r="CC18" s="46">
         <v>0.39082058414464499</v>
       </c>
-      <c r="BZ18" s="46">
-        <v>0.385291479820628</v>
-      </c>
-      <c r="CA18" s="46">
-        <v>0.39082058414464499</v>
-      </c>
-      <c r="CB18" s="47">
-        <v>5.5291043240175402E-3</v>
-      </c>
-      <c r="CC18" s="46">
-        <v>0.39184188393608099</v>
-      </c>
       <c r="CD18" s="46">
-        <v>0.39082058414464499</v>
+        <v>0.386865942028985</v>
       </c>
       <c r="CE18" s="46">
-        <v>-1.0212997914353899E-3</v>
+        <v>-3.9546421156598198E-3</v>
       </c>
       <c r="CF18" s="46">
-        <v>2.7814243518214599E-2</v>
+        <v>4.5059354622972697E-2</v>
       </c>
       <c r="CG18" s="46">
-        <v>4.5059354622972697E-2</v>
+        <v>3.3159604199712998E-2</v>
       </c>
       <c r="CH18" s="46">
-        <v>3.3159604199712998E-2</v>
+        <v>3.7488789237668199E-2</v>
       </c>
       <c r="CI18" s="46">
-        <v>3.7488789237668199E-2</v>
+        <v>3.2771210013908203E-2</v>
       </c>
       <c r="CJ18" s="46">
+        <v>3.3333333333333298E-2</v>
+      </c>
+      <c r="CK18" s="46">
+        <v>3.5038542396636299E-2</v>
+      </c>
+      <c r="CL18" s="46">
+        <v>3.3333333333333298E-2</v>
+      </c>
+      <c r="CM18" s="46">
+        <v>5.6212331942512999E-4</v>
+      </c>
+      <c r="CN18" s="46">
         <v>3.2771210013908203E-2</v>
       </c>
-      <c r="CK18" s="46">
-        <v>3.7488789237668199E-2</v>
-      </c>
-      <c r="CL18" s="46">
-        <v>3.2771210013908203E-2</v>
-      </c>
-      <c r="CM18" s="46">
-        <v>-4.7175792237599597E-3</v>
-      </c>
-      <c r="CN18" s="46">
-        <v>3.3052985702270797E-2</v>
-      </c>
       <c r="CO18" s="46">
-        <v>3.2771210013908203E-2</v>
+        <v>3.3333333333333298E-2</v>
       </c>
       <c r="CP18" s="46">
-        <v>-2.8177568836261502E-4</v>
+        <v>5.6212331942512999E-4</v>
       </c>
     </row>
     <row r="19" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5537,217 +5538,217 @@
         <v>35</v>
       </c>
       <c r="M19" s="44">
-        <v>7.0561324149275198E-2</v>
+        <v>0.12719211497890301</v>
       </c>
       <c r="N19" s="45">
-        <v>0.138166957952092</v>
+        <v>0.12719211497890301</v>
       </c>
       <c r="O19" s="45">
-        <v>-6.7605633802816895E-2</v>
+        <v>0</v>
       </c>
       <c r="P19" s="45">
-        <v>1.7466844864809299E-2</v>
+        <v>-0.12719211497890301</v>
       </c>
       <c r="Q19" s="45">
-        <v>-8.8028169014084501E-2</v>
+        <v>0</v>
       </c>
       <c r="R19" s="46">
-        <v>0.351874244256348</v>
+        <v>0.39332247557003303</v>
       </c>
       <c r="S19" s="46">
-        <v>0.39332247557003303</v>
+        <v>0.45781250000000001</v>
       </c>
       <c r="T19" s="46">
+        <v>0.51338028169014105</v>
+      </c>
+      <c r="U19" s="46">
+        <v>0.58394160583941601</v>
+      </c>
+      <c r="V19" s="46">
+        <v>0.59765625</v>
+      </c>
+      <c r="W19" s="46">
+        <v>0.47046413502109702</v>
+      </c>
+      <c r="X19" s="46">
+        <v>0.59765625</v>
+      </c>
+      <c r="Y19" s="46">
+        <v>0.12719211497890301</v>
+      </c>
+      <c r="Z19" s="46">
+        <v>0.58394160583941601</v>
+      </c>
+      <c r="AA19" s="46">
+        <v>0.59765625</v>
+      </c>
+      <c r="AB19" s="46">
+        <v>1.3714644160584001E-2</v>
+      </c>
+      <c r="AC19" s="46">
+        <v>0.27361563517915299</v>
+      </c>
+      <c r="AD19" s="46">
         <v>0.45781250000000001</v>
       </c>
-      <c r="U19" s="46">
-        <v>0.51338028169014105</v>
-      </c>
-      <c r="V19" s="46">
+      <c r="AE19" s="46">
+        <v>0.44577464788732402</v>
+      </c>
+      <c r="AF19" s="46">
         <v>0.58394160583941601</v>
       </c>
-      <c r="W19" s="46">
-        <v>0.51338028169014105</v>
-      </c>
-      <c r="X19" s="46">
+      <c r="AG19" s="46">
+        <v>0.59765625</v>
+      </c>
+      <c r="AH19" s="46">
+        <v>0.47046413502109702</v>
+      </c>
+      <c r="AI19" s="46">
+        <v>0.59765625</v>
+      </c>
+      <c r="AJ19" s="46">
+        <v>0.12719211497890301</v>
+      </c>
+      <c r="AK19" s="46">
         <v>0.58394160583941601</v>
       </c>
-      <c r="Y19" s="46">
-        <v>7.0561324149275198E-2</v>
-      </c>
-      <c r="Z19" s="46">
-        <v>0.51484375000000004</v>
-      </c>
-      <c r="AA19" s="46">
-        <v>0.58394160583941601</v>
-      </c>
-      <c r="AB19" s="46">
-        <v>6.9097855839415995E-2</v>
-      </c>
-      <c r="AC19" s="46">
-        <v>0.351874244256348</v>
-      </c>
-      <c r="AD19" s="46">
-        <v>0.27361563517915299</v>
-      </c>
-      <c r="AE19" s="46">
-        <v>0.45781250000000001</v>
-      </c>
-      <c r="AF19" s="46">
-        <v>0.44577464788732402</v>
-      </c>
-      <c r="AG19" s="46">
-        <v>0.58394160583941601</v>
-      </c>
-      <c r="AH19" s="46">
-        <v>0.44577464788732402</v>
-      </c>
-      <c r="AI19" s="46">
-        <v>0.58394160583941601</v>
-      </c>
-      <c r="AJ19" s="46">
-        <v>0.138166957952092</v>
-      </c>
-      <c r="AK19" s="46">
-        <v>0.41796875</v>
-      </c>
       <c r="AL19" s="46">
-        <v>0.58394160583941601</v>
+        <v>0.59765625</v>
       </c>
       <c r="AM19" s="46">
-        <v>0.16597285583941601</v>
+        <v>1.3714644160584001E-2</v>
       </c>
       <c r="AN19" s="46">
-        <v>0</v>
+        <v>0.119706840390879</v>
       </c>
       <c r="AO19" s="46">
-        <v>0.119706840390879</v>
+        <v>0</v>
       </c>
       <c r="AP19" s="46">
-        <v>0</v>
+        <v>6.7605633802816895E-2</v>
       </c>
       <c r="AQ19" s="46">
-        <v>6.7605633802816895E-2</v>
+        <v>0</v>
       </c>
       <c r="AR19" s="46">
         <v>0</v>
       </c>
       <c r="AS19" s="46">
-        <v>6.7605633802816895E-2</v>
+        <v>0</v>
       </c>
       <c r="AT19" s="46">
         <v>0</v>
       </c>
       <c r="AU19" s="46">
-        <v>-6.7605633802816895E-2</v>
+        <v>0</v>
       </c>
       <c r="AV19" s="46">
-        <v>9.6875000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="AW19" s="46">
         <v>0</v>
       </c>
       <c r="AX19" s="46">
-        <v>-9.6875000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="AY19" s="46">
-        <v>0.64812575574365205</v>
+        <v>0.51302931596091195</v>
       </c>
       <c r="AZ19" s="46">
-        <v>0.51302931596091195</v>
+        <v>0.54218750000000004</v>
       </c>
       <c r="BA19" s="46">
-        <v>0.54218750000000004</v>
+        <v>0.39859154929577501</v>
       </c>
       <c r="BB19" s="46">
-        <v>0.39859154929577501</v>
+        <v>0.41605839416058399</v>
       </c>
       <c r="BC19" s="46">
+        <v>0.40234375</v>
+      </c>
+      <c r="BD19" s="46">
+        <v>0.52953586497890304</v>
+      </c>
+      <c r="BE19" s="46">
+        <v>0.40234375</v>
+      </c>
+      <c r="BF19" s="47">
+        <v>-0.12719211497890301</v>
+      </c>
+      <c r="BG19" s="46">
         <v>0.41605839416058399</v>
       </c>
-      <c r="BD19" s="46">
-        <v>0.39859154929577501</v>
-      </c>
-      <c r="BE19" s="46">
-        <v>0.41605839416058399</v>
-      </c>
-      <c r="BF19" s="47">
-        <v>1.7466844864809299E-2</v>
-      </c>
-      <c r="BG19" s="46">
-        <v>0.39531250000000001</v>
-      </c>
       <c r="BH19" s="46">
-        <v>0.41605839416058399</v>
+        <v>0.40234375</v>
       </c>
       <c r="BI19" s="47">
-        <v>2.0745894160583901E-2</v>
+        <v>-1.37146441605839E-2</v>
       </c>
       <c r="BJ19" s="46">
-        <v>0</v>
+        <v>9.3648208469055402E-2</v>
       </c>
       <c r="BK19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BL19" s="46">
+        <v>8.8028169014084501E-2</v>
+      </c>
+      <c r="BM19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BP19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BQ19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BR19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BS19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BT19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BU19" s="46">
         <v>9.3648208469055402E-2</v>
       </c>
-      <c r="BL19" s="46">
-        <v>0</v>
-      </c>
-      <c r="BM19" s="46">
+      <c r="BV19" s="46">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="46">
         <v>8.8028169014084501E-2</v>
       </c>
-      <c r="BN19" s="46">
-        <v>0</v>
-      </c>
-      <c r="BO19" s="46">
-        <v>8.8028169014084501E-2</v>
-      </c>
-      <c r="BP19" s="46">
-        <v>0</v>
-      </c>
-      <c r="BQ19" s="46">
-        <v>-8.8028169014084501E-2</v>
-      </c>
-      <c r="BR19" s="46">
-        <v>8.984375E-2</v>
-      </c>
-      <c r="BS19" s="46">
-        <v>0</v>
-      </c>
-      <c r="BT19" s="46">
-        <v>-8.984375E-2</v>
-      </c>
-      <c r="BU19" s="46">
-        <v>0</v>
-      </c>
-      <c r="BV19" s="46">
-        <v>9.3648208469055402E-2</v>
-      </c>
-      <c r="BW19" s="46">
-        <v>0</v>
-      </c>
       <c r="BX19" s="46">
-        <v>8.8028169014084501E-2</v>
+        <v>0</v>
       </c>
       <c r="BY19" s="46">
         <v>0</v>
       </c>
       <c r="BZ19" s="46">
-        <v>8.8028169014084501E-2</v>
+        <v>0</v>
       </c>
       <c r="CA19" s="46">
         <v>0</v>
       </c>
       <c r="CB19" s="47">
-        <v>-8.8028169014084501E-2</v>
+        <v>0</v>
       </c>
       <c r="CC19" s="46">
-        <v>8.984375E-2</v>
+        <v>0</v>
       </c>
       <c r="CD19" s="46">
         <v>0</v>
       </c>
       <c r="CE19" s="46">
-        <v>-8.984375E-2</v>
+        <v>0</v>
       </c>
       <c r="CF19" s="46">
         <v>0</v>
@@ -5821,250 +5822,250 @@
         <v>35</v>
       </c>
       <c r="M20" s="44">
-        <v>-5.2672217778418897E-3</v>
+        <v>-6.3686642843089301E-3</v>
       </c>
       <c r="N20" s="45">
-        <v>-6.74933587481752E-3</v>
+        <v>-4.6793221713180002E-3</v>
       </c>
       <c r="O20" s="45">
-        <v>1.48211409697556E-3</v>
+        <v>-1.68934211299099E-3</v>
       </c>
       <c r="P20" s="45">
-        <v>9.3452241694169701E-4</v>
+        <v>2.8038076622011199E-4</v>
       </c>
       <c r="Q20" s="45">
-        <v>4.3326993609002096E-3</v>
+        <v>6.08828351808882E-3</v>
       </c>
       <c r="R20" s="46">
-        <v>0.46034574083883101</v>
+        <v>0.47572626242932298</v>
       </c>
       <c r="S20" s="46">
-        <v>0.47572626242932298</v>
+        <v>0.46475900657701003</v>
       </c>
       <c r="T20" s="46">
-        <v>0.46475900657701003</v>
+        <v>0.46767251572624502</v>
       </c>
       <c r="U20" s="46">
-        <v>0.46767251572624502</v>
+        <v>0.46240529394840302</v>
       </c>
       <c r="V20" s="46">
+        <v>0.46257456224745003</v>
+      </c>
+      <c r="W20" s="46">
+        <v>0.46894322653175902</v>
+      </c>
+      <c r="X20" s="46">
+        <v>0.46257456224745003</v>
+      </c>
+      <c r="Y20" s="46">
+        <v>-6.3686642843089301E-3</v>
+      </c>
+      <c r="Z20" s="46">
         <v>0.46240529394840302</v>
       </c>
-      <c r="W20" s="46">
-        <v>0.46767251572624502</v>
-      </c>
-      <c r="X20" s="46">
-        <v>0.46240529394840302</v>
-      </c>
-      <c r="Y20" s="46">
-        <v>-5.2672217778418897E-3</v>
-      </c>
-      <c r="Z20" s="46">
-        <v>0.46447880110025602</v>
-      </c>
       <c r="AA20" s="46">
-        <v>0.46240529394840302</v>
+        <v>0.46257456224745003</v>
       </c>
       <c r="AB20" s="46">
-        <v>-2.0735071518528901E-3</v>
+        <v>1.6926829904728699E-4</v>
       </c>
       <c r="AC20" s="46">
-        <v>0.34102181345403798</v>
+        <v>0.34772860206667999</v>
       </c>
       <c r="AD20" s="46">
-        <v>0.34772860206667999</v>
+        <v>0.34426229508196698</v>
       </c>
       <c r="AE20" s="46">
-        <v>0.34426229508196698</v>
+        <v>0.34342335524759998</v>
       </c>
       <c r="AF20" s="46">
-        <v>0.34342335524759998</v>
+        <v>0.33667401937278202</v>
       </c>
       <c r="AG20" s="46">
+        <v>0.339474696940543</v>
+      </c>
+      <c r="AH20" s="46">
+        <v>0.344154019111861</v>
+      </c>
+      <c r="AI20" s="46">
+        <v>0.339474696940543</v>
+      </c>
+      <c r="AJ20" s="46">
+        <v>-4.6793221713180002E-3</v>
+      </c>
+      <c r="AK20" s="46">
         <v>0.33667401937278202</v>
       </c>
-      <c r="AH20" s="46">
-        <v>0.34342335524759998</v>
-      </c>
-      <c r="AI20" s="46">
-        <v>0.33667401937278202</v>
-      </c>
-      <c r="AJ20" s="46">
-        <v>-6.74933587481752E-3</v>
-      </c>
-      <c r="AK20" s="46">
-        <v>0.33761737645831402</v>
-      </c>
       <c r="AL20" s="46">
-        <v>0.33667401937278202</v>
+        <v>0.339474696940543</v>
       </c>
       <c r="AM20" s="46">
-        <v>-9.4335708553139298E-4</v>
+        <v>2.80067756776042E-3</v>
       </c>
       <c r="AN20" s="46">
-        <v>0.119323927384793</v>
+        <v>0.12799766036264401</v>
       </c>
       <c r="AO20" s="46">
-        <v>0.12799766036264401</v>
+        <v>0.120496711495043</v>
       </c>
       <c r="AP20" s="46">
-        <v>0.120496711495043</v>
+        <v>0.124249160478645</v>
       </c>
       <c r="AQ20" s="46">
-        <v>0.124249160478645</v>
+        <v>0.125731274575621</v>
       </c>
       <c r="AR20" s="46">
+        <v>0.123099865306908</v>
+      </c>
+      <c r="AS20" s="46">
+        <v>0.124789207419899</v>
+      </c>
+      <c r="AT20" s="46">
+        <v>0.123099865306908</v>
+      </c>
+      <c r="AU20" s="46">
+        <v>-1.68934211299099E-3</v>
+      </c>
+      <c r="AV20" s="46">
         <v>0.125731274575621</v>
       </c>
-      <c r="AS20" s="46">
-        <v>0.124249160478645</v>
-      </c>
-      <c r="AT20" s="46">
-        <v>0.125731274575621</v>
-      </c>
-      <c r="AU20" s="46">
-        <v>1.48211409697556E-3</v>
-      </c>
-      <c r="AV20" s="46">
-        <v>0.126861424641943</v>
-      </c>
       <c r="AW20" s="46">
-        <v>0.125731274575621</v>
+        <v>0.123099865306908</v>
       </c>
       <c r="AX20" s="46">
-        <v>-1.1301500663215599E-3</v>
+        <v>-2.6314092687131402E-3</v>
       </c>
       <c r="AY20" s="46">
-        <v>0.442962392256946</v>
+        <v>0.42776369662702302</v>
       </c>
       <c r="AZ20" s="46">
-        <v>0.42776369662702302</v>
+        <v>0.42897810935505998</v>
       </c>
       <c r="BA20" s="46">
-        <v>0.42897810935505998</v>
+        <v>0.420375538003122</v>
       </c>
       <c r="BB20" s="46">
-        <v>0.420375538003122</v>
+        <v>0.42131006042006303</v>
       </c>
       <c r="BC20" s="46">
+        <v>0.41961708678083498</v>
+      </c>
+      <c r="BD20" s="46">
+        <v>0.41933670601461498</v>
+      </c>
+      <c r="BE20" s="46">
+        <v>0.41961708678083498</v>
+      </c>
+      <c r="BF20" s="47">
+        <v>2.8038076622011199E-4</v>
+      </c>
+      <c r="BG20" s="46">
         <v>0.42131006042006303</v>
       </c>
-      <c r="BD20" s="46">
-        <v>0.420375538003122</v>
-      </c>
-      <c r="BE20" s="46">
-        <v>0.42131006042006303</v>
-      </c>
-      <c r="BF20" s="47">
-        <v>9.3452241694169701E-4</v>
-      </c>
-      <c r="BG20" s="46">
-        <v>0.41809731575452902</v>
-      </c>
       <c r="BH20" s="46">
-        <v>0.42131006042006303</v>
+        <v>0.41961708678083498</v>
       </c>
       <c r="BI20" s="46">
-        <v>3.2127446655342302E-3</v>
+        <v>-1.69297363922821E-3</v>
       </c>
       <c r="BJ20" s="46">
-        <v>9.6691866904223003E-2</v>
+        <v>9.6510040943653702E-2</v>
       </c>
       <c r="BK20" s="46">
+        <v>0.10626288406793</v>
+      </c>
+      <c r="BL20" s="46">
+        <v>0.111951946270633</v>
+      </c>
+      <c r="BM20" s="46">
+        <v>0.116284645631534</v>
+      </c>
+      <c r="BN20" s="46">
+        <v>0.11780835097171399</v>
+      </c>
+      <c r="BO20" s="46">
+        <v>0.111720067453626</v>
+      </c>
+      <c r="BP20" s="46">
+        <v>0.11780835097171399</v>
+      </c>
+      <c r="BQ20" s="46">
+        <v>6.08828351808882E-3</v>
+      </c>
+      <c r="BR20" s="46">
+        <v>0.116284645631534</v>
+      </c>
+      <c r="BS20" s="46">
+        <v>0.11780835097171399</v>
+      </c>
+      <c r="BT20" s="47">
+        <v>1.52370534018094E-3</v>
+      </c>
+      <c r="BU20" s="46">
         <v>9.6510040943653702E-2</v>
       </c>
-      <c r="BL20" s="46">
-        <v>0.10626288406793</v>
-      </c>
-      <c r="BM20" s="46">
-        <v>0.111951946270633</v>
-      </c>
-      <c r="BN20" s="46">
-        <v>0.116284645631534</v>
-      </c>
-      <c r="BO20" s="46">
-        <v>0.111951946270633</v>
-      </c>
-      <c r="BP20" s="46">
-        <v>0.116284645631534</v>
-      </c>
-      <c r="BQ20" s="46">
-        <v>4.3326993609002096E-3</v>
-      </c>
-      <c r="BR20" s="46">
-        <v>0.117423883145215</v>
-      </c>
-      <c r="BS20" s="46">
-        <v>0.116284645631534</v>
-      </c>
-      <c r="BT20" s="47">
-        <v>-1.1392375136813199E-3</v>
-      </c>
-      <c r="BU20" s="46">
-        <v>9.6691866904223003E-2</v>
-      </c>
       <c r="BV20" s="46">
-        <v>9.6510040943653702E-2</v>
+        <v>9.8409737901246699E-2</v>
       </c>
       <c r="BW20" s="46">
-        <v>9.8409737901246699E-2</v>
+        <v>0.102066877926501</v>
       </c>
       <c r="BX20" s="46">
-        <v>0.102066877926501</v>
+        <v>0.10669415939388099</v>
       </c>
       <c r="BY20" s="46">
+        <v>0.108139311141043</v>
+      </c>
+      <c r="BZ20" s="46">
+        <v>0.10239835113359599</v>
+      </c>
+      <c r="CA20" s="46">
+        <v>0.108139311141043</v>
+      </c>
+      <c r="CB20" s="47">
+        <v>1.4451517471616401E-3</v>
+      </c>
+      <c r="CC20" s="46">
         <v>0.10669415939388099</v>
       </c>
-      <c r="BZ20" s="46">
-        <v>0.102066877926501</v>
-      </c>
-      <c r="CA20" s="46">
-        <v>0.10669415939388099</v>
-      </c>
-      <c r="CB20" s="47">
-        <v>4.62728146738077E-3</v>
-      </c>
-      <c r="CC20" s="46">
-        <v>0.10604192355117099</v>
-      </c>
       <c r="CD20" s="46">
-        <v>0.10669415939388099</v>
+        <v>0.108139311141043</v>
       </c>
       <c r="CE20" s="47">
-        <v>6.52235842709875E-4</v>
+        <v>1.4451517471616401E-3</v>
       </c>
       <c r="CF20" s="46">
         <v>0</v>
       </c>
       <c r="CG20" s="46">
-        <v>0</v>
+        <v>7.8531461666830303E-3</v>
       </c>
       <c r="CH20" s="46">
-        <v>7.8531461666830303E-3</v>
+        <v>9.8850683441328094E-3</v>
       </c>
       <c r="CI20" s="46">
-        <v>9.8850683441328094E-3</v>
+        <v>9.5904862376522508E-3</v>
       </c>
       <c r="CJ20" s="46">
+        <v>9.6690398306715393E-3</v>
+      </c>
+      <c r="CK20" s="46">
+        <v>9.3217163200299807E-3</v>
+      </c>
+      <c r="CL20" s="46">
+        <v>9.6690398306715393E-3</v>
+      </c>
+      <c r="CM20" s="47">
+        <v>7.8553593019292002E-5</v>
+      </c>
+      <c r="CN20" s="46">
         <v>9.5904862376522508E-3</v>
       </c>
-      <c r="CK20" s="46">
-        <v>9.8850683441328094E-3</v>
-      </c>
-      <c r="CL20" s="46">
-        <v>9.5904862376522508E-3</v>
-      </c>
-      <c r="CM20" s="47">
-        <v>-2.9458210648055998E-4</v>
-      </c>
-      <c r="CN20" s="46">
-        <v>1.13819595940434E-2</v>
-      </c>
       <c r="CO20" s="46">
-        <v>9.5904862376522508E-3</v>
+        <v>9.6690398306715393E-3</v>
       </c>
       <c r="CP20" s="47">
-        <v>-1.79147335639119E-3</v>
+        <v>7.8553593019292002E-5</v>
       </c>
     </row>
     <row r="21" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6105,217 +6106,217 @@
         <v>35</v>
       </c>
       <c r="M21" s="44">
-        <v>-6.0304671237463102E-2</v>
+        <v>2.4350977902890501E-2</v>
       </c>
       <c r="N21" s="45">
-        <v>-8.1893435424157408E-3</v>
+        <v>2.4691358024691398E-2</v>
       </c>
       <c r="O21" s="45">
-        <v>-5.21153276950473E-2</v>
+        <v>-3.4038012180087602E-4</v>
       </c>
       <c r="P21" s="45">
-        <v>-1.76257090314474E-3</v>
+        <v>-2.6604846276977401E-2</v>
       </c>
       <c r="Q21" s="45">
-        <v>6.2067242140607798E-2</v>
+        <v>2.2538683740869199E-3</v>
       </c>
       <c r="R21" s="46">
-        <v>0.41666666666666702</v>
+        <v>0.37149532710280397</v>
       </c>
       <c r="S21" s="46">
-        <v>0.37149532710280397</v>
+        <v>0.44190476190476202</v>
       </c>
       <c r="T21" s="46">
-        <v>0.44190476190476202</v>
+        <v>0.467320261437909</v>
       </c>
       <c r="U21" s="46">
-        <v>0.467320261437909</v>
+        <v>0.40701559020044498</v>
       </c>
       <c r="V21" s="46">
+        <v>0.40089418777943397</v>
+      </c>
+      <c r="W21" s="46">
+        <v>0.37654320987654299</v>
+      </c>
+      <c r="X21" s="46">
+        <v>0.40089418777943397</v>
+      </c>
+      <c r="Y21" s="46">
+        <v>2.4350977902890501E-2</v>
+      </c>
+      <c r="Z21" s="46">
         <v>0.40701559020044498</v>
       </c>
-      <c r="W21" s="46">
-        <v>0.467320261437909</v>
-      </c>
-      <c r="X21" s="46">
-        <v>0.40701559020044498</v>
-      </c>
-      <c r="Y21" s="46">
-        <v>-6.0304671237463102E-2</v>
-      </c>
-      <c r="Z21" s="46">
-        <v>0.445670159955874</v>
-      </c>
       <c r="AA21" s="46">
-        <v>0.40701559020044498</v>
+        <v>0.40089418777943397</v>
       </c>
       <c r="AB21" s="46">
-        <v>-3.8654569755428803E-2</v>
+        <v>-6.12140242101172E-3</v>
       </c>
       <c r="AC21" s="46">
-        <v>0.31054131054131101</v>
+        <v>0.28037383177570102</v>
       </c>
       <c r="AD21" s="46">
-        <v>0.28037383177570102</v>
+        <v>0.32507936507936502</v>
       </c>
       <c r="AE21" s="46">
-        <v>0.32507936507936502</v>
+        <v>0.35729847494553402</v>
       </c>
       <c r="AF21" s="46">
-        <v>0.35729847494553402</v>
+        <v>0.349109131403118</v>
       </c>
       <c r="AG21" s="46">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AH21" s="46">
+        <v>0.30864197530864201</v>
+      </c>
+      <c r="AI21" s="46">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AJ21" s="46">
+        <v>2.4691358024691398E-2</v>
+      </c>
+      <c r="AK21" s="46">
         <v>0.349109131403118</v>
       </c>
-      <c r="AH21" s="46">
-        <v>0.35729847494553402</v>
-      </c>
-      <c r="AI21" s="46">
-        <v>0.349109131403118</v>
-      </c>
-      <c r="AJ21" s="46">
-        <v>-8.1893435424157408E-3</v>
-      </c>
-      <c r="AK21" s="46">
-        <v>0.37727523441809202</v>
-      </c>
       <c r="AL21" s="46">
-        <v>0.349109131403118</v>
+        <v>0.33333333333333298</v>
       </c>
       <c r="AM21" s="46">
-        <v>-2.8166103014973499E-2</v>
+        <v>-1.5775798069784699E-2</v>
       </c>
       <c r="AN21" s="46">
-        <v>0.10612535612535599</v>
+        <v>9.11214953271028E-2</v>
       </c>
       <c r="AO21" s="46">
-        <v>9.11214953271028E-2</v>
+        <v>0.116825396825397</v>
       </c>
       <c r="AP21" s="46">
-        <v>0.116825396825397</v>
+        <v>0.110021786492375</v>
       </c>
       <c r="AQ21" s="46">
-        <v>0.110021786492375</v>
+        <v>5.7906458797327399E-2</v>
       </c>
       <c r="AR21" s="46">
+        <v>6.7560854446100396E-2</v>
+      </c>
+      <c r="AS21" s="46">
+        <v>6.7901234567901203E-2</v>
+      </c>
+      <c r="AT21" s="46">
+        <v>6.7560854446100396E-2</v>
+      </c>
+      <c r="AU21" s="46">
+        <v>-3.4038012180087602E-4</v>
+      </c>
+      <c r="AV21" s="46">
         <v>5.7906458797327399E-2</v>
       </c>
-      <c r="AS21" s="46">
-        <v>0.110021786492375</v>
-      </c>
-      <c r="AT21" s="46">
-        <v>5.7906458797327399E-2</v>
-      </c>
-      <c r="AU21" s="46">
-        <v>-5.21153276950473E-2</v>
-      </c>
-      <c r="AV21" s="46">
-        <v>6.8394925537782703E-2</v>
-      </c>
       <c r="AW21" s="46">
-        <v>5.7906458797327399E-2</v>
+        <v>6.7560854446100396E-2</v>
       </c>
       <c r="AX21" s="46">
-        <v>-1.04884667404553E-2</v>
+        <v>9.6543956487729603E-3</v>
       </c>
       <c r="AY21" s="46">
-        <v>0.37108262108262102</v>
+        <v>0.46962616822429898</v>
       </c>
       <c r="AZ21" s="46">
-        <v>0.46962616822429898</v>
+        <v>0.41714285714285698</v>
       </c>
       <c r="BA21" s="46">
-        <v>0.41714285714285698</v>
+        <v>0.34586056644880198</v>
       </c>
       <c r="BB21" s="46">
-        <v>0.34586056644880198</v>
+        <v>0.34409799554565701</v>
       </c>
       <c r="BC21" s="46">
+        <v>0.343765524093393</v>
+      </c>
+      <c r="BD21" s="46">
+        <v>0.37037037037037002</v>
+      </c>
+      <c r="BE21" s="46">
+        <v>0.343765524093393</v>
+      </c>
+      <c r="BF21" s="47">
+        <v>-2.6604846276977401E-2</v>
+      </c>
+      <c r="BG21" s="46">
         <v>0.34409799554565701</v>
       </c>
-      <c r="BD21" s="46">
-        <v>0.34586056644880198</v>
-      </c>
-      <c r="BE21" s="46">
-        <v>0.34409799554565701</v>
-      </c>
-      <c r="BF21" s="47">
-        <v>-1.76257090314474E-3</v>
-      </c>
-      <c r="BG21" s="46">
-        <v>0.32597904026475499</v>
-      </c>
       <c r="BH21" s="46">
-        <v>0.34409799554565701</v>
+        <v>0.343765524093393</v>
       </c>
       <c r="BI21" s="47">
-        <v>1.8118955280902498E-2</v>
+        <v>-3.3247145226406001E-4</v>
       </c>
       <c r="BJ21" s="46">
-        <v>0.21225071225071199</v>
+        <v>0.15887850467289699</v>
       </c>
       <c r="BK21" s="46">
+        <v>0.140952380952381</v>
+      </c>
+      <c r="BL21" s="46">
+        <v>0.18681917211328999</v>
+      </c>
+      <c r="BM21" s="46">
+        <v>0.24888641425389799</v>
+      </c>
+      <c r="BN21" s="46">
+        <v>0.25534028812717302</v>
+      </c>
+      <c r="BO21" s="46">
+        <v>0.25308641975308599</v>
+      </c>
+      <c r="BP21" s="46">
+        <v>0.25534028812717302</v>
+      </c>
+      <c r="BQ21" s="46">
+        <v>2.2538683740869199E-3</v>
+      </c>
+      <c r="BR21" s="46">
+        <v>0.24888641425389799</v>
+      </c>
+      <c r="BS21" s="46">
+        <v>0.25534028812717302</v>
+      </c>
+      <c r="BT21" s="47">
+        <v>6.4538738732758099E-3</v>
+      </c>
+      <c r="BU21" s="46">
         <v>0.15887850467289699</v>
       </c>
-      <c r="BL21" s="46">
+      <c r="BV21" s="46">
         <v>0.140952380952381</v>
       </c>
-      <c r="BM21" s="46">
+      <c r="BW21" s="46">
         <v>0.18681917211328999</v>
       </c>
-      <c r="BN21" s="46">
+      <c r="BX21" s="46">
         <v>0.24888641425389799</v>
       </c>
-      <c r="BO21" s="46">
-        <v>0.18681917211328999</v>
-      </c>
-      <c r="BP21" s="46">
+      <c r="BY21" s="46">
+        <v>0.25534028812717302</v>
+      </c>
+      <c r="BZ21" s="46">
+        <v>0.25308641975308599</v>
+      </c>
+      <c r="CA21" s="46">
+        <v>0.25534028812717302</v>
+      </c>
+      <c r="CB21" s="46">
+        <v>6.4538738732758099E-3</v>
+      </c>
+      <c r="CC21" s="46">
         <v>0.24888641425389799</v>
       </c>
-      <c r="BQ21" s="46">
-        <v>6.2067242140607798E-2</v>
-      </c>
-      <c r="BR21" s="46">
-        <v>0.22835079977937101</v>
-      </c>
-      <c r="BS21" s="46">
-        <v>0.24888641425389799</v>
-      </c>
-      <c r="BT21" s="47">
-        <v>2.0535614474526301E-2</v>
-      </c>
-      <c r="BU21" s="46">
-        <v>0.21225071225071199</v>
-      </c>
-      <c r="BV21" s="46">
-        <v>0.15887850467289699</v>
-      </c>
-      <c r="BW21" s="46">
-        <v>0.140952380952381</v>
-      </c>
-      <c r="BX21" s="46">
-        <v>0.18681917211328999</v>
-      </c>
-      <c r="BY21" s="46">
-        <v>0.24888641425389799</v>
-      </c>
-      <c r="BZ21" s="46">
-        <v>0.18681917211328999</v>
-      </c>
-      <c r="CA21" s="46">
-        <v>0.24888641425389799</v>
-      </c>
-      <c r="CB21" s="46">
-        <v>6.2067242140607798E-2</v>
-      </c>
-      <c r="CC21" s="46">
-        <v>0.22835079977937101</v>
-      </c>
       <c r="CD21" s="46">
-        <v>0.24888641425389799</v>
+        <v>0.25534028812717302</v>
       </c>
       <c r="CE21" s="47">
-        <v>2.0535614474526301E-2</v>
+        <v>6.4538738732758099E-3</v>
       </c>
       <c r="CF21" s="46">
         <v>0</v>
@@ -6605,83 +6606,76 @@
         <v>10</v>
       </c>
       <c r="B4" s="54">
-        <v>0.343542430432489</v>
+        <v>0.33758422899148</v>
       </c>
       <c r="C4" s="54">
+        <v>0.339650831985919</v>
+      </c>
+      <c r="D4" s="54">
+        <v>0.33915726677409402</v>
+      </c>
+      <c r="E4" s="54">
+        <v>0.33675168049224202</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0.34037882811116998</v>
+      </c>
+      <c r="G4" s="55">
+        <v>3.6271476189281299E-3</v>
+      </c>
+      <c r="H4" s="40">
         <v>0.33758422899148</v>
       </c>
-      <c r="D4" s="54">
-        <v>0.339650831985919</v>
-      </c>
-      <c r="E4" s="54">
-        <v>0.33818616907233601</v>
-      </c>
-      <c r="F4" s="54">
-        <v>0.33675168049224202</v>
-      </c>
-      <c r="G4" s="55">
-        <f>F4-E4</f>
-        <v>-1.4344885800939844E-3</v>
-      </c>
-      <c r="H4" s="40">
-        <v>0.343542430432489</v>
-      </c>
       <c r="I4" s="40">
-        <v>0.33675168049224202</v>
+        <v>0.34037882811116998</v>
       </c>
       <c r="J4" s="41">
-        <f>IFERROR(I4-H4,"")</f>
-        <v>-6.7907499402469762E-3</v>
+        <v>2.7945991196904299E-3</v>
       </c>
       <c r="K4" s="40">
-        <v>8.7694971658933196E-2</v>
+        <v>9.0152865177925007E-2</v>
       </c>
       <c r="L4" s="40">
-        <v>8.8678012769633802E-2</v>
+        <v>8.9686670207116306E-2</v>
       </c>
       <c r="M4" s="41">
-        <f>IFERROR(L4-K4,"")</f>
-        <v>9.830411107006054E-4</v>
+        <v>-4.6619497080874201E-4</v>
       </c>
       <c r="N4" s="40">
-        <v>0.39116083386317801</v>
+        <v>0.39154647212786098</v>
       </c>
       <c r="O4" s="40">
-        <v>0.38795664786575701</v>
+        <v>0.386496725084086</v>
       </c>
       <c r="P4" s="41">
-        <f>IFERROR(O4-N4,"")</f>
-        <v>-3.2041859974210052E-3</v>
+        <v>-5.04974704377531E-3</v>
       </c>
       <c r="Q4" s="40">
-        <v>0.17760176404540001</v>
+        <v>0.18071643370273399</v>
       </c>
       <c r="R4" s="40">
-        <v>0.186613658872367</v>
+        <v>0.183437776597628</v>
       </c>
       <c r="S4" s="41">
-        <f>IFERROR(R4-Q4,"")</f>
-        <v>9.0118948269669874E-3</v>
+        <v>2.7213428948935901E-3</v>
       </c>
       <c r="T4" s="40">
-        <v>0.166860567362455</v>
+        <v>0.17024697889402499</v>
       </c>
       <c r="U4" s="40">
-        <v>0.17595824933798801</v>
+        <v>0.17341122322534999</v>
       </c>
       <c r="V4" s="41">
-        <f>IFERROR(U4-T4,"")</f>
-        <v>9.0976819755330118E-3</v>
+        <v>3.16424433132501E-3</v>
       </c>
       <c r="W4" s="40">
-        <v>1.0741196682945301E-2</v>
+        <v>1.0469454808709699E-2</v>
       </c>
       <c r="X4" s="40">
-        <v>1.0655409534379E-2</v>
+        <v>1.0026553372278301E-2</v>
       </c>
       <c r="Y4" s="41">
-        <f>IFERROR(X4-W4,"")</f>
-        <v>-8.578714856630025E-5</v>
+        <v>-4.4290143643141601E-4</v>
       </c>
     </row>
   </sheetData>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="104">
   <si>
     <t>LMTD</t>
   </si>
@@ -301,9 +301,6 @@
     <t>NAMA PT</t>
   </si>
   <si>
-    <t>W4-Jul</t>
-  </si>
-  <si>
     <t>W4-Aug</t>
   </si>
   <si>
@@ -329,6 +326,15 @@
   </si>
   <si>
     <t>SEPT 2026</t>
+  </si>
+  <si>
+    <t>W3-Aug</t>
+  </si>
+  <si>
+    <t>W2-Sep</t>
+  </si>
+  <si>
+    <t>W3-Sep</t>
   </si>
 </sst>
 </file>
@@ -736,10 +742,6 @@
     <xf numFmtId="165" fontId="15" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="9" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -758,6 +760,10 @@
     <xf numFmtId="17" fontId="6" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,97 +1170,97 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="52" t="s">
+      <c r="R3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="52" t="s">
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="59"/>
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="52" t="s">
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
+      <c r="AK3" s="59"/>
+      <c r="AL3" s="59"/>
+      <c r="AM3" s="59"/>
+      <c r="AN3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="53"/>
-      <c r="AQ3" s="53"/>
-      <c r="AR3" s="53"/>
-      <c r="AS3" s="53"/>
-      <c r="AT3" s="53"/>
-      <c r="AU3" s="53"/>
-      <c r="AV3" s="53"/>
-      <c r="AW3" s="53"/>
-      <c r="AX3" s="53"/>
-      <c r="AY3" s="52" t="s">
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59"/>
+      <c r="AT3" s="59"/>
+      <c r="AU3" s="59"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="59"/>
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="AZ3" s="53"/>
-      <c r="BA3" s="53"/>
-      <c r="BB3" s="53"/>
-      <c r="BC3" s="53"/>
-      <c r="BD3" s="53"/>
-      <c r="BE3" s="53"/>
-      <c r="BF3" s="53"/>
-      <c r="BG3" s="53"/>
-      <c r="BH3" s="53"/>
-      <c r="BI3" s="53"/>
-      <c r="BJ3" s="52" t="s">
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="59"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="59"/>
+      <c r="BJ3" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="BK3" s="53"/>
-      <c r="BL3" s="53"/>
-      <c r="BM3" s="53"/>
-      <c r="BN3" s="53"/>
-      <c r="BO3" s="53"/>
-      <c r="BP3" s="53"/>
-      <c r="BQ3" s="53"/>
-      <c r="BR3" s="53"/>
-      <c r="BS3" s="53"/>
-      <c r="BT3" s="53"/>
-      <c r="BU3" s="52" t="s">
+      <c r="BK3" s="59"/>
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="59"/>
+      <c r="BO3" s="59"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="BV3" s="53"/>
-      <c r="BW3" s="53"/>
-      <c r="BX3" s="53"/>
-      <c r="BY3" s="53"/>
-      <c r="BZ3" s="53"/>
-      <c r="CA3" s="53"/>
-      <c r="CB3" s="53"/>
-      <c r="CC3" s="53"/>
-      <c r="CD3" s="53"/>
-      <c r="CE3" s="53"/>
-      <c r="CF3" s="52" t="s">
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59"/>
+      <c r="BX3" s="59"/>
+      <c r="BY3" s="59"/>
+      <c r="BZ3" s="59"/>
+      <c r="CA3" s="59"/>
+      <c r="CB3" s="59"/>
+      <c r="CC3" s="59"/>
+      <c r="CD3" s="59"/>
+      <c r="CE3" s="59"/>
+      <c r="CF3" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="CG3" s="53"/>
-      <c r="CH3" s="53"/>
-      <c r="CI3" s="53"/>
-      <c r="CJ3" s="53"/>
-      <c r="CK3" s="53"/>
-      <c r="CL3" s="53"/>
-      <c r="CM3" s="53"/>
-      <c r="CN3" s="53"/>
-      <c r="CO3" s="53"/>
-      <c r="CP3" s="53"/>
+      <c r="CG3" s="59"/>
+      <c r="CH3" s="59"/>
+      <c r="CI3" s="59"/>
+      <c r="CJ3" s="59"/>
+      <c r="CK3" s="59"/>
+      <c r="CL3" s="59"/>
+      <c r="CM3" s="59"/>
+      <c r="CN3" s="59"/>
+      <c r="CO3" s="59"/>
+      <c r="CP3" s="59"/>
     </row>
     <row r="4" spans="1:94" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
@@ -1308,20 +1314,20 @@
       <c r="Q4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="57" t="s">
+      <c r="R4" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="S4" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="S4" s="58" t="s">
+      <c r="T4" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="T4" s="58" t="s">
+      <c r="U4" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="U4" s="57" t="s">
+      <c r="V4" s="57" t="s">
         <v>100</v>
-      </c>
-      <c r="V4" s="59" t="s">
-        <v>101</v>
       </c>
       <c r="W4" s="13" t="s">
         <v>0</v>
@@ -1342,19 +1348,19 @@
         <v>27</v>
       </c>
       <c r="AC4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="AD4" s="9" t="s">
+      <c r="AE4" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="14" t="s">
+      <c r="AF4" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="14" t="s">
+      <c r="AG4" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="AG4" s="14" t="s">
-        <v>101</v>
       </c>
       <c r="AH4" s="9" t="s">
         <v>0</v>
@@ -1375,19 +1381,19 @@
         <v>4</v>
       </c>
       <c r="AN4" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO4" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AO4" s="16" t="s">
+      <c r="AP4" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AP4" s="15" t="s">
+      <c r="AQ4" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="AQ4" s="15" t="s">
+      <c r="AR4" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="AR4" s="16" t="s">
-        <v>101</v>
       </c>
       <c r="AS4" s="16" t="s">
         <v>0</v>
@@ -1408,19 +1414,19 @@
         <v>27</v>
       </c>
       <c r="AY4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ4" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="AZ4" s="18" t="s">
+      <c r="BA4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="BA4" s="17" t="s">
+      <c r="BB4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BB4" s="17" t="s">
+      <c r="BC4" s="18" t="s">
         <v>100</v>
-      </c>
-      <c r="BC4" s="18" t="s">
-        <v>101</v>
       </c>
       <c r="BD4" s="18" t="s">
         <v>0</v>
@@ -1441,19 +1447,19 @@
         <v>27</v>
       </c>
       <c r="BJ4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="BK4" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="BK4" s="20" t="s">
+      <c r="BL4" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="BL4" s="19" t="s">
+      <c r="BM4" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="BM4" s="19" t="s">
+      <c r="BN4" s="20" t="s">
         <v>100</v>
-      </c>
-      <c r="BN4" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="BO4" s="20" t="s">
         <v>0</v>
@@ -1474,19 +1480,19 @@
         <v>27</v>
       </c>
       <c r="BU4" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV4" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="BV4" s="22" t="s">
+      <c r="BW4" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="BW4" s="21" t="s">
+      <c r="BX4" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="BX4" s="21" t="s">
+      <c r="BY4" s="22" t="s">
         <v>100</v>
-      </c>
-      <c r="BY4" s="22" t="s">
-        <v>101</v>
       </c>
       <c r="BZ4" s="22" t="s">
         <v>0</v>
@@ -1507,19 +1513,19 @@
         <v>27</v>
       </c>
       <c r="CF4" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG4" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="CG4" s="16" t="s">
+      <c r="CH4" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CH4" s="15" t="s">
+      <c r="CI4" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="CI4" s="15" t="s">
+      <c r="CJ4" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="CJ4" s="16" t="s">
-        <v>101</v>
       </c>
       <c r="CK4" s="16" t="s">
         <v>0</v>
@@ -1571,25 +1577,25 @@
       <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="54" t="s">
+      <c r="L5" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="55">
+      <c r="M5" s="53">
         <v>-1.1417580764457E-2</v>
       </c>
-      <c r="N5" s="56">
+      <c r="N5" s="54">
         <v>-6.6496702841865596E-3</v>
       </c>
-      <c r="O5" s="56">
+      <c r="O5" s="54">
         <v>-4.7679104802704304E-3</v>
       </c>
-      <c r="P5" s="56">
+      <c r="P5" s="54">
         <v>-4.1343161880321704E-3</v>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="54">
         <v>1.5551896952489199E-2</v>
       </c>
       <c r="R5" s="42">
@@ -1855,25 +1861,25 @@
       <c r="J6" s="4">
         <v>1</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="L6" s="54" t="s">
+      <c r="L6" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="53">
         <v>-3.40718108838758E-2</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="54">
         <v>1.59627752355616E-2</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="54">
         <v>-5.0034586119437403E-2</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="54">
         <v>2.8330339452691299E-3</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="54">
         <v>3.1238776938606699E-2</v>
       </c>
       <c r="R6" s="42">
@@ -2139,25 +2145,25 @@
       <c r="J7" s="4">
         <v>3</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="54" t="s">
+      <c r="L7" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="55">
+      <c r="M7" s="53">
         <v>-1.1940760828396299E-2</v>
       </c>
-      <c r="N7" s="56">
+      <c r="N7" s="54">
         <v>-1.1940760828396299E-2</v>
       </c>
-      <c r="O7" s="56">
-        <v>0</v>
-      </c>
-      <c r="P7" s="56">
+      <c r="O7" s="54">
+        <v>0</v>
+      </c>
+      <c r="P7" s="54">
         <v>2.1313804418397898E-2</v>
       </c>
-      <c r="Q7" s="56">
+      <c r="Q7" s="54">
         <v>-9.3730435900016805E-3</v>
       </c>
       <c r="R7" s="42">
@@ -2423,25 +2429,25 @@
       <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="K8" s="54" t="s">
+      <c r="K8" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="54" t="s">
+      <c r="L8" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="55">
+      <c r="M8" s="53">
         <v>-1.31297178114245E-2</v>
       </c>
-      <c r="N8" s="56">
+      <c r="N8" s="54">
         <v>-2.22560699770122E-2</v>
       </c>
-      <c r="O8" s="56">
+      <c r="O8" s="54">
         <v>9.1263521655877405E-3</v>
       </c>
-      <c r="P8" s="56">
+      <c r="P8" s="54">
         <v>1.6553606576849102E-2</v>
       </c>
-      <c r="Q8" s="56">
+      <c r="Q8" s="54">
         <v>-3.4238887654246199E-3</v>
       </c>
       <c r="R8" s="42">
@@ -2707,25 +2713,25 @@
       <c r="J9" s="4">
         <v>0</v>
       </c>
-      <c r="K9" s="54" t="s">
+      <c r="K9" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="55">
+      <c r="L9" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" s="53">
         <v>3.5572075563052301E-2</v>
       </c>
-      <c r="N9" s="56">
+      <c r="N9" s="54">
         <v>-2.44890035004021E-2</v>
       </c>
-      <c r="O9" s="56">
+      <c r="O9" s="54">
         <v>6.0061079063454398E-2</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="54">
         <v>-3.1190116501160901E-2</v>
       </c>
-      <c r="Q9" s="56">
+      <c r="Q9" s="54">
         <v>-4.3819590618913397E-3</v>
       </c>
       <c r="R9" s="42">
@@ -2991,25 +2997,25 @@
       <c r="J10" s="4">
         <v>3</v>
       </c>
-      <c r="K10" s="54" t="s">
+      <c r="K10" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="54" t="s">
+      <c r="L10" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M10" s="55">
+      <c r="M10" s="53">
         <v>1.18560275071239E-2</v>
       </c>
-      <c r="N10" s="56">
+      <c r="N10" s="54">
         <v>3.47451351595907E-3</v>
       </c>
-      <c r="O10" s="56">
+      <c r="O10" s="54">
         <v>8.3815139911648292E-3</v>
       </c>
-      <c r="P10" s="56">
+      <c r="P10" s="54">
         <v>4.0878115790160497E-3</v>
       </c>
-      <c r="Q10" s="56">
+      <c r="Q10" s="54">
         <v>-1.5943839086139899E-2</v>
       </c>
       <c r="R10" s="42">
@@ -3275,25 +3281,25 @@
       <c r="J11" s="4">
         <v>11</v>
       </c>
-      <c r="K11" s="54" t="s">
+      <c r="K11" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="54" t="s">
+      <c r="L11" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M11" s="55">
+      <c r="M11" s="53">
         <v>7.7173410346352798E-3</v>
       </c>
-      <c r="N11" s="56">
+      <c r="N11" s="54">
         <v>4.3085169153803697E-3</v>
       </c>
-      <c r="O11" s="56">
+      <c r="O11" s="54">
         <v>3.4088241192548499E-3</v>
       </c>
-      <c r="P11" s="56">
+      <c r="P11" s="54">
         <v>-5.9217136051366902E-3</v>
       </c>
-      <c r="Q11" s="56">
+      <c r="Q11" s="54">
         <v>-1.7956274294986E-3</v>
       </c>
       <c r="R11" s="42">
@@ -3559,25 +3565,25 @@
       <c r="J12" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="54" t="s">
+      <c r="K12" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="54" t="s">
+      <c r="L12" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="55">
+      <c r="M12" s="53">
         <v>2.6217479332740799E-2</v>
       </c>
-      <c r="N12" s="56">
+      <c r="N12" s="54">
         <v>3.9016378162952399E-2</v>
       </c>
-      <c r="O12" s="56">
+      <c r="O12" s="54">
         <v>-1.2798898830211699E-2</v>
       </c>
-      <c r="P12" s="56">
+      <c r="P12" s="54">
         <v>-7.3040762529151303E-3</v>
       </c>
-      <c r="Q12" s="56">
+      <c r="Q12" s="54">
         <v>-1.89134030798256E-2</v>
       </c>
       <c r="R12" s="42">
@@ -3843,25 +3849,25 @@
       <c r="J13" s="4">
         <v>6</v>
       </c>
-      <c r="K13" s="54" t="s">
+      <c r="K13" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="54" t="s">
+      <c r="L13" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M13" s="55">
+      <c r="M13" s="53">
         <v>-6.3668600902643493E-2</v>
       </c>
-      <c r="N13" s="56">
+      <c r="N13" s="54">
         <v>-6.3668600902643493E-2</v>
       </c>
-      <c r="O13" s="56">
-        <v>0</v>
-      </c>
-      <c r="P13" s="56">
+      <c r="O13" s="54">
+        <v>0</v>
+      </c>
+      <c r="P13" s="54">
         <v>4.9161831076724699E-2</v>
       </c>
-      <c r="Q13" s="56">
+      <c r="Q13" s="54">
         <v>1.45067698259188E-2</v>
       </c>
       <c r="R13" s="42">
@@ -4127,25 +4133,25 @@
       <c r="J14" s="4">
         <v>8</v>
       </c>
-      <c r="K14" s="54" t="s">
+      <c r="K14" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="54" t="s">
+      <c r="L14" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="55">
+      <c r="M14" s="53">
         <v>-2.2548324282075399E-2</v>
       </c>
-      <c r="N14" s="56">
+      <c r="N14" s="54">
         <v>2.2472473369013399E-2</v>
       </c>
-      <c r="O14" s="56">
+      <c r="O14" s="54">
         <v>-4.5020797651088802E-2</v>
       </c>
-      <c r="P14" s="56">
+      <c r="P14" s="54">
         <v>1.29601389672714E-2</v>
       </c>
-      <c r="Q14" s="56">
+      <c r="Q14" s="54">
         <v>9.5881853148039303E-3</v>
       </c>
       <c r="R14" s="42">
@@ -4411,25 +4417,25 @@
       <c r="J15" s="4">
         <v>0</v>
       </c>
-      <c r="K15" s="54" t="s">
+      <c r="K15" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L15" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" s="55">
+      <c r="L15" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="53">
         <v>5.9616999186853396E-3</v>
       </c>
-      <c r="N15" s="56">
+      <c r="N15" s="54">
         <v>9.1739876721604902E-3</v>
       </c>
-      <c r="O15" s="56">
+      <c r="O15" s="54">
         <v>-3.2122877534751398E-3</v>
       </c>
-      <c r="P15" s="56">
+      <c r="P15" s="54">
         <v>-1.35885130316169E-2</v>
       </c>
-      <c r="Q15" s="56">
+      <c r="Q15" s="54">
         <v>7.6268131129315899E-3</v>
       </c>
       <c r="R15" s="42">
@@ -4695,25 +4701,25 @@
       <c r="J16" s="4">
         <v>4</v>
       </c>
-      <c r="K16" s="54" t="s">
+      <c r="K16" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="54" t="s">
+      <c r="L16" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M16" s="55">
+      <c r="M16" s="53">
         <v>3.6640367238685301E-2</v>
       </c>
-      <c r="N16" s="56">
+      <c r="N16" s="54">
         <v>-5.8484827293232601E-3</v>
       </c>
-      <c r="O16" s="56">
+      <c r="O16" s="54">
         <v>4.2488849968008599E-2</v>
       </c>
-      <c r="P16" s="56">
+      <c r="P16" s="54">
         <v>-1.2261121067480601E-2</v>
       </c>
-      <c r="Q16" s="56">
+      <c r="Q16" s="54">
         <v>-2.4379246171204801E-2</v>
       </c>
       <c r="R16" s="42">
@@ -4979,25 +4985,25 @@
       <c r="J17" s="4">
         <v>7</v>
       </c>
-      <c r="K17" s="54" t="s">
+      <c r="K17" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="54" t="s">
+      <c r="L17" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M17" s="55">
+      <c r="M17" s="53">
         <v>-5.1980154394710197E-3</v>
       </c>
-      <c r="N17" s="56">
+      <c r="N17" s="54">
         <v>-5.9098648549230103E-4</v>
       </c>
-      <c r="O17" s="56">
+      <c r="O17" s="54">
         <v>-4.6070289539786998E-3</v>
       </c>
-      <c r="P17" s="56">
+      <c r="P17" s="54">
         <v>-5.14822768970352E-3</v>
       </c>
-      <c r="Q17" s="56">
+      <c r="Q17" s="54">
         <v>1.0346243129174501E-2</v>
       </c>
       <c r="R17" s="42">
@@ -5263,25 +5269,25 @@
       <c r="J18" s="4">
         <v>9</v>
       </c>
-      <c r="K18" s="54" t="s">
+      <c r="K18" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L18" s="54" t="s">
+      <c r="L18" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="55">
+      <c r="M18" s="53">
         <v>9.2029047750505407E-3</v>
       </c>
-      <c r="N18" s="56">
+      <c r="N18" s="54">
         <v>-4.8068211901162701E-3</v>
       </c>
-      <c r="O18" s="56">
+      <c r="O18" s="54">
         <v>1.40097259651668E-2</v>
       </c>
-      <c r="P18" s="56">
+      <c r="P18" s="54">
         <v>-9.5765587121586192E-3</v>
       </c>
-      <c r="Q18" s="56">
+      <c r="Q18" s="54">
         <v>3.7365393710814298E-4</v>
       </c>
       <c r="R18" s="42">
@@ -5547,25 +5553,25 @@
       <c r="J19" s="4">
         <v>0</v>
       </c>
-      <c r="K19" s="54" t="s">
+      <c r="K19" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="M19" s="55">
+      <c r="L19" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="M19" s="53">
         <v>1.15298763736263E-2</v>
       </c>
-      <c r="N19" s="56">
+      <c r="N19" s="54">
         <v>0.108404876373626</v>
       </c>
-      <c r="O19" s="56">
+      <c r="O19" s="54">
         <v>-9.6875000000000003E-2</v>
       </c>
-      <c r="P19" s="56">
+      <c r="P19" s="54">
         <v>-2.71806318681319E-2</v>
       </c>
-      <c r="Q19" s="56">
+      <c r="Q19" s="54">
         <v>1.5650755494505501E-2</v>
       </c>
       <c r="R19" s="42">
@@ -5831,25 +5837,25 @@
       <c r="J20" s="4">
         <v>8</v>
       </c>
-      <c r="K20" s="54" t="s">
+      <c r="K20" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="54" t="s">
+      <c r="L20" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M20" s="55">
+      <c r="M20" s="53">
         <v>-1.6765916146188799E-2</v>
       </c>
-      <c r="N20" s="56">
+      <c r="N20" s="54">
         <v>-7.8063430916611703E-3</v>
       </c>
-      <c r="O20" s="56">
+      <c r="O20" s="54">
         <v>-8.9595730545275996E-3</v>
       </c>
-      <c r="P20" s="56">
+      <c r="P20" s="54">
         <v>1.29560423301013E-2</v>
       </c>
-      <c r="Q20" s="56">
+      <c r="Q20" s="54">
         <v>3.8098738160874698E-3</v>
       </c>
       <c r="R20" s="42">
@@ -6115,25 +6121,25 @@
       <c r="J21" s="4">
         <v>5</v>
       </c>
-      <c r="K21" s="54" t="s">
+      <c r="K21" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L21" s="54" t="s">
+      <c r="L21" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="M21" s="55">
+      <c r="M21" s="53">
         <v>-2.7788721666272699E-2</v>
       </c>
-      <c r="N21" s="56">
+      <c r="N21" s="54">
         <v>-2.88787329603656E-2</v>
       </c>
-      <c r="O21" s="56">
+      <c r="O21" s="54">
         <v>1.09001129409293E-3</v>
       </c>
-      <c r="P21" s="56">
+      <c r="P21" s="54">
         <v>-1.2567961547553399E-2</v>
       </c>
-      <c r="Q21" s="56">
+      <c r="Q21" s="54">
         <v>4.03566832138261E-2</v>
       </c>
       <c r="R21" s="42">
@@ -6545,22 +6551,22 @@
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="49" t="s">
-        <v>39</v>
-      </c>
       <c r="D3" s="49" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F3" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="49" t="s">
         <v>94</v>
-      </c>
-      <c r="G3" s="49" t="s">
-        <v>95</v>
       </c>
       <c r="H3" s="31" t="s">
         <v>4</v>
@@ -6622,76 +6628,76 @@
         <v>10</v>
       </c>
       <c r="B4" s="50">
-        <v>0.33758422899148</v>
+        <v>0.33915726677409402</v>
       </c>
       <c r="C4" s="50">
-        <v>0.339650831985919</v>
+        <v>0.33818616907233601</v>
       </c>
       <c r="D4" s="50">
-        <v>0.33915726677409402</v>
+        <v>0.33675168049224202</v>
       </c>
       <c r="E4" s="50">
-        <v>0.33675168049224202</v>
+        <v>0.33907282887309398</v>
       </c>
       <c r="F4" s="50">
-        <v>0.34037882811116998</v>
+        <v>0.33732223007157203</v>
       </c>
       <c r="G4" s="51">
-        <v>3.6271476189281299E-3</v>
+        <v>-1.7505988015226201E-3</v>
       </c>
       <c r="H4" s="39">
-        <v>0.33758422899148</v>
+        <v>0.33818616907233601</v>
       </c>
       <c r="I4" s="39">
-        <v>0.34037882811116998</v>
+        <v>0.33732223007157203</v>
       </c>
       <c r="J4" s="40">
-        <v>2.7945991196904299E-3</v>
+        <v>-8.63939000764258E-4</v>
       </c>
       <c r="K4" s="39">
-        <v>9.0152865177925007E-2</v>
+        <v>8.9965350061207996E-2</v>
       </c>
       <c r="L4" s="39">
-        <v>8.9686670207116306E-2</v>
+        <v>8.6985064828491707E-2</v>
       </c>
       <c r="M4" s="40">
-        <v>-4.6619497080874201E-4</v>
+        <v>-2.9802852327162799E-3</v>
       </c>
       <c r="N4" s="39">
-        <v>0.39154647212786098</v>
+        <v>0.38614970710081697</v>
       </c>
       <c r="O4" s="39">
-        <v>0.386496725084086</v>
+        <v>0.38669463889424099</v>
       </c>
       <c r="P4" s="40">
-        <v>-5.04974704377531E-3</v>
+        <v>5.4493179342390797E-4</v>
       </c>
       <c r="Q4" s="39">
-        <v>0.18071643370273399</v>
+        <v>0.18569877376563901</v>
       </c>
       <c r="R4" s="39">
-        <v>0.183437776597628</v>
+        <v>0.18899806620569601</v>
       </c>
       <c r="S4" s="40">
-        <v>2.7213428948935901E-3</v>
+        <v>3.2992924400566401E-3</v>
       </c>
       <c r="T4" s="39">
-        <v>0.17024697889402499</v>
+        <v>0.17466058967141301</v>
       </c>
       <c r="U4" s="39">
-        <v>0.17341122322534999</v>
+        <v>0.17752374428246201</v>
       </c>
       <c r="V4" s="40">
-        <v>3.16424433132501E-3</v>
+        <v>2.8631546110489698E-3</v>
       </c>
       <c r="W4" s="39">
-        <v>1.0469454808709699E-2</v>
+        <v>1.10381840942257E-2</v>
       </c>
       <c r="X4" s="39">
-        <v>1.0026553372278301E-2</v>
+        <v>1.14743219232334E-2</v>
       </c>
       <c r="Y4" s="40">
-        <v>-4.4290143643141601E-4</v>
+        <v>4.3613782900765898E-4</v>
       </c>
     </row>
   </sheetData>
@@ -6843,14 +6849,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="44">
-        <v>0.47945205479452102</v>
+        <v>0.48275862068965503</v>
       </c>
       <c r="C5" s="44">
-        <v>0.73469387755102</v>
+        <v>0.67857142857142905</v>
       </c>
       <c r="D5" s="45">
-        <f>IFERROR(C5-B5,"")</f>
-        <v>0.25524182275649898</v>
+        <v>0.19581280788177299</v>
       </c>
       <c r="E5" s="45">
         <v>0</v>
@@ -6862,34 +6867,31 @@
         <v>0</v>
       </c>
       <c r="H5" s="44">
-        <v>0.27168949771689499</v>
+        <v>0</v>
       </c>
       <c r="I5" s="44">
-        <v>0.26530612244898</v>
+        <v>0</v>
       </c>
       <c r="J5" s="45">
-        <f>IFERROR(I5-H5,"")</f>
-        <v>-6.3833752679149924E-3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="44">
-        <v>0.24885844748858399</v>
+        <v>0.51724137931034497</v>
       </c>
       <c r="L5" s="44">
-        <v>0</v>
+        <v>0.32142857142857101</v>
       </c>
       <c r="M5" s="45">
-        <f>IFERROR(L5-K5,"")</f>
-        <v>-0.24885844748858399</v>
+        <v>-0.19581280788177299</v>
       </c>
       <c r="N5" s="44">
-        <v>0.24885844748858399</v>
+        <v>0.51724137931034497</v>
       </c>
       <c r="O5" s="44">
-        <v>0</v>
+        <v>0.32142857142857101</v>
       </c>
       <c r="P5" s="45">
-        <f>IFERROR(O5-N5,"")</f>
-        <v>-0.24885844748858399</v>
+        <v>-0.19581280788177299</v>
       </c>
       <c r="Q5" s="44">
         <v>0</v>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>WOW</t>
-  </si>
-  <si>
-    <t>BENGKAYANG|BENGKAYANG</t>
   </si>
   <si>
     <t>SDP JAGOI BABANG</t>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>NO DATA</t>
+  </si>
+  <si>
+    <t>BENGKAYANG|BENGKAYANG</t>
   </si>
 </sst>
 </file>
@@ -997,30 +997,31 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7265625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6328125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="20.1796875" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="7.1796875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="6" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.453125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="6" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="7.36328125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1796875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="7.6328125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.81640625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="7.36328125" hidden="1" customWidth="1"/>
+    <col min="26" max="27" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="7.36328125" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7.6328125" bestFit="1" customWidth="1"/>
@@ -1286,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -1561,28 +1562,28 @@
     </row>
     <row r="5" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4">
         <v>32.258000000000003</v>
@@ -1591,10 +1592,10 @@
         <v>8</v>
       </c>
       <c r="K5" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="46" t="s">
         <v>34</v>
-      </c>
-      <c r="L5" s="46" t="s">
-        <v>35</v>
       </c>
       <c r="M5" s="47">
         <v>-8.2941392937548302E-3</v>
@@ -1845,28 +1846,28 @@
     </row>
     <row r="6" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4">
         <v>6.1909999999999998</v>
@@ -1875,10 +1876,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M6" s="47">
         <v>-1.2006859207729099E-2</v>
@@ -2129,28 +2130,28 @@
     </row>
     <row r="7" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I7" s="4">
         <v>13.444000000000001</v>
@@ -2159,10 +2160,10 @@
         <v>4</v>
       </c>
       <c r="K7" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="46" t="s">
         <v>34</v>
-      </c>
-      <c r="L7" s="46" t="s">
-        <v>35</v>
       </c>
       <c r="M7" s="47">
         <v>-1.0516736959945899E-2</v>
@@ -2413,28 +2414,28 @@
     </row>
     <row r="8" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I8" s="4">
         <v>6.2549999999999999</v>
@@ -2443,10 +2444,10 @@
         <v>3</v>
       </c>
       <c r="K8" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M8" s="47">
         <v>1.22535923659816E-2</v>
@@ -2697,28 +2698,28 @@
     </row>
     <row r="9" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" s="4">
         <v>15.622</v>
@@ -2727,10 +2728,10 @@
         <v>6</v>
       </c>
       <c r="K9" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L9" s="46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" s="47">
         <v>-6.5836847325302398E-3</v>
@@ -2981,28 +2982,28 @@
     </row>
     <row r="10" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" s="4">
         <v>19.111000000000001</v>
@@ -3011,10 +3012,10 @@
         <v>8</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L10" s="46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M10" s="47">
         <v>2.23501277300545E-2</v>
@@ -3265,22 +3266,22 @@
     </row>
     <row r="11" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>10</v>
@@ -3295,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L11" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M11" s="47">
         <v>-2.6862828331967702E-3</v>
@@ -3549,22 +3550,22 @@
     </row>
     <row r="12" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>10</v>
@@ -3579,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M12" s="47">
         <v>-0.143110795454545</v>
@@ -3833,28 +3834,28 @@
     </row>
     <row r="13" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I13" s="4">
         <v>16.844000000000001</v>
@@ -3863,10 +3864,10 @@
         <v>8</v>
       </c>
       <c r="K13" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="46" t="s">
         <v>34</v>
-      </c>
-      <c r="L13" s="46" t="s">
-        <v>35</v>
       </c>
       <c r="M13" s="47">
         <v>-7.6618440429617202E-3</v>
@@ -4117,28 +4118,28 @@
     </row>
     <row r="14" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I14" s="4">
         <v>9.0890000000000004</v>
@@ -4147,10 +4148,10 @@
         <v>5</v>
       </c>
       <c r="K14" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="46" t="s">
         <v>34</v>
-      </c>
-      <c r="L14" s="46" t="s">
-        <v>35</v>
       </c>
       <c r="M14" s="47">
         <v>1.21592124944139E-2</v>
@@ -4594,22 +4595,22 @@
         <v>3</v>
       </c>
       <c r="B3" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>78</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>4</v>
@@ -4621,22 +4622,22 @@
         <v>4</v>
       </c>
       <c r="K3" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="27" t="s">
         <v>77</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>78</v>
       </c>
       <c r="Q3" s="27" t="s">
         <v>5</v>
@@ -4695,7 +4696,7 @@
     </row>
     <row r="4" spans="1:34" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="44">
         <v>0.35336834001677597</v>
@@ -4944,61 +4945,61 @@
     </row>
     <row r="5" spans="1:19" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="38">
         <v>0.73170731707317105</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="39">
         <v>0</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="38">
         <v>0.26829268292682901</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K5" s="38">
         <v>0</v>
       </c>
       <c r="L5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="39">
         <v>0</v>
       </c>
       <c r="O5" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="39">
         <v>0</v>
       </c>
       <c r="R5" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5016,7 +5017,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>4</v>
@@ -5033,7 +5034,7 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="22">
         <v>0.35460000000000003</v>
@@ -5067,7 +5068,7 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="22">
         <v>0.35600000000000004</v>
@@ -5084,7 +5085,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="22">
         <v>0.36349999999999999</v>
@@ -5118,7 +5119,7 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>4</v>
@@ -5135,7 +5136,7 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="22">
         <v>0.28760000000000002</v>
@@ -5169,7 +5170,7 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="22">
         <v>0.30760000000000004</v>
@@ -5186,7 +5187,7 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B13" s="22">
         <v>0.26419999999999999</v>
@@ -5220,7 +5221,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>4</v>
@@ -5237,7 +5238,7 @@
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="22">
         <v>0.19820000000000002</v>
@@ -5271,7 +5272,7 @@
     </row>
     <row r="20" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="22">
         <v>0.2122</v>
@@ -5288,7 +5289,7 @@
     </row>
     <row r="21" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="22">
         <v>0.23980000000000001</v>
@@ -5322,7 +5323,7 @@
     </row>
     <row r="25" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>4</v>
@@ -5339,7 +5340,7 @@
     </row>
     <row r="26" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="22">
         <v>0.50309999999999999</v>
@@ -5373,7 +5374,7 @@
     </row>
     <row r="28" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="22">
         <v>0.51649999999999996</v>
@@ -5390,7 +5391,7 @@
     </row>
     <row r="29" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="22">
         <v>0.48899999999999999</v>
@@ -5424,7 +5425,7 @@
     </row>
     <row r="33" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>4</v>
@@ -5441,7 +5442,7 @@
     </row>
     <row r="34" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34" s="22">
         <v>0.17910000000000001</v>
@@ -5475,7 +5476,7 @@
     </row>
     <row r="36" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="22">
         <v>0.17480000000000001</v>
@@ -5492,7 +5493,7 @@
     </row>
     <row r="37" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37" s="22">
         <v>0.15659999999999999</v>
@@ -5526,7 +5527,7 @@
     </row>
     <row r="41" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>4</v>
@@ -5543,7 +5544,7 @@
     </row>
     <row r="42" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="22">
         <v>0.37340000000000001</v>
@@ -5577,7 +5578,7 @@
     </row>
     <row r="44" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="22">
         <v>0.36060000000000003</v>
@@ -5594,7 +5595,7 @@
     </row>
     <row r="45" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" s="22">
         <v>0.36090000000000005</v>
@@ -5628,7 +5629,7 @@
     </row>
     <row r="49" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>4</v>
@@ -5645,7 +5646,7 @@
     </row>
     <row r="50" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="22">
         <v>0.5262</v>
@@ -5679,7 +5680,7 @@
     </row>
     <row r="52" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="22">
         <v>0.53010000000000002</v>
@@ -5696,7 +5697,7 @@
     </row>
     <row r="53" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B53" s="22">
         <v>0.52560000000000007</v>
@@ -5730,7 +5731,7 @@
     </row>
     <row r="57" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>4</v>
@@ -5747,7 +5748,7 @@
     </row>
     <row r="58" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="22">
         <v>0.3836</v>
@@ -5781,7 +5782,7 @@
     </row>
     <row r="60" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" s="22">
         <v>0.39479999999999998</v>
@@ -5798,7 +5799,7 @@
     </row>
     <row r="61" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="22">
         <v>0.41649999999999998</v>
@@ -5832,7 +5833,7 @@
     </row>
     <row r="65" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>4</v>
@@ -5849,7 +5850,7 @@
     </row>
     <row r="66" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="22">
         <v>0.42749999999999999</v>
@@ -5883,7 +5884,7 @@
     </row>
     <row r="68" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" s="22">
         <v>0.5</v>
@@ -5900,7 +5901,7 @@
     </row>
     <row r="69" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B69" s="22">
         <v>0.44390000000000002</v>
@@ -5934,7 +5935,7 @@
     </row>
     <row r="73" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" s="20" t="s">
         <v>4</v>
@@ -5951,7 +5952,7 @@
     </row>
     <row r="74" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" s="22">
         <v>0.28149999999999997</v>
@@ -5985,7 +5986,7 @@
     </row>
     <row r="76" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" s="22">
         <v>0.28260000000000002</v>
@@ -6002,7 +6003,7 @@
     </row>
     <row r="77" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B77" s="22">
         <v>0.30590000000000001</v>
@@ -6036,7 +6037,7 @@
     </row>
     <row r="81" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>4</v>
@@ -6053,7 +6054,7 @@
     </row>
     <row r="82" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" s="22">
         <v>0.3</v>
@@ -6087,7 +6088,7 @@
     </row>
     <row r="84" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" s="22">
         <v>0.28760000000000002</v>
@@ -6104,7 +6105,7 @@
     </row>
     <row r="85" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B85" s="22">
         <v>0.27550000000000002</v>
@@ -6138,7 +6139,7 @@
     </row>
     <row r="89" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>4</v>
@@ -6155,7 +6156,7 @@
     </row>
     <row r="90" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B90" s="22">
         <v>0.3342</v>
@@ -6189,7 +6190,7 @@
     </row>
     <row r="92" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" s="22">
         <v>0.31329999999999997</v>
@@ -6206,7 +6207,7 @@
     </row>
     <row r="93" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B93" s="22">
         <v>0.31069999999999998</v>
@@ -6240,7 +6241,7 @@
     </row>
     <row r="97" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B97" s="20" t="s">
         <v>4</v>
@@ -6257,7 +6258,7 @@
     </row>
     <row r="98" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B98" s="22">
         <v>0.22949999999999998</v>
@@ -6291,7 +6292,7 @@
     </row>
     <row r="100" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100" s="22">
         <v>0.22889999999999999</v>
@@ -6308,7 +6309,7 @@
     </row>
     <row r="101" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B101" s="22">
         <v>0.22940000000000002</v>
@@ -6342,7 +6343,7 @@
     </row>
     <row r="105" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B105" s="20" t="s">
         <v>4</v>
@@ -6359,7 +6360,7 @@
     </row>
     <row r="106" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B106" s="22">
         <v>0.1245</v>
@@ -6393,7 +6394,7 @@
     </row>
     <row r="108" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B108" s="22">
         <v>0.11550000000000001</v>
@@ -6410,7 +6411,7 @@
     </row>
     <row r="109" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B109" s="22">
         <v>0.12939999999999999</v>
@@ -6444,7 +6445,7 @@
     </row>
     <row r="113" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B113" s="20" t="s">
         <v>4</v>
@@ -6461,7 +6462,7 @@
     </row>
     <row r="114" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B114" s="22">
         <v>0.35189999999999999</v>
@@ -6495,7 +6496,7 @@
     </row>
     <row r="116" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A116" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B116" s="22">
         <v>0.45779999999999998</v>
@@ -6512,7 +6513,7 @@
     </row>
     <row r="117" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A117" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B117" s="22">
         <v>0.44579999999999997</v>
@@ -6546,7 +6547,7 @@
     </row>
     <row r="121" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B121" s="20" t="s">
         <v>4</v>
@@ -6563,7 +6564,7 @@
     </row>
     <row r="122" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B122" s="22">
         <v>0.34100000000000003</v>
@@ -6597,7 +6598,7 @@
     </row>
     <row r="124" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B124" s="22">
         <v>0.34429999999999999</v>
@@ -6614,7 +6615,7 @@
     </row>
     <row r="125" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B125" s="22">
         <v>0.34340000000000004</v>
@@ -6648,7 +6649,7 @@
     </row>
     <row r="129" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B129" s="20" t="s">
         <v>4</v>
@@ -6665,7 +6666,7 @@
     </row>
     <row r="130" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B130" s="22">
         <v>0.3105</v>
@@ -6699,7 +6700,7 @@
     </row>
     <row r="132" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B132" s="22">
         <v>0.3251</v>
@@ -6716,7 +6717,7 @@
     </row>
     <row r="133" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B133" s="22">
         <v>0.35729999999999995</v>
@@ -6763,63 +6764,63 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="K1" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="22">
         <v>0.35460000000000003</v>
@@ -6931,7 +6932,7 @@
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="22">
         <v>0.35600000000000004</v>
@@ -6987,7 +6988,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="22">
         <v>0.36349999999999999</v>
@@ -7099,63 +7100,63 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="20" t="s">
+      <c r="D9" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="E9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F9" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="H9" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="I9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="J9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="K9" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="L9" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="20" t="s">
+      <c r="O9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="20" t="s">
+      <c r="P9" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P9" s="20" t="s">
+      <c r="Q9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="R9" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R9" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="22">
         <v>0.3538</v>
@@ -7211,7 +7212,7 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="22">
         <v>0.35320000000000001</v>
@@ -7267,63 +7268,63 @@
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="E14" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="H14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="I14" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="J14" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="K14" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="L14" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M14" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="O14" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="20" t="s">
+      <c r="P14" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P14" s="20" t="s">
+      <c r="Q14" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q14" s="20" t="s">
+      <c r="R14" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R14" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="22">
         <v>8.7899999999999992E-2</v>
@@ -7435,7 +7436,7 @@
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="22">
         <v>8.5299999999999987E-2</v>
@@ -7491,7 +7492,7 @@
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="22">
         <v>8.2899999999999988E-2</v>
@@ -7603,63 +7604,63 @@
     </row>
     <row r="22" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="E22" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F22" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="H22" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="I22" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="J22" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J22" s="20" t="s">
+      <c r="K22" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="L22" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M22" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N22" s="20" t="s">
+      <c r="O22" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="20" t="s">
+      <c r="P22" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P22" s="20" t="s">
+      <c r="Q22" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="20" t="s">
+      <c r="R22" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R22" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="22">
         <v>8.48E-2</v>
@@ -7715,7 +7716,7 @@
     </row>
     <row r="24" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="22">
         <v>8.6599999999999996E-2</v>
@@ -7771,63 +7772,63 @@
     </row>
     <row r="27" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="D27" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="E27" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F27" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="H27" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="I27" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="J27" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="K27" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="L27" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L27" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M27" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N27" s="20" t="s">
+      <c r="O27" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O27" s="20" t="s">
+      <c r="P27" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P27" s="20" t="s">
+      <c r="Q27" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q27" s="20" t="s">
+      <c r="R27" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R27" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="22">
         <v>0.4204</v>
@@ -7939,7 +7940,7 @@
     </row>
     <row r="30" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="22">
         <v>0.42520000000000002</v>
@@ -7995,7 +7996,7 @@
     </row>
     <row r="31" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="22">
         <v>0.42680000000000001</v>
@@ -8107,63 +8108,63 @@
     </row>
     <row r="35" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="20" t="s">
+      <c r="D35" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="E35" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F35" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="H35" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="I35" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="20" t="s">
+      <c r="J35" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J35" s="20" t="s">
+      <c r="K35" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K35" s="20" t="s">
+      <c r="L35" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L35" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M35" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N35" s="20" t="s">
+      <c r="O35" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O35" s="20" t="s">
+      <c r="P35" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P35" s="20" t="s">
+      <c r="Q35" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q35" s="20" t="s">
+      <c r="R35" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R35" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="22">
         <v>0.42799999999999999</v>
@@ -8219,7 +8220,7 @@
     </row>
     <row r="37" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="22">
         <v>0.42219999999999996</v>
@@ -8275,63 +8276,63 @@
     </row>
     <row r="40" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="20" t="s">
+      <c r="D40" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="E40" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F40" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="H40" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="I40" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="20" t="s">
+      <c r="J40" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J40" s="20" t="s">
+      <c r="K40" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K40" s="20" t="s">
+      <c r="L40" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L40" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M40" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N40" s="20" t="s">
+      <c r="O40" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O40" s="20" t="s">
+      <c r="P40" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P40" s="20" t="s">
+      <c r="Q40" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q40" s="20" t="s">
+      <c r="R40" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R40" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="22">
         <v>0.13720000000000002</v>
@@ -8443,7 +8444,7 @@
     </row>
     <row r="43" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" s="22">
         <v>0.13350000000000001</v>
@@ -8499,7 +8500,7 @@
     </row>
     <row r="44" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B44" s="22">
         <v>0.1268</v>
@@ -8611,63 +8612,63 @@
     </row>
     <row r="48" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="20" t="s">
+      <c r="D48" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="E48" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E48" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="F48" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="20" t="s">
+      <c r="H48" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H48" s="20" t="s">
+      <c r="I48" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="20" t="s">
+      <c r="J48" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J48" s="20" t="s">
+      <c r="K48" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="K48" s="20" t="s">
+      <c r="L48" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L48" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="M48" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="N48" s="20" t="s">
+      <c r="O48" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O48" s="20" t="s">
+      <c r="P48" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="P48" s="20" t="s">
+      <c r="Q48" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="20" t="s">
+      <c r="R48" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="R48" s="20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" s="22">
         <v>0.13339999999999999</v>
@@ -8723,7 +8724,7 @@
     </row>
     <row r="50" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B50" s="22">
         <v>0.13800000000000001</v>

--- a/FB Market Share.xlsx
+++ b/FB Market Share.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="KEC MS MOM " sheetId="1" r:id="rId1"/>
@@ -996,32 +996,31 @@
   <dimension ref="A2:CP15"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.90625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1796875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7265625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.6328125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="20.1796875" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="7.1796875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="6" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="6" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="7.36328125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1796875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="7.6328125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="7.81640625" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="7.36328125" hidden="1" customWidth="1"/>
-    <col min="26" max="27" width="6.81640625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="7.36328125" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7.6328125" bestFit="1" customWidth="1"/>
@@ -1598,19 +1597,19 @@
         <v>34</v>
       </c>
       <c r="M5" s="47">
-        <v>-8.2941392937548302E-3</v>
+        <v>2.0052444995643502E-3</v>
       </c>
       <c r="N5" s="48">
-        <v>-6.9896383927734503E-3</v>
+        <v>1.3328478459347401E-3</v>
       </c>
       <c r="O5" s="48">
-        <v>-1.3045009009814001E-3</v>
+        <v>6.7239665362961399E-4</v>
       </c>
       <c r="P5" s="48">
-        <v>8.5654994354261705E-4</v>
+        <v>8.2886127980069701E-4</v>
       </c>
       <c r="Q5" s="48">
-        <v>7.4375893502122703E-3</v>
+        <v>-2.8341057793650499E-3</v>
       </c>
       <c r="R5" s="36">
         <v>0.44123961542051698</v>
@@ -1625,25 +1624,25 @@
         <v>0.43160310623447701</v>
       </c>
       <c r="V5" s="36">
-        <v>0.43475590042030399</v>
+        <v>0.43596871161678202</v>
       </c>
       <c r="W5" s="36">
-        <v>0.44305003971405899</v>
+        <v>0.433963467117218</v>
       </c>
       <c r="X5" s="36">
-        <v>0.43475590042030399</v>
+        <v>0.43596871161678202</v>
       </c>
       <c r="Y5" s="36">
-        <v>-8.2941392937548302E-3</v>
+        <v>2.0052444995643502E-3</v>
       </c>
       <c r="Z5" s="36">
-        <v>0.43160310623447701</v>
+        <v>0.433823529411765</v>
       </c>
       <c r="AA5" s="36">
-        <v>0.43475590042030399</v>
+        <v>0.43596871161678202</v>
       </c>
       <c r="AB5" s="36">
-        <v>3.1527941858272598E-3</v>
+        <v>2.14518220501725E-3</v>
       </c>
       <c r="AC5" s="36">
         <v>0.35595382557018002</v>
@@ -1658,25 +1657,25 @@
         <v>0.350614644575094</v>
       </c>
       <c r="AG5" s="36">
-        <v>0.34862592951826699</v>
+        <v>0.35454780528799501</v>
       </c>
       <c r="AH5" s="36">
-        <v>0.35561556791103999</v>
+        <v>0.35321495744206099</v>
       </c>
       <c r="AI5" s="36">
-        <v>0.34862592951826699</v>
+        <v>0.35454780528799501</v>
       </c>
       <c r="AJ5" s="36">
-        <v>-6.9896383927734503E-3</v>
+        <v>1.3328478459347401E-3</v>
       </c>
       <c r="AK5" s="36">
-        <v>0.350614644575094</v>
+        <v>0.34888107416879799</v>
       </c>
       <c r="AL5" s="36">
-        <v>0.34862592951826699</v>
+        <v>0.35454780528799501</v>
       </c>
       <c r="AM5" s="36">
-        <v>-1.9887150568265199E-3</v>
+        <v>5.6667311191974101E-3</v>
       </c>
       <c r="AN5" s="36">
         <v>8.5285789850337607E-2</v>
@@ -1691,25 +1690,25 @@
         <v>8.0988461659383199E-2</v>
       </c>
       <c r="AR5" s="36">
-        <v>8.6129970902036904E-2</v>
+        <v>8.1420906328786596E-2</v>
       </c>
       <c r="AS5" s="36">
-        <v>8.7434471803018304E-2</v>
+        <v>8.0748509675156996E-2</v>
       </c>
       <c r="AT5" s="36">
-        <v>8.6129970902036904E-2</v>
+        <v>8.1420906328786596E-2</v>
       </c>
       <c r="AU5" s="36">
-        <v>-1.3045009009814001E-3</v>
+        <v>6.7239665362961399E-4</v>
       </c>
       <c r="AV5" s="36">
-        <v>8.0988461659383199E-2</v>
+        <v>8.49424552429668E-2</v>
       </c>
       <c r="AW5" s="36">
-        <v>8.6129970902036904E-2</v>
+        <v>8.1420906328786596E-2</v>
       </c>
       <c r="AX5" s="36">
-        <v>5.1415092426537103E-3</v>
+        <v>-3.5215489141801502E-3</v>
       </c>
       <c r="AY5" s="36">
         <v>0.42524658514577302</v>
@@ -1724,25 +1723,25 @@
         <v>0.42091363536328502</v>
       </c>
       <c r="BC5" s="36">
-        <v>0.42010992563853899</v>
+        <v>0.415314499967677</v>
       </c>
       <c r="BD5" s="36">
-        <v>0.41925337569499599</v>
+        <v>0.41448563868787702</v>
       </c>
       <c r="BE5" s="36">
-        <v>0.42010992563853899</v>
+        <v>0.415314499967677</v>
       </c>
       <c r="BF5" s="37">
-        <v>8.5654994354261705E-4</v>
+        <v>8.2886127980069701E-4</v>
       </c>
       <c r="BG5" s="36">
-        <v>0.42091363536328502</v>
+        <v>0.41739130434782601</v>
       </c>
       <c r="BH5" s="36">
-        <v>0.42010992563853899</v>
+        <v>0.415314499967677</v>
       </c>
       <c r="BI5" s="37">
-        <v>-8.0370972474613799E-4</v>
+        <v>-2.0768043801487899E-3</v>
       </c>
       <c r="BJ5" s="36">
         <v>0.13351379943371</v>
@@ -1757,25 +1756,25 @@
         <v>0.147483258402238</v>
       </c>
       <c r="BN5" s="36">
-        <v>0.14513417394115699</v>
+        <v>0.14871678841554101</v>
       </c>
       <c r="BO5" s="36">
-        <v>0.137696584590945</v>
+        <v>0.151550894194906</v>
       </c>
       <c r="BP5" s="36">
-        <v>0.14513417394115699</v>
+        <v>0.14871678841554101</v>
       </c>
       <c r="BQ5" s="36">
-        <v>7.4375893502122703E-3</v>
+        <v>-2.8341057793650499E-3</v>
       </c>
       <c r="BR5" s="36">
-        <v>0.147483258402238</v>
+        <v>0.14878516624040899</v>
       </c>
       <c r="BS5" s="36">
-        <v>0.14513417394115699</v>
+        <v>0.14871678841554101</v>
       </c>
       <c r="BT5" s="36">
-        <v>-2.3490844610810401E-3</v>
+        <v>-6.8377824868459696E-5</v>
       </c>
       <c r="BU5" s="36">
         <v>0.12850430940601801</v>
@@ -1790,25 +1789,25 @@
         <v>0.13927751752758799</v>
       </c>
       <c r="BY5" s="36">
-        <v>0.139282250242483</v>
+        <v>0.14383605921520501</v>
       </c>
       <c r="BZ5" s="36">
-        <v>0.13261318506751399</v>
+        <v>0.14074404667028001</v>
       </c>
       <c r="CA5" s="36">
-        <v>0.139282250242483</v>
+        <v>0.14383605921520501</v>
       </c>
       <c r="CB5" s="36">
-        <v>4.7327148947617897E-6</v>
+        <v>4.5585416876163199E-3</v>
       </c>
       <c r="CC5" s="36">
-        <v>0.13927751752758799</v>
+        <v>0.14459718670076699</v>
       </c>
       <c r="CD5" s="36">
-        <v>0.139282250242483</v>
+        <v>0.14383605921520501</v>
       </c>
       <c r="CE5" s="36">
-        <v>4.7327148947617897E-6</v>
+        <v>-7.6112748556267395E-4</v>
       </c>
       <c r="CF5" s="36">
         <v>5.0094900276922098E-3</v>
@@ -1823,25 +1822,25 @@
         <v>8.2057408746502303E-3</v>
       </c>
       <c r="CJ5" s="36">
-        <v>5.8519236986744301E-3</v>
+        <v>4.8807292003361603E-3</v>
       </c>
       <c r="CK5" s="36">
-        <v>5.0833995234312902E-3</v>
+        <v>1.08068475246262E-2</v>
       </c>
       <c r="CL5" s="36">
-        <v>5.8519236986744301E-3</v>
+        <v>4.8807292003361603E-3</v>
       </c>
       <c r="CM5" s="36">
-        <v>-2.3538171759758101E-3</v>
+        <v>-3.3250116743140799E-3</v>
       </c>
       <c r="CN5" s="36">
-        <v>8.2057408746502303E-3</v>
+        <v>4.1879795396419402E-3</v>
       </c>
       <c r="CO5" s="36">
-        <v>5.8519236986744301E-3</v>
+        <v>4.8807292003361603E-3</v>
       </c>
       <c r="CP5" s="36">
-        <v>-2.3538171759758101E-3</v>
+        <v>6.92749660694212E-4</v>
       </c>
     </row>
     <row r="6" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1882,19 +1881,19 @@
         <v>34</v>
       </c>
       <c r="M6" s="47">
-        <v>-1.2006859207729099E-2</v>
+        <v>1.3097675512343801E-2</v>
       </c>
       <c r="N6" s="48">
-        <v>3.2678607169711299E-2</v>
+        <v>1.3097675512343801E-2</v>
       </c>
       <c r="O6" s="48">
-        <v>-4.4685466377440301E-2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="48">
-        <v>3.3314760820291903E-2</v>
+        <v>8.0328048558401307E-3</v>
       </c>
       <c r="Q6" s="48">
-        <v>-2.13079016125629E-2</v>
+        <v>-2.11304803681838E-2</v>
       </c>
       <c r="R6" s="36">
         <v>0.21222130470685399</v>
@@ -1909,25 +1908,25 @@
         <v>0.254553339115351</v>
       </c>
       <c r="V6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="W6" s="36">
-        <v>0.246420824295011</v>
+        <v>0.19427780341485901</v>
       </c>
       <c r="X6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="Y6" s="36">
-        <v>-1.2006859207729099E-2</v>
+        <v>1.3097675512343801E-2</v>
       </c>
       <c r="Z6" s="36">
-        <v>0.254553339115351</v>
+        <v>0.22022022022022</v>
       </c>
       <c r="AA6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="AB6" s="36">
-        <v>-2.01393740280695E-2</v>
+        <v>-1.2844741293017201E-2</v>
       </c>
       <c r="AC6" s="36">
         <v>0.21222130470685399</v>
@@ -1942,25 +1941,25 @@
         <v>0.20468343451864701</v>
       </c>
       <c r="AG6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="AH6" s="36">
-        <v>0.20173535791757</v>
+        <v>0.19427780341485901</v>
       </c>
       <c r="AI6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="AJ6" s="36">
-        <v>3.2678607169711299E-2</v>
+        <v>1.3097675512343801E-2</v>
       </c>
       <c r="AK6" s="36">
-        <v>0.20468343451864701</v>
+        <v>0.22022022022022</v>
       </c>
       <c r="AL6" s="36">
-        <v>0.23441396508728199</v>
+        <v>0.20737547892720301</v>
       </c>
       <c r="AM6" s="36">
-        <v>2.9730530568634801E-2</v>
+        <v>-1.2844741293017201E-2</v>
       </c>
       <c r="AN6" s="36">
         <v>0</v>
@@ -1978,22 +1977,22 @@
         <v>0</v>
       </c>
       <c r="AS6" s="36">
-        <v>4.4685466377440301E-2</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="36">
         <v>0</v>
       </c>
       <c r="AU6" s="36">
-        <v>-4.4685466377440301E-2</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="36">
-        <v>4.98699045967042E-2</v>
+        <v>0</v>
       </c>
       <c r="AW6" s="36">
         <v>0</v>
       </c>
       <c r="AX6" s="36">
-        <v>-4.98699045967042E-2</v>
+        <v>0</v>
       </c>
       <c r="AY6" s="36">
         <v>0.68166804293971905</v>
@@ -2008,25 +2007,25 @@
         <v>0.65915004336513405</v>
       </c>
       <c r="BC6" s="36">
-        <v>0.67930174563590995</v>
+        <v>0.68869731800766298</v>
       </c>
       <c r="BD6" s="36">
-        <v>0.645986984815618</v>
+        <v>0.68066451315182297</v>
       </c>
       <c r="BE6" s="36">
-        <v>0.67930174563590995</v>
+        <v>0.68869731800766298</v>
       </c>
       <c r="BF6" s="36">
-        <v>3.3314760820291903E-2</v>
+        <v>8.0328048558401307E-3</v>
       </c>
       <c r="BG6" s="36">
-        <v>0.65915004336513405</v>
+        <v>0.64564564564564597</v>
       </c>
       <c r="BH6" s="36">
-        <v>0.67930174563590995</v>
+        <v>0.68869731800766298</v>
       </c>
       <c r="BI6" s="37">
-        <v>2.0151702270775802E-2</v>
+        <v>4.30516723620172E-2</v>
       </c>
       <c r="BJ6" s="36">
         <v>0.106110652353427</v>
@@ -2041,25 +2040,25 @@
         <v>8.6296617519514299E-2</v>
       </c>
       <c r="BN6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="BO6" s="36">
-        <v>0.107592190889371</v>
+        <v>0.125057683433318</v>
       </c>
       <c r="BP6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="BQ6" s="37">
-        <v>-2.13079016125629E-2</v>
+        <v>-2.11304803681838E-2</v>
       </c>
       <c r="BR6" s="36">
-        <v>8.6296617519514299E-2</v>
+        <v>0.134134134134134</v>
       </c>
       <c r="BS6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="BT6" s="36">
-        <v>-1.23282427063331E-5</v>
+        <v>-3.0206931069E-2</v>
       </c>
       <c r="BU6" s="36">
         <v>0.106110652353427</v>
@@ -2074,25 +2073,25 @@
         <v>8.6296617519514299E-2</v>
       </c>
       <c r="BY6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="BZ6" s="36">
-        <v>0.107592190889371</v>
+        <v>0.125057683433318</v>
       </c>
       <c r="CA6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="CB6" s="36">
-        <v>-1.23282427063331E-5</v>
+        <v>1.76305855456198E-2</v>
       </c>
       <c r="CC6" s="36">
-        <v>8.6296617519514299E-2</v>
+        <v>0.134134134134134</v>
       </c>
       <c r="CD6" s="36">
-        <v>8.6284289276807993E-2</v>
+        <v>0.10392720306513401</v>
       </c>
       <c r="CE6" s="36">
-        <v>-1.23282427063331E-5</v>
+        <v>-3.0206931069E-2</v>
       </c>
       <c r="CF6" s="36">
         <v>0</v>
@@ -2166,19 +2165,19 @@
         <v>34</v>
       </c>
       <c r="M7" s="47">
-        <v>-1.0516736959945899E-2</v>
+        <v>2.1580740583886499E-2</v>
       </c>
       <c r="N7" s="48">
-        <v>-2.12140885955663E-2</v>
+        <v>4.8619815903059499E-2</v>
       </c>
       <c r="O7" s="48">
-        <v>1.06973516356205E-2</v>
+        <v>-2.7039075319173E-2</v>
       </c>
       <c r="P7" s="48">
-        <v>1.46543317148523E-2</v>
+        <v>-2.7511283288776601E-2</v>
       </c>
       <c r="Q7" s="48">
-        <v>-4.1375947549064304E-3</v>
+        <v>5.9305427048900704E-3</v>
       </c>
       <c r="R7" s="36">
         <v>0.617042775345234</v>
@@ -2193,25 +2192,25 @@
         <v>0.55907746895328203</v>
       </c>
       <c r="V7" s="36">
-        <v>0.56932471264367801</v>
+        <v>0.57909166766003095</v>
       </c>
       <c r="W7" s="36">
-        <v>0.57984144960362405</v>
+        <v>0.55751092707614402</v>
       </c>
       <c r="X7" s="36">
-        <v>0.56932471264367801</v>
+        <v>0.57909166766003095</v>
       </c>
       <c r="Y7" s="36">
-        <v>-1.0516736959945899E-2</v>
+        <v>2.1580740583886499E-2</v>
       </c>
       <c r="Z7" s="36">
-        <v>0.55907746895328203</v>
+        <v>0.57289033345371398</v>
       </c>
       <c r="AA7" s="36">
-        <v>0.56932471264367801</v>
+        <v>0.57909166766003095</v>
       </c>
       <c r="AB7" s="36">
-        <v>1.0247243690396099E-2</v>
+        <v>6.2013342063171901E-3</v>
       </c>
       <c r="AC7" s="36">
         <v>0.51650387335803305</v>
@@ -2226,25 +2225,25 @@
         <v>0.45156712004730898</v>
       </c>
       <c r="AG7" s="36">
-        <v>0.453304597701149</v>
+        <v>0.48754321134819401</v>
       </c>
       <c r="AH7" s="36">
-        <v>0.47451868629671601</v>
+        <v>0.43892339544513498</v>
       </c>
       <c r="AI7" s="36">
-        <v>0.453304597701149</v>
+        <v>0.48754321134819401</v>
       </c>
       <c r="AJ7" s="36">
-        <v>-2.12140885955663E-2</v>
+        <v>4.8619815903059499E-2</v>
       </c>
       <c r="AK7" s="36">
-        <v>0.45156712004730898</v>
+        <v>0.474178403755869</v>
       </c>
       <c r="AL7" s="36">
-        <v>0.453304597701149</v>
+        <v>0.48754321134819401</v>
       </c>
       <c r="AM7" s="36">
-        <v>1.7374776538401401E-3</v>
+        <v>1.3364807592325501E-2</v>
       </c>
       <c r="AN7" s="36">
         <v>0.100538901987201</v>
@@ -2259,25 +2258,25 @@
         <v>0.107510348905973</v>
       </c>
       <c r="AR7" s="36">
-        <v>0.11602011494252901</v>
+        <v>9.1548456311836904E-2</v>
       </c>
       <c r="AS7" s="36">
-        <v>0.105322763306908</v>
+        <v>0.11858753163101</v>
       </c>
       <c r="AT7" s="36">
-        <v>0.11602011494252901</v>
+        <v>9.1548456311836904E-2</v>
       </c>
       <c r="AU7" s="36">
-        <v>1.06973516356205E-2</v>
+        <v>-2.7039075319173E-2</v>
       </c>
       <c r="AV7" s="36">
-        <v>0.107510348905973</v>
+        <v>9.8711929697845202E-2</v>
       </c>
       <c r="AW7" s="36">
-        <v>0.11602011494252901</v>
+        <v>9.1548456311836904E-2</v>
       </c>
       <c r="AX7" s="37">
-        <v>8.5097660365559304E-3</v>
+        <v>-7.1634733860082601E-3</v>
       </c>
       <c r="AY7" s="36">
         <v>0.337318962613675</v>
@@ -2292,25 +2291,25 @@
         <v>0.38888231815493801</v>
       </c>
       <c r="BC7" s="36">
-        <v>0.38158524904214602</v>
+        <v>0.356776731434021</v>
       </c>
       <c r="BD7" s="36">
-        <v>0.36693091732729299</v>
+        <v>0.384288014722797</v>
       </c>
       <c r="BE7" s="36">
-        <v>0.38158524904214602</v>
+        <v>0.356776731434021</v>
       </c>
       <c r="BF7" s="37">
-        <v>1.46543317148523E-2</v>
+        <v>-2.7511283288776601E-2</v>
       </c>
       <c r="BG7" s="36">
-        <v>0.38888231815493801</v>
+        <v>0.36222462983026399</v>
       </c>
       <c r="BH7" s="36">
-        <v>0.38158524904214602</v>
+        <v>0.356776731434021</v>
       </c>
       <c r="BI7" s="37">
-        <v>-7.2970691127923204E-3</v>
+        <v>-5.4478983962429296E-3</v>
       </c>
       <c r="BJ7" s="36">
         <v>4.5638262041091303E-2</v>
@@ -2325,25 +2324,25 @@
         <v>5.2040212891779999E-2</v>
       </c>
       <c r="BN7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>6.4131600905948299E-2</v>
       </c>
       <c r="BO7" s="36">
-        <v>5.3227633069082701E-2</v>
+        <v>5.8201058201058198E-2</v>
       </c>
       <c r="BP7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>6.4131600905948299E-2</v>
       </c>
       <c r="BQ7" s="36">
-        <v>-4.1375947549064304E-3</v>
+        <v>5.9305427048900704E-3</v>
       </c>
       <c r="BR7" s="36">
-        <v>5.2040212891779999E-2</v>
+        <v>6.4885036716022595E-2</v>
       </c>
       <c r="BS7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>6.4131600905948299E-2</v>
       </c>
       <c r="BT7" s="36">
-        <v>-2.9501745776037698E-3</v>
+        <v>-7.5343581007436501E-4</v>
       </c>
       <c r="BU7" s="36">
         <v>4.5638262041091303E-2</v>
@@ -2358,25 +2357,25 @@
         <v>5.2040212891779999E-2</v>
       </c>
       <c r="BY7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>4.9946358326379801E-2</v>
       </c>
       <c r="BZ7" s="36">
-        <v>5.3227633069082701E-2</v>
+        <v>5.8201058201058198E-2</v>
       </c>
       <c r="CA7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>4.9946358326379801E-2</v>
       </c>
       <c r="CB7" s="37">
-        <v>-2.9501745776037698E-3</v>
+        <v>-2.0938545654002301E-3</v>
       </c>
       <c r="CC7" s="36">
-        <v>5.2040212891779999E-2</v>
+        <v>5.16431924882629E-2</v>
       </c>
       <c r="CD7" s="36">
-        <v>4.9090038314176201E-2</v>
+        <v>4.9946358326379801E-2</v>
       </c>
       <c r="CE7" s="36">
-        <v>-2.9501745776037698E-3</v>
+        <v>-1.6968341618831301E-3</v>
       </c>
       <c r="CF7" s="36">
         <v>0</v>
@@ -2391,25 +2390,25 @@
         <v>0</v>
       </c>
       <c r="CJ7" s="36">
-        <v>0</v>
+        <v>1.41852425795685E-2</v>
       </c>
       <c r="CK7" s="36">
         <v>0</v>
       </c>
       <c r="CL7" s="36">
-        <v>0</v>
+        <v>1.41852425795685E-2</v>
       </c>
       <c r="CM7" s="36">
-        <v>0</v>
+        <v>1.41852425795685E-2</v>
       </c>
       <c r="CN7" s="36">
-        <v>0</v>
+        <v>1.3241844227759701E-2</v>
       </c>
       <c r="CO7" s="36">
-        <v>0</v>
+        <v>1.41852425795685E-2</v>
       </c>
       <c r="CP7" s="36">
-        <v>0</v>
+        <v>9.4339835180876205E-4</v>
       </c>
     </row>
     <row r="8" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2450,19 +2449,19 @@
         <v>34</v>
       </c>
       <c r="M8" s="47">
-        <v>1.22535923659816E-2</v>
+        <v>-2.0190418332406299E-2</v>
       </c>
       <c r="N8" s="48">
-        <v>1.7287536022529901E-2</v>
+        <v>-7.3422466762171302E-3</v>
       </c>
       <c r="O8" s="48">
-        <v>-5.0339436565482697E-3</v>
+        <v>-1.28481716561892E-2</v>
       </c>
       <c r="P8" s="48">
-        <v>-7.1791640171222602E-3</v>
+        <v>5.1986499869018897E-3</v>
       </c>
       <c r="Q8" s="48">
-        <v>-5.0744283488594099E-3</v>
+        <v>1.49917683455043E-2</v>
       </c>
       <c r="R8" s="36">
         <v>0.39028397089884997</v>
@@ -2477,25 +2476,25 @@
         <v>0.37792854871196901</v>
       </c>
       <c r="V8" s="36">
-        <v>0.38772819472616599</v>
+        <v>0.373674360573924</v>
       </c>
       <c r="W8" s="36">
-        <v>0.37547460236018498</v>
+        <v>0.39386477890632998</v>
       </c>
       <c r="X8" s="36">
-        <v>0.38772819472616599</v>
+        <v>0.373674360573924</v>
       </c>
       <c r="Y8" s="36">
-        <v>1.22535923659816E-2</v>
+        <v>-2.0190418332406299E-2</v>
       </c>
       <c r="Z8" s="36">
-        <v>0.37792854871196901</v>
+        <v>0.38422312415443899</v>
       </c>
       <c r="AA8" s="36">
-        <v>0.38772819472616599</v>
+        <v>0.373674360573924</v>
       </c>
       <c r="AB8" s="36">
-        <v>9.7996460141976903E-3</v>
+        <v>-1.05487635805147E-2</v>
       </c>
       <c r="AC8" s="36">
         <v>0.360596104200892</v>
@@ -2510,25 +2509,25 @@
         <v>0.35683239690448398</v>
       </c>
       <c r="AG8" s="36">
-        <v>0.36115618661257598</v>
+        <v>0.344458307340403</v>
       </c>
       <c r="AH8" s="36">
-        <v>0.34386865059004601</v>
+        <v>0.35180055401662103</v>
       </c>
       <c r="AI8" s="36">
-        <v>0.36115618661257598</v>
+        <v>0.344458307340403</v>
       </c>
       <c r="AJ8" s="36">
-        <v>1.7287536022529901E-2</v>
+        <v>-7.3422466762171302E-3</v>
       </c>
       <c r="AK8" s="36">
-        <v>0.35683239690448398</v>
+        <v>0.355812259340202</v>
       </c>
       <c r="AL8" s="36">
-        <v>0.36115618661257598</v>
+        <v>0.344458307340403</v>
       </c>
       <c r="AM8" s="36">
-        <v>4.3237897080918297E-3</v>
+        <v>-1.13539519997985E-2</v>
       </c>
       <c r="AN8" s="36">
         <v>2.9687866697958198E-2</v>
@@ -2543,25 +2542,25 @@
         <v>2.1096151807484399E-2</v>
       </c>
       <c r="AR8" s="36">
-        <v>2.6572008113590301E-2</v>
+        <v>2.92160532335205E-2</v>
       </c>
       <c r="AS8" s="36">
-        <v>3.1605951770138502E-2</v>
+        <v>4.2064224889709699E-2</v>
       </c>
       <c r="AT8" s="36">
-        <v>2.6572008113590301E-2</v>
+        <v>2.92160532335205E-2</v>
       </c>
       <c r="AU8" s="36">
-        <v>-5.0339436565482697E-3</v>
+        <v>-1.28481716561892E-2</v>
       </c>
       <c r="AV8" s="36">
-        <v>2.1096151807484399E-2</v>
+        <v>2.84108648142367E-2</v>
       </c>
       <c r="AW8" s="36">
-        <v>2.6572008113590301E-2</v>
+        <v>2.92160532335205E-2</v>
       </c>
       <c r="AX8" s="36">
-        <v>5.4758563061058996E-3</v>
+        <v>8.0518841928382801E-4</v>
       </c>
       <c r="AY8" s="36">
         <v>0.51842290542126301</v>
@@ -2576,25 +2575,25 @@
         <v>0.52528357892504995</v>
       </c>
       <c r="BC8" s="36">
-        <v>0.52139959432048699</v>
+        <v>0.53233520482428798</v>
       </c>
       <c r="BD8" s="36">
-        <v>0.52857875833760903</v>
+        <v>0.52713655483738597</v>
       </c>
       <c r="BE8" s="36">
-        <v>0.52139959432048699</v>
+        <v>0.53233520482428798</v>
       </c>
       <c r="BF8" s="36">
-        <v>-7.1791640171222602E-3</v>
+        <v>5.1986499869018897E-3</v>
       </c>
       <c r="BG8" s="36">
-        <v>0.52528357892504995</v>
+        <v>0.52315537516911204</v>
       </c>
       <c r="BH8" s="36">
-        <v>0.52139959432048699</v>
+        <v>0.53233520482428798</v>
       </c>
       <c r="BI8" s="37">
-        <v>-3.8839846045636301E-3</v>
+        <v>9.1798296551754994E-3</v>
       </c>
       <c r="BJ8" s="36">
         <v>9.1293123679887303E-2</v>
@@ -2609,25 +2608,25 @@
         <v>9.6787872362981003E-2</v>
       </c>
       <c r="BN8" s="36">
-        <v>9.0872210953346896E-2</v>
+        <v>9.3990434601788297E-2</v>
       </c>
       <c r="BO8" s="36">
-        <v>9.5946639302206302E-2</v>
+        <v>7.8998666256284003E-2</v>
       </c>
       <c r="BP8" s="36">
-        <v>9.0872210953346896E-2</v>
+        <v>9.3990434601788297E-2</v>
       </c>
       <c r="BQ8" s="37">
-        <v>-5.0744283488594099E-3</v>
+        <v>1.49917683455043E-2</v>
       </c>
       <c r="BR8" s="36">
-        <v>9.6787872362981003E-2</v>
+        <v>9.2621500676449198E-2</v>
       </c>
       <c r="BS8" s="36">
-        <v>9.0872210953346896E-2</v>
+        <v>9.3990434601788297E-2</v>
       </c>
       <c r="BT8" s="37">
-        <v>-5.9156614096341599E-3</v>
+        <v>1.36893392533916E-3</v>
       </c>
       <c r="BU8" s="36">
         <v>9.1293123679887303E-2</v>
@@ -2642,25 +2641,25 @@
         <v>7.7917947630658305E-2</v>
       </c>
       <c r="BY8" s="36">
-        <v>7.5557809330628806E-2</v>
+        <v>8.0370139322104406E-2</v>
       </c>
       <c r="BZ8" s="36">
-        <v>8.2606464853771197E-2</v>
+        <v>7.8998666256284003E-2</v>
       </c>
       <c r="CA8" s="36">
-        <v>7.5557809330628806E-2</v>
+        <v>8.0370139322104406E-2</v>
       </c>
       <c r="CB8" s="37">
-        <v>-2.3601383000295302E-3</v>
+        <v>2.45219169144606E-3</v>
       </c>
       <c r="CC8" s="36">
-        <v>7.7917947630658305E-2</v>
+        <v>8.0029139348527401E-2</v>
       </c>
       <c r="CD8" s="36">
-        <v>7.5557809330628806E-2</v>
+        <v>8.0370139322104406E-2</v>
       </c>
       <c r="CE8" s="37">
-        <v>-2.3601383000295302E-3</v>
+        <v>3.4099997357696398E-4</v>
       </c>
       <c r="CF8" s="36">
         <v>0</v>
@@ -2675,25 +2674,25 @@
         <v>1.8869924732322699E-2</v>
       </c>
       <c r="CJ8" s="36">
-        <v>1.5314401622718099E-2</v>
+        <v>1.36202952796839E-2</v>
       </c>
       <c r="CK8" s="36">
-        <v>1.33401744484351E-2</v>
+        <v>0</v>
       </c>
       <c r="CL8" s="36">
-        <v>1.5314401622718099E-2</v>
+        <v>1.36202952796839E-2</v>
       </c>
       <c r="CM8" s="36">
-        <v>-3.5555231096046401E-3</v>
+        <v>-5.2496294526387698E-3</v>
       </c>
       <c r="CN8" s="36">
-        <v>1.8869924732322699E-2</v>
+        <v>1.25923613279217E-2</v>
       </c>
       <c r="CO8" s="36">
-        <v>1.5314401622718099E-2</v>
+        <v>1.36202952796839E-2</v>
       </c>
       <c r="CP8" s="36">
-        <v>-3.5555231096046401E-3</v>
+        <v>1.0279339517621901E-3</v>
       </c>
     </row>
     <row r="9" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2734,19 +2733,19 @@
         <v>34</v>
       </c>
       <c r="M9" s="47">
-        <v>-6.5836847325302398E-3</v>
+        <v>2.4140657242445701E-3</v>
       </c>
       <c r="N9" s="48">
-        <v>-4.3551213945083801E-2</v>
+        <v>2.4140657242445701E-3</v>
       </c>
       <c r="O9" s="48">
-        <v>3.6967529212553599E-2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="48">
-        <v>2.2525540649444301E-2</v>
+        <v>2.3933476867897298E-3</v>
       </c>
       <c r="Q9" s="48">
-        <v>-1.5941855916914102E-2</v>
+        <v>-4.8074134110342604E-3</v>
       </c>
       <c r="R9" s="36">
         <v>0.5</v>
@@ -2761,25 +2760,25 @@
         <v>0.44923258559622198</v>
       </c>
       <c r="V9" s="36">
-        <v>0.455864570737606</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="W9" s="36">
-        <v>0.46244825547013602</v>
+        <v>0.44874274661508701</v>
       </c>
       <c r="X9" s="36">
-        <v>0.455864570737606</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="Y9" s="36">
-        <v>-6.5836847325302398E-3</v>
+        <v>2.4140657242445701E-3</v>
       </c>
       <c r="Z9" s="36">
-        <v>0.44923258559622198</v>
+        <v>0.45781556572923499</v>
       </c>
       <c r="AA9" s="36">
-        <v>0.455864570737606</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="AB9" s="36">
-        <v>6.6319851413837996E-3</v>
+        <v>-6.6587533899031799E-3</v>
       </c>
       <c r="AC9" s="36">
         <v>0.5</v>
@@ -2794,25 +2793,25 @@
         <v>0.38961038961039002</v>
       </c>
       <c r="AG9" s="36">
-        <v>0.36094316807738802</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="AH9" s="36">
-        <v>0.40449438202247201</v>
+        <v>0.44874274661508701</v>
       </c>
       <c r="AI9" s="36">
-        <v>0.36094316807738802</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="AJ9" s="36">
-        <v>-4.3551213945083801E-2</v>
+        <v>2.4140657242445701E-3</v>
       </c>
       <c r="AK9" s="36">
-        <v>0.38961038961039002</v>
+        <v>0.45781556572923499</v>
       </c>
       <c r="AL9" s="36">
-        <v>0.36094316807738802</v>
+        <v>0.45115681233933203</v>
       </c>
       <c r="AM9" s="36">
-        <v>-2.86672215330015E-2</v>
+        <v>-6.6587533899031799E-3</v>
       </c>
       <c r="AN9" s="36">
         <v>0</v>
@@ -2827,25 +2826,25 @@
         <v>5.9622195985832301E-2</v>
       </c>
       <c r="AR9" s="36">
-        <v>9.4921402660217702E-2</v>
+        <v>0</v>
       </c>
       <c r="AS9" s="36">
-        <v>5.7953873447664103E-2</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="36">
-        <v>9.4921402660217702E-2</v>
+        <v>0</v>
       </c>
       <c r="AU9" s="36">
-        <v>3.6967529212553599E-2</v>
+        <v>0</v>
       </c>
       <c r="AV9" s="36">
-        <v>5.9622195985832301E-2</v>
+        <v>0</v>
       </c>
       <c r="AW9" s="36">
-        <v>9.4921402660217702E-2</v>
+        <v>0</v>
       </c>
       <c r="AX9" s="37">
-        <v>3.5299206674385297E-2</v>
+        <v>0</v>
       </c>
       <c r="AY9" s="36">
         <v>0.39113924050632898</v>
@@ -2860,25 +2859,25 @@
         <v>0.46103896103896103</v>
       </c>
       <c r="BC9" s="36">
-        <v>0.46191051995163201</v>
+        <v>0.45758354755784098</v>
       </c>
       <c r="BD9" s="36">
-        <v>0.43938497930218801</v>
+        <v>0.45519019987105103</v>
       </c>
       <c r="BE9" s="36">
-        <v>0.46191051995163201</v>
+        <v>0.45758354755784098</v>
       </c>
       <c r="BF9" s="37">
-        <v>2.2525540649444301E-2</v>
+        <v>2.3933476867897298E-3</v>
       </c>
       <c r="BG9" s="36">
-        <v>0.46103896103896103</v>
+        <v>0.47089601046435597</v>
       </c>
       <c r="BH9" s="36">
-        <v>0.46191051995163201</v>
+        <v>0.45758354755784098</v>
       </c>
       <c r="BI9" s="37">
-        <v>8.7155891267137698E-4</v>
+        <v>-1.33124629065152E-2</v>
       </c>
       <c r="BJ9" s="36">
         <v>0.10886075949367099</v>
@@ -2893,25 +2892,25 @@
         <v>8.9728453364816996E-2</v>
       </c>
       <c r="BN9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="BO9" s="36">
-        <v>9.8166765227675895E-2</v>
+        <v>9.6067053513861994E-2</v>
       </c>
       <c r="BP9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="BQ9" s="37">
-        <v>-1.5941855916914102E-2</v>
+        <v>-4.8074134110342604E-3</v>
       </c>
       <c r="BR9" s="36">
-        <v>8.9728453364816996E-2</v>
+        <v>7.1288423806409401E-2</v>
       </c>
       <c r="BS9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="BT9" s="36">
-        <v>-7.50354405405521E-3</v>
+        <v>1.99712162964183E-2</v>
       </c>
       <c r="BU9" s="36">
         <v>0.10886075949367099</v>
@@ -2926,25 +2925,25 @@
         <v>8.9728453364816996E-2</v>
       </c>
       <c r="BY9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="BZ9" s="36">
-        <v>9.8166765227675895E-2</v>
+        <v>9.6067053513861994E-2</v>
       </c>
       <c r="CA9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="CB9" s="37">
-        <v>-7.50354405405521E-3</v>
+        <v>1.53118673801077E-3</v>
       </c>
       <c r="CC9" s="36">
-        <v>8.9728453364816996E-2</v>
+        <v>7.1288423806409401E-2</v>
       </c>
       <c r="CD9" s="36">
-        <v>8.2224909310761804E-2</v>
+        <v>9.1259640102827805E-2</v>
       </c>
       <c r="CE9" s="36">
-        <v>-7.50354405405521E-3</v>
+        <v>1.99712162964183E-2</v>
       </c>
       <c r="CF9" s="36">
         <v>0</v>
@@ -3018,19 +3017,19 @@
         <v>34</v>
       </c>
       <c r="M10" s="47">
-        <v>2.23501277300545E-2</v>
+        <v>4.2514046184446701E-2</v>
       </c>
       <c r="N10" s="48">
-        <v>1.83009145632314E-2</v>
+        <v>-2.46413096916469E-2</v>
       </c>
       <c r="O10" s="48">
-        <v>4.0492131668230704E-3</v>
+        <v>6.71553558760936E-2</v>
       </c>
       <c r="P10" s="48">
-        <v>-1.50362286147405E-2</v>
+        <v>-5.9529138377879799E-2</v>
       </c>
       <c r="Q10" s="48">
-        <v>-7.3138991153139698E-3</v>
+        <v>1.7015092193433098E-2</v>
       </c>
       <c r="R10" s="36">
         <v>0.32198883275724499</v>
@@ -3045,25 +3044,25 @@
         <v>0.339290208910143</v>
       </c>
       <c r="V10" s="36">
-        <v>0.33159722222222199</v>
+        <v>0.35493024355639602</v>
       </c>
       <c r="W10" s="36">
-        <v>0.30924709449216797</v>
+        <v>0.31241619737194998</v>
       </c>
       <c r="X10" s="36">
-        <v>0.33159722222222199</v>
+        <v>0.35493024355639602</v>
       </c>
       <c r="Y10" s="36">
-        <v>2.23501277300545E-2</v>
+        <v>4.2514046184446701E-2</v>
       </c>
       <c r="Z10" s="36">
-        <v>0.339290208910143</v>
+        <v>0.32437185929648199</v>
       </c>
       <c r="AA10" s="36">
-        <v>0.33159722222222199</v>
+        <v>0.35493024355639602</v>
       </c>
       <c r="AB10" s="36">
-        <v>-7.6929866879212301E-3</v>
+        <v>3.05583842599139E-2</v>
       </c>
       <c r="AC10" s="36">
         <v>0.28263759638393998</v>
@@ -3078,25 +3077,25 @@
         <v>0.28064434935816801</v>
       </c>
       <c r="AG10" s="36">
-        <v>0.29141865079365098</v>
+        <v>0.28777488768030302</v>
       </c>
       <c r="AH10" s="36">
-        <v>0.27311773623041902</v>
+        <v>0.31241619737194998</v>
       </c>
       <c r="AI10" s="36">
-        <v>0.29141865079365098</v>
+        <v>0.28777488768030302</v>
       </c>
       <c r="AJ10" s="36">
-        <v>1.83009145632314E-2</v>
+        <v>-2.46413096916469E-2</v>
       </c>
       <c r="AK10" s="36">
-        <v>0.28064434935816801</v>
+        <v>0.27512562814070401</v>
       </c>
       <c r="AL10" s="36">
-        <v>0.29141865079365098</v>
+        <v>0.28777488768030302</v>
       </c>
       <c r="AM10" s="36">
-        <v>1.07743014354832E-2</v>
+        <v>1.26492595395992E-2</v>
       </c>
       <c r="AN10" s="36">
         <v>3.9351236373305003E-2</v>
@@ -3111,25 +3110,25 @@
         <v>5.86458595519758E-2</v>
       </c>
       <c r="AR10" s="36">
-        <v>4.0178571428571397E-2</v>
+        <v>6.71553558760936E-2</v>
       </c>
       <c r="AS10" s="36">
-        <v>3.6129358261748401E-2</v>
+        <v>0</v>
       </c>
       <c r="AT10" s="36">
-        <v>4.0178571428571397E-2</v>
+        <v>6.71553558760936E-2</v>
       </c>
       <c r="AU10" s="37">
-        <v>4.0492131668230704E-3</v>
+        <v>6.71553558760936E-2</v>
       </c>
       <c r="AV10" s="36">
-        <v>5.86458595519758E-2</v>
+        <v>4.9246231155778898E-2</v>
       </c>
       <c r="AW10" s="36">
-        <v>4.0178571428571397E-2</v>
+        <v>6.71553558760936E-2</v>
       </c>
       <c r="AX10" s="37">
-        <v>-1.84672881234044E-2</v>
+        <v>1.7909124720314799E-2</v>
       </c>
       <c r="AY10" s="36">
         <v>0.471151289550651</v>
@@ -3144,25 +3143,25 @@
         <v>0.476969544424868</v>
       </c>
       <c r="BC10" s="36">
-        <v>0.47991071428571402</v>
+        <v>0.44596831402222697</v>
       </c>
       <c r="BD10" s="36">
-        <v>0.49494694290045499</v>
+        <v>0.50549745240010702</v>
       </c>
       <c r="BE10" s="36">
-        <v>0.47991071428571402</v>
+        <v>0.44596831402222697</v>
       </c>
       <c r="BF10" s="36">
-        <v>-1.50362286147405E-2</v>
+        <v>-5.9529138377879799E-2</v>
       </c>
       <c r="BG10" s="36">
-        <v>0.476969544424868</v>
+        <v>0.46180904522613098</v>
       </c>
       <c r="BH10" s="36">
-        <v>0.47991071428571402</v>
+        <v>0.44596831402222697</v>
       </c>
       <c r="BI10" s="36">
-        <v>2.9411698608464701E-3</v>
+        <v>-1.58407312039032E-2</v>
       </c>
       <c r="BJ10" s="36">
         <v>0.20685987769210301</v>
@@ -3177,25 +3176,25 @@
         <v>0.183740246664989</v>
       </c>
       <c r="BN10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="BO10" s="36">
-        <v>0.19580596260737701</v>
+        <v>0.18208635022794301</v>
       </c>
       <c r="BP10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="BQ10" s="37">
-        <v>-7.3138991153139698E-3</v>
+        <v>1.7015092193433098E-2</v>
       </c>
       <c r="BR10" s="36">
-        <v>0.183740246664989</v>
+        <v>0.21381909547738701</v>
       </c>
       <c r="BS10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="BT10" s="37">
-        <v>4.7518168270748199E-3</v>
+        <v>-1.47176530560107E-2</v>
       </c>
       <c r="BU10" s="36">
         <v>0.20685987769210301</v>
@@ -3210,25 +3209,25 @@
         <v>0.183740246664989</v>
       </c>
       <c r="BY10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="BZ10" s="36">
-        <v>0.19580596260737701</v>
+        <v>0.18208635022794301</v>
       </c>
       <c r="CA10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="CB10" s="37">
-        <v>4.7518168270748199E-3</v>
+        <v>1.5361195756387501E-2</v>
       </c>
       <c r="CC10" s="36">
-        <v>0.183740246664989</v>
+        <v>0.21381909547738701</v>
       </c>
       <c r="CD10" s="36">
-        <v>0.18849206349206299</v>
+        <v>0.19910144242137601</v>
       </c>
       <c r="CE10" s="37">
-        <v>4.7518168270748199E-3</v>
+        <v>-1.47176530560107E-2</v>
       </c>
       <c r="CF10" s="36">
         <v>0</v>
@@ -3302,19 +3301,19 @@
         <v>78</v>
       </c>
       <c r="M11" s="47">
-        <v>-2.6862828331967702E-3</v>
+        <v>1.4699170311483401E-2</v>
       </c>
       <c r="N11" s="48">
-        <v>1.7645102449021299E-2</v>
+        <v>2.0466462039991799E-2</v>
       </c>
       <c r="O11" s="48">
-        <v>-2.0331385282217999E-2</v>
+        <v>-5.7672917285083404E-3</v>
       </c>
       <c r="P11" s="48">
-        <v>-5.6230721297594903E-3</v>
+        <v>-4.2803926371350904E-3</v>
       </c>
       <c r="Q11" s="48">
-        <v>8.3093549629562301E-3</v>
+        <v>-1.0418777674348401E-2</v>
       </c>
       <c r="R11" s="36">
         <v>0.35317611259033899</v>
@@ -3329,25 +3328,25 @@
         <v>0.37996289424860902</v>
       </c>
       <c r="V11" s="36">
-        <v>0.39529235942462199</v>
+        <v>0.39037133793618201</v>
       </c>
       <c r="W11" s="36">
-        <v>0.39797864225781798</v>
+        <v>0.37567216762469902</v>
       </c>
       <c r="X11" s="36">
-        <v>0.39529235942462199</v>
+        <v>0.39037133793618201</v>
       </c>
       <c r="Y11" s="36">
-        <v>-2.6862828331967702E-3</v>
+        <v>1.4699170311483401E-2</v>
       </c>
       <c r="Z11" s="36">
-        <v>0.37996289424860902</v>
+        <v>0.39340942562592002</v>
       </c>
       <c r="AA11" s="36">
-        <v>0.39529235942462199</v>
+        <v>0.39037133793618201</v>
       </c>
       <c r="AB11" s="36">
-        <v>1.5329465176013199E-2</v>
+        <v>-3.0380876897383399E-3</v>
       </c>
       <c r="AC11" s="36">
         <v>0.28756181057436297</v>
@@ -3362,25 +3361,25 @@
         <v>0.31539888682745798</v>
       </c>
       <c r="AG11" s="36">
-        <v>0.33457874089295703</v>
+        <v>0.33457734651987298</v>
       </c>
       <c r="AH11" s="36">
-        <v>0.31693363844393602</v>
+        <v>0.314110884479881</v>
       </c>
       <c r="AI11" s="36">
-        <v>0.33457874089295703</v>
+        <v>0.33457734651987298</v>
       </c>
       <c r="AJ11" s="36">
-        <v>1.7645102449021299E-2</v>
+        <v>2.0466462039991799E-2</v>
       </c>
       <c r="AK11" s="36">
-        <v>0.31539888682745798</v>
+        <v>0.326583210603829</v>
       </c>
       <c r="AL11" s="36">
-        <v>0.33457874089295703</v>
+        <v>0.33457734651987298</v>
       </c>
       <c r="AM11" s="36">
-        <v>1.9179854065498901E-2</v>
+        <v>7.9941359160439207E-3</v>
       </c>
       <c r="AN11" s="36">
         <v>6.5614302015975706E-2</v>
@@ -3395,25 +3394,25 @@
         <v>6.4564007421150302E-2</v>
       </c>
       <c r="AR11" s="36">
-        <v>6.0713618531664501E-2</v>
+        <v>5.5793991416309002E-2</v>
       </c>
       <c r="AS11" s="36">
-        <v>8.1045003813882494E-2</v>
+        <v>6.1561283144817402E-2</v>
       </c>
       <c r="AT11" s="36">
-        <v>6.0713618531664501E-2</v>
+        <v>5.5793991416309002E-2</v>
       </c>
       <c r="AU11" s="36">
-        <v>-2.0331385282217999E-2</v>
+        <v>-5.7672917285083404E-3</v>
       </c>
       <c r="AV11" s="36">
-        <v>6.4564007421150302E-2</v>
+        <v>6.6826215022091295E-2</v>
       </c>
       <c r="AW11" s="36">
-        <v>6.0713618531664501E-2</v>
+        <v>5.5793991416309002E-2</v>
       </c>
       <c r="AX11" s="36">
-        <v>-3.8503888894857899E-3</v>
+        <v>-1.10322236057823E-2</v>
       </c>
       <c r="AY11" s="36">
         <v>0.48269303917839501</v>
@@ -3428,25 +3427,25 @@
         <v>0.44471243042671599</v>
       </c>
       <c r="BC11" s="36">
-        <v>0.42648981879320003</v>
+        <v>0.43870125023325202</v>
       </c>
       <c r="BD11" s="36">
-        <v>0.43211289092296001</v>
+        <v>0.44298164287038799</v>
       </c>
       <c r="BE11" s="36">
-        <v>0.42648981879320003</v>
+        <v>0.43870125023325202</v>
       </c>
       <c r="BF11" s="37">
-        <v>-5.6230721297594903E-3</v>
+        <v>-4.2803926371350904E-3</v>
       </c>
       <c r="BG11" s="36">
-        <v>0.44471243042671599</v>
+        <v>0.43777614138438897</v>
       </c>
       <c r="BH11" s="36">
-        <v>0.42648981879320003</v>
+        <v>0.43870125023325202</v>
       </c>
       <c r="BI11" s="37">
-        <v>-1.82226116335161E-2</v>
+        <v>9.2510884886365396E-4</v>
       </c>
       <c r="BJ11" s="36">
         <v>0.164130848231267</v>
@@ -3461,25 +3460,25 @@
         <v>0.17532467532467499</v>
       </c>
       <c r="BN11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="BO11" s="36">
-        <v>0.169908466819222</v>
+        <v>0.18134618950491399</v>
       </c>
       <c r="BP11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="BQ11" s="36">
-        <v>8.3093549629562301E-3</v>
+        <v>-1.0418777674348401E-2</v>
       </c>
       <c r="BR11" s="36">
-        <v>0.17532467532467499</v>
+        <v>0.16881443298969101</v>
       </c>
       <c r="BS11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="BT11" s="37">
-        <v>2.8931464575028799E-3</v>
+        <v>2.11297884087466E-3</v>
       </c>
       <c r="BU11" s="36">
         <v>0.164130848231267</v>
@@ -3494,25 +3493,25 @@
         <v>0.17532467532467499</v>
       </c>
       <c r="BY11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="BZ11" s="36">
-        <v>0.169908466819222</v>
+        <v>0.18134618950491399</v>
       </c>
       <c r="CA11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="CB11" s="37">
-        <v>2.8931464575028799E-3</v>
+        <v>-4.3972634941099303E-3</v>
       </c>
       <c r="CC11" s="36">
-        <v>0.17532467532467499</v>
+        <v>0.16881443298969101</v>
       </c>
       <c r="CD11" s="36">
-        <v>0.17821782178217799</v>
+        <v>0.17092741183056501</v>
       </c>
       <c r="CE11" s="37">
-        <v>2.8931464575028799E-3</v>
+        <v>2.11297884087466E-3</v>
       </c>
       <c r="CF11" s="36">
         <v>0</v>
@@ -3586,19 +3585,19 @@
         <v>78</v>
       </c>
       <c r="M12" s="47">
-        <v>-0.143110795454545</v>
+        <v>5.4762276263290402E-2</v>
       </c>
       <c r="N12" s="48">
-        <v>-0.143110795454545</v>
+        <v>-6.3898981343200406E-2</v>
       </c>
       <c r="O12" s="48">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="P12" s="48">
-        <v>0.143110795454545</v>
+        <v>5.0732229231215002E-2</v>
       </c>
       <c r="Q12" s="48">
-        <v>0</v>
+        <v>-0.10549450549450499</v>
       </c>
       <c r="R12" s="36">
         <v>0.45781250000000001</v>
@@ -3613,25 +3612,25 @@
         <v>0.55569155446756402</v>
       </c>
       <c r="V12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.58113590263691695</v>
       </c>
       <c r="W12" s="36">
-        <v>0.59765625</v>
+        <v>0.52637362637362595</v>
       </c>
       <c r="X12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.58113590263691695</v>
       </c>
       <c r="Y12" s="36">
-        <v>-0.143110795454545</v>
+        <v>5.4762276263290402E-2</v>
       </c>
       <c r="Z12" s="36">
-        <v>0.55569155446756402</v>
+        <v>0.512820512820513</v>
       </c>
       <c r="AA12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.58113590263691695</v>
       </c>
       <c r="AB12" s="36">
-        <v>-0.10114609992211</v>
+        <v>6.8315389816404101E-2</v>
       </c>
       <c r="AC12" s="36">
         <v>0.45781250000000001</v>
@@ -3646,25 +3645,25 @@
         <v>0.55569155446756402</v>
       </c>
       <c r="AG12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.46247464503042601</v>
       </c>
       <c r="AH12" s="36">
-        <v>0.59765625</v>
+        <v>0.52637362637362595</v>
       </c>
       <c r="AI12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.46247464503042601</v>
       </c>
       <c r="AJ12" s="36">
-        <v>-0.143110795454545</v>
+        <v>-6.3898981343200406E-2</v>
       </c>
       <c r="AK12" s="36">
-        <v>0.55569155446756402</v>
+        <v>0.512820512820513</v>
       </c>
       <c r="AL12" s="36">
-        <v>0.45454545454545497</v>
+        <v>0.46247464503042601</v>
       </c>
       <c r="AM12" s="36">
-        <v>-0.10114609992211</v>
+        <v>-5.0345867790086797E-2</v>
       </c>
       <c r="AN12" s="36">
         <v>0</v>
@@ -3679,25 +3678,25 @@
         <v>0</v>
       </c>
       <c r="AR12" s="36">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="AS12" s="36">
         <v>0</v>
       </c>
       <c r="AT12" s="36">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="AU12" s="36">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="AV12" s="36">
         <v>0</v>
       </c>
       <c r="AW12" s="36">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="AX12" s="36">
-        <v>0</v>
+        <v>0.118661257606491</v>
       </c>
       <c r="AY12" s="36">
         <v>0.54218750000000004</v>
@@ -3712,25 +3711,25 @@
         <v>0.44430844553243598</v>
       </c>
       <c r="BC12" s="36">
-        <v>0.54545454545454497</v>
+        <v>0.418864097363083</v>
       </c>
       <c r="BD12" s="36">
-        <v>0.40234375</v>
+        <v>0.36813186813186799</v>
       </c>
       <c r="BE12" s="36">
-        <v>0.54545454545454497</v>
+        <v>0.418864097363083</v>
       </c>
       <c r="BF12" s="37">
-        <v>0.143110795454545</v>
+        <v>5.0732229231215002E-2</v>
       </c>
       <c r="BG12" s="36">
-        <v>0.44430844553243598</v>
+        <v>0.487179487179487</v>
       </c>
       <c r="BH12" s="36">
-        <v>0.54545454545454497</v>
+        <v>0.418864097363083</v>
       </c>
       <c r="BI12" s="37">
-        <v>0.10114609992211</v>
+        <v>-6.8315389816404004E-2</v>
       </c>
       <c r="BJ12" s="36">
         <v>0</v>
@@ -3748,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="BO12" s="36">
-        <v>0</v>
+        <v>0.10549450549450499</v>
       </c>
       <c r="BP12" s="36">
         <v>0</v>
       </c>
       <c r="BQ12" s="36">
-        <v>0</v>
+        <v>-0.10549450549450499</v>
       </c>
       <c r="BR12" s="36">
         <v>0</v>
@@ -3814,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="CK12" s="36">
-        <v>0</v>
+        <v>0.10549450549450499</v>
       </c>
       <c r="CL12" s="36">
         <v>0</v>
@@ -3870,19 +3869,19 @@
         <v>34</v>
       </c>
       <c r="M13" s="47">
-        <v>-7.6618440429617202E-3</v>
+        <v>9.1134266516560408E-3</v>
       </c>
       <c r="N13" s="48">
-        <v>-8.4522530502683102E-3</v>
+        <v>-2.7009536983207998E-4</v>
       </c>
       <c r="O13" s="48">
-        <v>7.90409007306633E-4</v>
+        <v>9.3835220214880909E-3</v>
       </c>
       <c r="P13" s="48">
-        <v>2.9265541169204998E-3</v>
+        <v>-1.0693660151403101E-2</v>
       </c>
       <c r="Q13" s="48">
-        <v>4.7352899260411597E-3</v>
+        <v>1.58023349974698E-3</v>
       </c>
       <c r="R13" s="36">
         <v>0.46475900657701003</v>
@@ -3897,25 +3896,25 @@
         <v>0.45549817739975701</v>
       </c>
       <c r="V13" s="36">
-        <v>0.45491271820448898</v>
+        <v>0.45682631160572301</v>
       </c>
       <c r="W13" s="36">
-        <v>0.46257456224745003</v>
+        <v>0.44771288495406703</v>
       </c>
       <c r="X13" s="36">
-        <v>0.45491271820448898</v>
+        <v>0.45682631160572301</v>
       </c>
       <c r="Y13" s="36">
-        <v>-7.6618440429617202E-3</v>
+        <v>9.1134266516560408E-3</v>
       </c>
       <c r="Z13" s="36">
-        <v>0.45549817739975701</v>
+        <v>0.45386119257086999</v>
       </c>
       <c r="AA13" s="36">
-        <v>0.45491271820448898</v>
+        <v>0.45682631160572301</v>
       </c>
       <c r="AB13" s="36">
-        <v>-5.8545919526825597E-4</v>
+        <v>2.9651190348533602E-3</v>
       </c>
       <c r="AC13" s="36">
         <v>0.34426229508196698</v>
@@ -3930,25 +3929,25 @@
         <v>0.329991899554475</v>
       </c>
       <c r="AG13" s="36">
-        <v>0.33102244389027402</v>
+        <v>0.32954093799681999</v>
       </c>
       <c r="AH13" s="36">
-        <v>0.339474696940543</v>
+        <v>0.32981103336665202</v>
       </c>
       <c r="AI13" s="36">
-        <v>0.33102244389027402</v>
+        <v>0.32954093799681999</v>
       </c>
       <c r="AJ13" s="36">
-        <v>-8.4522530502683102E-3</v>
+        <v>-2.7009536983207998E-4</v>
       </c>
       <c r="AK13" s="36">
-        <v>0.329991899554475</v>
+        <v>0.32913000977517098</v>
       </c>
       <c r="AL13" s="36">
-        <v>0.33102244389027402</v>
+        <v>0.32954093799681999</v>
       </c>
       <c r="AM13" s="36">
-        <v>1.0305443357988E-3</v>
+        <v>4.10928221649287E-4</v>
       </c>
       <c r="AN13" s="36">
         <v>0.120496711495043</v>
@@ -3963,25 +3962,25 @@
         <v>0.12550627784528101</v>
       </c>
       <c r="AR13" s="36">
-        <v>0.123890274314214</v>
+        <v>0.12728537360890299</v>
       </c>
       <c r="AS13" s="36">
-        <v>0.123099865306908</v>
+        <v>0.11790185158741499</v>
       </c>
       <c r="AT13" s="36">
-        <v>0.123890274314214</v>
+        <v>0.12728537360890299</v>
       </c>
       <c r="AU13" s="36">
-        <v>7.90409007306633E-4</v>
+        <v>9.3835220214880909E-3</v>
       </c>
       <c r="AV13" s="36">
-        <v>0.12550627784528101</v>
+        <v>0.124731182795699</v>
       </c>
       <c r="AW13" s="36">
-        <v>0.123890274314214</v>
+        <v>0.12728537360890299</v>
       </c>
       <c r="AX13" s="36">
-        <v>-1.61600353106701E-3</v>
+        <v>2.5541908132041E-3</v>
       </c>
       <c r="AY13" s="36">
         <v>0.42897810935505998</v>
@@ -3996,25 +3995,25 @@
         <v>0.420615633859862</v>
       </c>
       <c r="BC13" s="36">
-        <v>0.42254364089775598</v>
+        <v>0.42035969793322697</v>
       </c>
       <c r="BD13" s="36">
-        <v>0.41961708678083498</v>
+        <v>0.43105335808463002</v>
       </c>
       <c r="BE13" s="36">
-        <v>0.42254364089775598</v>
+        <v>0.42035969793322697</v>
       </c>
       <c r="BF13" s="37">
-        <v>2.9265541169204998E-3</v>
+        <v>-1.0693660151403101E-2</v>
       </c>
       <c r="BG13" s="36">
-        <v>0.420615633859862</v>
+        <v>0.42238514173997999</v>
       </c>
       <c r="BH13" s="36">
-        <v>0.42254364089775598</v>
+        <v>0.42035969793322697</v>
       </c>
       <c r="BI13" s="36">
-        <v>1.92800703789331E-3</v>
+        <v>-2.0254438067530702E-3</v>
       </c>
       <c r="BJ13" s="36">
         <v>0.10626288406793</v>
@@ -4029,25 +4028,25 @@
         <v>0.123886188740381</v>
       </c>
       <c r="BN13" s="36">
-        <v>0.122543640897756</v>
+        <v>0.122813990461049</v>
       </c>
       <c r="BO13" s="36">
-        <v>0.11780835097171399</v>
+        <v>0.12123375696130199</v>
       </c>
       <c r="BP13" s="36">
-        <v>0.122543640897756</v>
+        <v>0.122813990461049</v>
       </c>
       <c r="BQ13" s="36">
-        <v>4.7352899260411597E-3</v>
+        <v>1.58023349974698E-3</v>
       </c>
       <c r="BR13" s="36">
-        <v>0.123886188740381</v>
+        <v>0.12375366568915</v>
       </c>
       <c r="BS13" s="36">
-        <v>0.122543640897756</v>
+        <v>0.122813990461049</v>
       </c>
       <c r="BT13" s="37">
-        <v>-1.34254784262511E-3</v>
+        <v>-9.3967522810027603E-4</v>
       </c>
       <c r="BU13" s="36">
         <v>9.8409737901246699E-2</v>
@@ -4062,25 +4061,25 @@
         <v>0.113811259619279</v>
       </c>
       <c r="BY13" s="36">
-        <v>0.112518703241895</v>
+        <v>0.11178457869634301</v>
       </c>
       <c r="BZ13" s="36">
-        <v>0.108139311141043</v>
+        <v>0.107858536817554</v>
       </c>
       <c r="CA13" s="36">
-        <v>0.112518703241895</v>
+        <v>0.11178457869634301</v>
       </c>
       <c r="CB13" s="37">
-        <v>-1.2925563773837901E-3</v>
+        <v>-2.0266809229356501E-3</v>
       </c>
       <c r="CC13" s="36">
-        <v>0.113811259619279</v>
+        <v>0.113000977517107</v>
       </c>
       <c r="CD13" s="36">
-        <v>0.112518703241895</v>
+        <v>0.11178457869634301</v>
       </c>
       <c r="CE13" s="37">
-        <v>-1.2925563773837901E-3</v>
+        <v>-1.21639882076315E-3</v>
       </c>
       <c r="CF13" s="36">
         <v>7.8531461666830303E-3</v>
@@ -4095,25 +4094,25 @@
         <v>1.00749291211017E-2</v>
       </c>
       <c r="CJ13" s="36">
-        <v>1.0024937655860299E-2</v>
+        <v>1.10294117647059E-2</v>
       </c>
       <c r="CK13" s="36">
-        <v>9.6690398306715393E-3</v>
+        <v>1.3375220143747899E-2</v>
       </c>
       <c r="CL13" s="36">
-        <v>1.0024937655860299E-2</v>
+        <v>1.10294117647059E-2</v>
       </c>
       <c r="CM13" s="37">
-        <v>-4.9991465241309998E-5</v>
+        <v>9.5448264360422296E-4</v>
       </c>
       <c r="CN13" s="36">
-        <v>1.00749291211017E-2</v>
+        <v>1.0752688172042999E-2</v>
       </c>
       <c r="CO13" s="36">
-        <v>1.0024937655860299E-2</v>
+        <v>1.10294117647059E-2</v>
       </c>
       <c r="CP13" s="37">
-        <v>-4.9991465241309998E-5</v>
+        <v>2.7672359266287102E-4</v>
       </c>
     </row>
     <row r="14" spans="1:94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4154,19 +4153,19 @@
         <v>34</v>
       </c>
       <c r="M14" s="47">
-        <v>1.21592124944139E-2</v>
+        <v>-1.39694578495038E-2</v>
       </c>
       <c r="N14" s="48">
-        <v>2.90582686748821E-2</v>
+        <v>-2.1862325090706799E-3</v>
       </c>
       <c r="O14" s="48">
-        <v>-1.6899056180468199E-2</v>
+        <v>-1.17832253404331E-2</v>
       </c>
       <c r="P14" s="48">
-        <v>1.4061951944945699E-2</v>
+        <v>1.81292635810874E-2</v>
       </c>
       <c r="Q14" s="48">
-        <v>-2.6221164439359599E-2</v>
+        <v>-4.1598057315835896E-3</v>
       </c>
       <c r="R14" s="36">
         <v>0.44190476190476202</v>
@@ -4181,25 +4180,25 @@
         <v>0.36781002638522398</v>
       </c>
       <c r="V14" s="36">
-        <v>0.41305340027384801</v>
+        <v>0.40391198044009802</v>
       </c>
       <c r="W14" s="36">
-        <v>0.40089418777943397</v>
+        <v>0.417881438289602</v>
       </c>
       <c r="X14" s="36">
-        <v>0.41305340027384801</v>
+        <v>0.40391198044009802</v>
       </c>
       <c r="Y14" s="36">
-        <v>1.21592124944139E-2</v>
+        <v>-1.39694578495038E-2</v>
       </c>
       <c r="Z14" s="36">
-        <v>0.36781002638522398</v>
+        <v>0.41920801092398702</v>
       </c>
       <c r="AA14" s="36">
-        <v>0.41305340027384801</v>
+        <v>0.40391198044009802</v>
       </c>
       <c r="AB14" s="36">
-        <v>4.5243373888623303E-2</v>
+        <v>-1.5296030483889399E-2</v>
       </c>
       <c r="AC14" s="36">
         <v>0.32507936507936502</v>
@@ -4214,25 +4213,25 @@
         <v>0.36781002638522398</v>
       </c>
       <c r="AG14" s="36">
-        <v>0.36239160200821502</v>
+        <v>0.34621026894865498</v>
       </c>
       <c r="AH14" s="36">
-        <v>0.33333333333333298</v>
+        <v>0.34839650145772599</v>
       </c>
       <c r="AI14" s="36">
-        <v>0.36239160200821502</v>
+        <v>0.34621026894865498</v>
       </c>
       <c r="AJ14" s="36">
-        <v>2.90582686748821E-2</v>
+        <v>-2.1862325090706799E-3</v>
       </c>
       <c r="AK14" s="36">
-        <v>0.36781002638522398</v>
+        <v>0.35229858898498001</v>
       </c>
       <c r="AL14" s="36">
-        <v>0.36239160200821502</v>
+        <v>0.34621026894865498</v>
       </c>
       <c r="AM14" s="36">
-        <v>-5.4184243770088502E-3</v>
+        <v>-6.0883200363242599E-3</v>
       </c>
       <c r="AN14" s="36">
         <v>0.116825396825397</v>
@@ -4247,25 +4246,25 @@
         <v>0</v>
       </c>
       <c r="AR14" s="36">
-        <v>5.0661798265632101E-2</v>
+        <v>5.7701711491442501E-2</v>
       </c>
       <c r="AS14" s="36">
-        <v>6.7560854446100396E-2</v>
+        <v>6.9484936831875593E-2</v>
       </c>
       <c r="AT14" s="36">
-        <v>5.0661798265632101E-2</v>
+        <v>5.7701711491442501E-2</v>
       </c>
       <c r="AU14" s="36">
-        <v>-1.6899056180468199E-2</v>
+        <v>-1.17832253404331E-2</v>
       </c>
       <c r="AV14" s="36">
-        <v>0</v>
+        <v>6.6909421939007702E-2</v>
       </c>
       <c r="AW14" s="36">
-        <v>5.0661798265632101E-2</v>
+        <v>5.7701711491442501E-2</v>
       </c>
       <c r="AX14" s="36">
-        <v>5.0661798265632101E-2</v>
+        <v>-9.2077104475651993E-3</v>
       </c>
       <c r="AY14" s="36">
         <v>0.41714285714285698</v>
@@ -4280,25 +4279,25 @@
         <v>0.35778364116095002</v>
       </c>
       <c r="BC14" s="36">
-        <v>0.35782747603833898</v>
+        <v>0.33154034229828799</v>
       </c>
       <c r="BD14" s="36">
-        <v>0.343765524093393</v>
+        <v>0.31341107871720097</v>
       </c>
       <c r="BE14" s="36">
-        <v>0.35782747603833898</v>
+        <v>0.33154034229828799</v>
       </c>
       <c r="BF14" s="37">
-        <v>1.4061951944945699E-2</v>
+        <v>1.81292635810874E-2</v>
       </c>
       <c r="BG14" s="36">
-        <v>0.35778364116095002</v>
+        <v>0.32862994993172501</v>
       </c>
       <c r="BH14" s="36">
-        <v>0.35782747603833898</v>
+        <v>0.33154034229828799</v>
       </c>
       <c r="BI14" s="37">
-        <v>4.3834877388793103E-5</v>
+        <v>2.9103923665634301E-3</v>
       </c>
       <c r="BJ14" s="36">
         <v>0.140952380952381</v>
@@ -4313,25 +4312,25 @@
         <v>0.27440633245382601</v>
       </c>
       <c r="BN14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="BO14" s="36">
-        <v>0.25534028812717302</v>
+        <v>0.26870748299319702</v>
       </c>
       <c r="BP14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="BQ14" s="36">
-        <v>-2.6221164439359599E-2</v>
+        <v>-4.1598057315835896E-3</v>
       </c>
       <c r="BR14" s="36">
-        <v>0.27440633245382601</v>
+        <v>0.25216203914428797</v>
       </c>
       <c r="BS14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="BT14" s="37">
-        <v>-4.5287208766012103E-2</v>
+        <v>1.2385638117326099E-2</v>
       </c>
       <c r="BU14" s="36">
         <v>0.140952380952381</v>
@@ -4346,25 +4345,25 @@
         <v>0.27440633245382601</v>
       </c>
       <c r="BY14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="BZ14" s="36">
-        <v>0.25534028812717302</v>
+        <v>0.26870748299319702</v>
       </c>
       <c r="CA14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="CB14" s="36">
-        <v>-4.5287208766012103E-2</v>
+        <v>-9.8586551922121308E-3</v>
       </c>
       <c r="CC14" s="36">
-        <v>0.27440633245382601</v>
+        <v>0.25216203914428797</v>
       </c>
       <c r="CD14" s="36">
-        <v>0.22911912368781401</v>
+        <v>0.26454767726161399</v>
       </c>
       <c r="CE14" s="37">
-        <v>-4.5287208766012103E-2</v>
+        <v>1.2385638117326099E-2</v>
       </c>
       <c r="CF14" s="36">
         <v>0</v>
@@ -4699,104 +4698,104 @@
         <v>80</v>
       </c>
       <c r="B4" s="44">
-        <v>0.35336834001677597</v>
+        <v>0.35190578554422902</v>
       </c>
       <c r="C4" s="44">
-        <v>0.35563263009199197</v>
+        <v>0.35122998603206901</v>
       </c>
       <c r="D4" s="44">
-        <v>0.35190578554422902</v>
+        <v>0.350225672926265</v>
       </c>
       <c r="E4" s="44">
-        <v>0.350225672926265</v>
+        <v>0.35292469352014</v>
       </c>
       <c r="F4" s="44">
-        <v>0.35137453007518799</v>
+        <v>0.35523108652854601</v>
       </c>
       <c r="G4" s="45">
-        <v>1.14885714892338E-3</v>
+        <v>2.3063930084058501E-3</v>
       </c>
       <c r="H4" s="33">
-        <v>0.35563263009199197</v>
+        <v>0.35122998603206901</v>
       </c>
       <c r="I4" s="33">
-        <v>0.35137453007518799</v>
+        <v>0.35523108652854601</v>
       </c>
       <c r="J4" s="34">
-        <v>-4.2581000168037701E-3</v>
+        <v>4.0011004964774499E-3</v>
       </c>
       <c r="K4" s="33">
-        <v>8.4808861210373301E-2</v>
+        <v>8.5199824330259105E-2</v>
       </c>
       <c r="L4" s="33">
-        <v>8.5606330320535606E-2</v>
+        <v>7.9951978020709497E-2</v>
       </c>
       <c r="M4" s="33">
-        <v>8.5199824330259105E-2</v>
+        <v>8.1382568228058297E-2</v>
       </c>
       <c r="N4" s="33">
-        <v>8.1382568228058297E-2</v>
+        <v>8.1821366024518394E-2</v>
       </c>
       <c r="O4" s="33">
-        <v>8.3811090225563906E-2</v>
+        <v>8.1419330645917304E-2</v>
       </c>
       <c r="P4" s="34">
-        <v>2.4285219975056201E-3</v>
+        <v>-4.0203537860107602E-4</v>
       </c>
       <c r="Q4" s="33">
-        <v>8.5606330320535606E-2</v>
+        <v>7.9951978020709497E-2</v>
       </c>
       <c r="R4" s="33">
-        <v>8.3811090225563906E-2</v>
+        <v>8.1419330645917304E-2</v>
       </c>
       <c r="S4" s="34">
-        <v>-1.7952400949717399E-3</v>
+        <v>1.46735262520784E-3</v>
       </c>
       <c r="T4" s="33">
-        <v>0.43493390603286902</v>
+        <v>0.43833908596626903</v>
       </c>
       <c r="U4" s="33">
-        <v>0.43820488721804501</v>
+        <v>0.432420080622481</v>
       </c>
       <c r="V4" s="34">
-        <v>3.2709811851761601E-3</v>
+        <v>-5.9190053437886397E-3</v>
       </c>
       <c r="W4" s="33">
-        <v>0.12382713355460399</v>
+        <v>0.130478949980953</v>
       </c>
       <c r="X4" s="33">
-        <v>0.12660949248120301</v>
+        <v>0.13092950220305599</v>
       </c>
       <c r="Y4" s="34">
-        <v>2.78235892659941E-3</v>
+        <v>4.5055222210332901E-4</v>
       </c>
       <c r="Z4" s="33">
-        <v>0.118188186923616</v>
+        <v>0.122213628545373</v>
       </c>
       <c r="AA4" s="33">
-        <v>0.120347744360902</v>
+        <v>0.123628949095341</v>
       </c>
       <c r="AB4" s="34">
-        <v>2.15955743728644E-3</v>
+        <v>1.4153205499680701E-3</v>
       </c>
       <c r="AC4" s="33">
-        <v>5.6389466309877904E-3</v>
+        <v>8.2653214355801301E-3</v>
       </c>
       <c r="AD4" s="33">
-        <v>6.2617481203007504E-3</v>
+        <v>7.3005531077153796E-3</v>
       </c>
       <c r="AE4" s="34">
-        <v>6.2280148931296003E-4</v>
+        <v>-9.6476832786474595E-4</v>
       </c>
       <c r="AF4" s="55">
-        <v>0.44123896041252703</v>
+        <v>0.43118196405277798</v>
       </c>
       <c r="AG4" s="55">
-        <v>0.43518562030075197</v>
+        <v>0.43665041717446301</v>
       </c>
       <c r="AH4" s="56">
         <f>AG4/AF4-1</f>
-        <v>-1.3718961050301681E-2</v>
+        <v>1.2682471850830268E-2</v>
       </c>
     </row>
   </sheetData>
